--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_6.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_6.xlsx
@@ -618,247 +618,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02755</t>
+          <t>X ≈ -0.02754</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-32.02457821385138</v>
+        <v>-31.99179993544988</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-25.270474623566</v>
+        <v>-25.23722723505686</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-19.61152451293071</v>
+        <v>-19.57654253493688</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.126164607927102</v>
+        <v>-6.090234936388867</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.491811880292744</v>
+        <v>-6.426561474107629</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.7959337848514849</v>
+        <v>0.861058297451919</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.134000380528526</v>
+        <v>7.200095326105519</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6.859170646464904</v>
+        <v>6.925622524236587</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.902492262093432</v>
+        <v>6.968933581173602</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.36066651146594</v>
+        <v>20.4281071294818</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.5245112239988</v>
+        <v>13.59163588999588</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.25045667267906</v>
+        <v>13.31793906576547</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.014450891481737</v>
+        <v>5.083240920932631</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.91682617832591</v>
+        <v>11.98593707918232</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4.139983919791042</v>
+        <v>4.209871460083129</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.73472697743248</v>
+        <v>4.803964945025101</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>4.602592389648748</v>
+        <v>4.672025063256157</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.499380073768478</v>
+        <v>4.568974081976265</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.415709690194966</v>
+        <v>-2.346339649176066</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.229625666731337</v>
+        <v>-2.160430965399897</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.363501622331249</v>
+        <v>4.433378888479076</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.288929764792037</v>
+        <v>4.35893577522544</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-2.575805593918581</v>
+        <v>-2.506082501124894</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.652464494571383</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02566</t>
+          <t>X ≈ -0.02565</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-13.57915583469885</v>
+        <v>-13.54623108894411</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-20.53850020519738</v>
+        <v>-20.50522068670796</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-35.22584845689212</v>
+        <v>-35.19098939060284</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-35.94599010055038</v>
+        <v>-35.91027849948198</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-29.69189647514998</v>
+        <v>-29.62680936667498</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-22.88509673390716</v>
+        <v>-22.82012923922023</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.02817458995815</v>
+        <v>-16.96223031064244</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-17.31022345743515</v>
+        <v>-17.2439135156876</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-23.91078767183195</v>
+        <v>-23.8445154953282</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.41071130599182</v>
+        <v>-11.34343233027191</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.78179775107673</v>
+        <v>-17.71482157064202</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-11.42258712844557</v>
+        <v>-11.35521305253075</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.54649487035051</v>
+        <v>-12.47777644112369</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5222975769171754</v>
+        <v>0.5913661297060742</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.782852492738158</v>
+        <v>-6.713002006722135</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-12.84201999341472</v>
+        <v>-12.77283421783095</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.32680377356143</v>
+        <v>-6.257399926302099</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.2213350943081593</v>
+        <v>0.2909188489689356</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.219467630716913</v>
+        <v>-6.15010548831215</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-6.034537701029876</v>
+        <v>-5.965349314315482</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.579014675790795</v>
+        <v>-6.509149802039026</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.005775812393629565</v>
+        <v>0.07577839333082181</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>6.945138991621057</v>
+        <v>7.014865341518615</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.871345029238249</v>
+        <v>6.941199376948553</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02378</t>
+          <t>X ≈ -0.02377</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.913407724720308</v>
+        <v>4.94648247781867</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.43325988423393</v>
+        <v>11.46679031677751</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.43179172606482</v>
+        <v>13.46701604371717</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16.1537006032007</v>
+        <v>16.18978526270378</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.347719618646686</v>
+        <v>-1.282445047775873</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.695663170421923</v>
+        <v>5.760811135452677</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.928379738521038</v>
+        <v>4.994453988449088</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.652931781901266</v>
+        <v>4.719364048253304</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.169494100460362</v>
+        <v>-2.10310938824319</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4932429248801782</v>
+        <v>0.5605778768188827</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.668241019916898</v>
+        <v>-2.601198248947981</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.947244313866427</v>
+        <v>-2.879837372818642</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.505349066936461</v>
+        <v>-7.436614614997062</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.290679416621131</v>
+        <v>-4.221631359253877</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-4.94855398229565</v>
+        <v>-4.878700573576744</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-4.356518158853547</v>
+        <v>-4.287310598294091</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.491457230019741</v>
+        <v>-4.422051063242549</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.597461678164152</v>
+        <v>-4.527890300523737</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.9400183857365931</v>
+        <v>-0.8706482255910188</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.7535125097892248</v>
+        <v>-0.6843176924822529</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-1.296401382334139</v>
+        <v>-1.226531707361566</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.073482298059602</v>
+        <v>2.143485831989437</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.348807433606744</v>
+        <v>2.418531866594314</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.721919741884228</v>
+        <v>5.791774089589943</v>
       </c>
     </row>
     <row r="9">
@@ -868,79 +868,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.430102507988252</v>
+        <v>-5.28465945574056</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-10.60315209980076</v>
+        <v>-8.735407352201122</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-8.725729714311896</v>
+        <v>-7.103018263298047</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-19.37700785299387</v>
+        <v>-17.15603110161935</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-9.803992724147946</v>
+        <v>-11.2903297532096</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.992540189924945</v>
+        <v>-3.134636023752293</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.078401963526304</v>
+        <v>-7.012387970329279</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.040423956314491</v>
+        <v>-4.181353156383338</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.318035376594956</v>
+        <v>-7.251665808146143</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.771534016031708</v>
+        <v>-4.911662209164078</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.179754994823263</v>
+        <v>-1.527719312884592</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.862795855815534</v>
+        <v>1.307507416495767</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.57901668991795</v>
+        <v>-2.925527415541261</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.123911634548385</v>
+        <v>-6.262560062152588</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.458180634337808</v>
+        <v>-3.803839928137073</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.190908891346403</v>
+        <v>-6.329524624755663</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.326425250493877</v>
+        <v>-6.464905762401386</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.43301051656934</v>
+        <v>-6.571389338196497</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-6.219246077552143</v>
+        <v>-6.357896334578349</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.705124224382871</v>
+        <v>-3.052087922214398</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-3.248606112591396</v>
+        <v>-3.595021590341453</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-3.325525279059718</v>
+        <v>-3.67193648840459</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-3.051847337929296</v>
+        <v>-3.398663635293317</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-3.128654970760238</v>
+        <v>-3.475467289719624</v>
       </c>
     </row>
     <row r="10">
@@ -950,161 +950,161 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.565858299354048</v>
+        <v>4.536677875041917</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.233574751353913</v>
+        <v>5.987143442813824</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.015363164237073</v>
+        <v>-8.692383758060565</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.31469212916614</v>
+        <v>0.5380115058354917</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.678719312964098</v>
+        <v>0.203946520199473</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.920580548349314</v>
+        <v>3.702553284862262</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.473288559645603</v>
+        <v>-7.011719799418991</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-8.961900519847546</v>
+        <v>-7.290577455053679</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-18.55548738758459</v>
+        <v>-17.20480681889667</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-12.90789354239811</v>
+        <v>-11.3417259702366</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-22.27745915221744</v>
+        <v>-21.03242598019021</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-19.3487725473843</v>
+        <v>-17.99586628354415</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-14.04514124909418</v>
+        <v>-12.47614612128163</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.27036230127896</v>
+        <v>-12.70060227899749</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-18.14820481996877</v>
+        <v>-16.68440865603356</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-14.34245652512669</v>
+        <v>-12.77160607299292</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-14.48052108414991</v>
+        <v>-12.90900601456134</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-11.36984155931557</v>
+        <v>-9.690362117395985</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-7.936835121010567</v>
+        <v>-6.14969976895496</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.308945239481055</v>
+        <v>0.6933420317715928</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-5.074809476451932</v>
+        <v>-3.178679485484814</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-5.152312600206344</v>
+        <v>-3.255486036895867</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-4.879221494545462</v>
+        <v>-2.982107321502788</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.49500094321899</v>
+        <v>3.607866043613704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01813</t>
+          <t>X ≈ -0.01812</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.406935323319232</v>
+        <v>-6.564118788863318</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.295849063364486</v>
+        <v>4.449690064845186</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.386017980192804</v>
+        <v>10.23781031566038</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13.20023714264531</v>
+        <v>12.37233324317421</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10.07942811791379</v>
+        <v>9.200856113287855</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.741772169075141</v>
+        <v>6.543239035658097</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.975146226327674</v>
+        <v>5.778075138463791</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.69951811129215</v>
+        <v>2.660287110716894</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.742893602633416</v>
+        <v>2.703312121785018</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.557886867689639</v>
+        <v>-3.754943483748086</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.05188245955145</v>
+        <v>-6.32866091827588</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2028245950201892</v>
+        <v>-0.9158398072002925</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.9173702297872524</v>
+        <v>-2.035058582630043</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.138569761076702</v>
+        <v>-2.256324489328279</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.514456642720809</v>
+        <v>5.634596691580434</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.568205231112287</v>
+        <v>0.5290526533087743</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.206729888516733</v>
+        <v>3.246631956395873</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.330730422111749</v>
+        <v>0.2912553904324682</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.226664069967853</v>
+        <v>-2.345936555797522</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.814731445203911</v>
+        <v>-5.013815471069861</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-7.133706787994761</v>
+        <v>-8.411800081097198</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-9.987924739127862</v>
+        <v>-11.34561847376627</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-9.716384383770318</v>
+        <v>-11.07479417848312</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-12.57309941520531</v>
+        <v>-14.01118157543391</v>
       </c>
     </row>
     <row r="12">
@@ -1117,1142 +1117,1142 @@
         <v>52</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8567658047630502</v>
+        <v>-0.9723789224630792</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.016404917317026</v>
+        <v>-7.059901067561725</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.564569651022587</v>
+        <v>-6.656381218959503</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.268877398685007</v>
+        <v>3.233951973054012</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.07630479005907631</v>
+        <v>0.1427184366378569</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.096808175693042</v>
+        <v>4.163271679891253</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.312832443508839</v>
+        <v>3.380244076592277</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.030662954995542</v>
+        <v>3.09844333002065</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.587039016549987</v>
+        <v>-4.519307080093789</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.289465338869647</v>
+        <v>-7.220787860731626</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-7.013872210441001</v>
+        <v>-6.945471040935558</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.547887590968934</v>
+        <v>-1.479088218116843</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.36048527285727</v>
+        <v>-10.29034388106217</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.669901552856864</v>
+        <v>-8.599444457340077</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-17.0171056592488</v>
+        <v>-16.94584423765213</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-10.66079074321288</v>
+        <v>-10.59016571391028</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-10.8013101203138</v>
+        <v>-10.73047643292298</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.920424382504741</v>
+        <v>-7.001784767598139</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.706647890598639</v>
+        <v>-6.783451758087686</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-5.521824958942886</v>
+        <v>-6.593421817140403</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.144922807930925</v>
+        <v>-5.228175105266196</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-8.065898086751709</v>
+        <v>-7.995906776531342</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.716300395090542</v>
+        <v>-9.646582820701674</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-13.64147548358075</v>
+        <v>-13.5716211358739</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01436</t>
+          <t>X ≈ -0.01435</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>66</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-8.976141879540556</v>
+        <v>-8.954820490747018</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.728229789821079</v>
+        <v>2.765131770087578</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.907187866296503</v>
+        <v>-4.715605556340222</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.404269996482029</v>
+        <v>0.5956715358892808</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.477202312603545</v>
+        <v>-4.265812473418919</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-9.321989953672066</v>
+        <v>-10.10151069003508</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.571141112855571</v>
+        <v>-5.505156993482672</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-13.38872190676207</v>
+        <v>-13.32242114123179</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.33367708870311</v>
+        <v>-10.26736186354076</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.598565210744816</v>
+        <v>-9.531303379249117</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.81902479581138</v>
+        <v>-7.75202480022449</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.081156931564337</v>
+        <v>-5.013771580013326</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.348397658334306</v>
+        <v>1.417158306625844</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.127753483702158</v>
+        <v>1.196815020945486</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.039690638181433</v>
+        <v>-0.9698283849327183</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.4466922766485411</v>
+        <v>-0.3774736422225473</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.443744859458761</v>
+        <v>2.513171622808798</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.6854485598871918</v>
+        <v>-0.6161322834370822</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.982750191447956</v>
+        <v>-1.9140537849457</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.82316427973425</v>
+        <v>-4.75553711256164</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.340003173522128</v>
+        <v>-2.270918605318506</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-5.445027771328803</v>
+        <v>-5.375036588012961</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.142889818685738</v>
+        <v>-2.073170255055864</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-3.734715576820847</v>
+        <v>-3.664861229113214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01248</t>
+          <t>X ≈ -0.01247</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>79</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.44183514259052</v>
+        <v>-2.412360043159232</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.519983971699745</v>
+        <v>-1.488603092052259</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4535398882611901</v>
+        <v>-0.4191597281379558</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.170258391665229</v>
+        <v>-1.135069158648172</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4320056906263758</v>
+        <v>-0.215035008551034</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.159747012058411</v>
+        <v>-3.802438649545948</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.929182468226678</v>
+        <v>-4.580544439826916</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-9.244509252789769</v>
+        <v>-9.903966585626932</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.90544283598102</v>
+        <v>-2.839103340387943</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.156061055680162</v>
+        <v>-1.088770695525241</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.899010507624986</v>
+        <v>2.966049882883759</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.620595609730515</v>
+        <v>2.688003679525785</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.501136254251691</v>
+        <v>1.569886278331261</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.280577379711133</v>
+        <v>1.349629282948264</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.41196254647901</v>
+        <v>4.481834135768686</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.269547675793724</v>
+        <v>6.338778719561688</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>7.40099511406315</v>
+        <v>7.470428501913048</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.243175512280061</v>
+        <v>2.31345593125603</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.195847159065188</v>
+        <v>1.265571715582816</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.382889898699538</v>
+        <v>1.452516395221515</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4238922628271808</v>
+        <v>-0.354207570317655</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.7650395772046323</v>
+        <v>0.8350334213794426</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2255815993069135</v>
+        <v>-0.1558624712503729</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.567473536161081</v>
+        <v>-1.497619188453804</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0106</t>
+          <t>X ≈ -0.01059</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>101</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7.134435052638381</v>
+        <v>7.176918874773676</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.766844948114681</v>
+        <v>8.812311143275409</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>9.289634424236652</v>
+        <v>9.337429981943465</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.54589122109518</v>
+        <v>10.59313834810521</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>12.14738783831575</v>
+        <v>12.22567544310775</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.432726513956162</v>
+        <v>6.502971473788186</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.613115036065672</v>
+        <v>8.682844505112975</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>9.319606337455866</v>
+        <v>9.389816332199445</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11.33528601176101</v>
+        <v>11.40247330845087</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>13.51875316898619</v>
+        <v>13.58690005394632</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>9.854552357244174</v>
+        <v>9.922398762692815</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>10.56574608267988</v>
+        <v>10.63396390702911</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>14.37135253216622</v>
+        <v>14.44094860583568</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12.17932278826847</v>
+        <v>12.24921076756534</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12.50568144259562</v>
+        <v>12.57638838415142</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>8.170817291474414</v>
+        <v>8.240853406457376</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>9.027207015405253</v>
+        <v>9.097446710454079</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>12.87333608925432</v>
+        <v>12.94795565354204</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>12.69360290264134</v>
+        <v>12.18105252872636</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>13.87334726599794</v>
+        <v>13.36371230475569</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>13.33552998766601</v>
+        <v>12.81980077185977</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>14.25362485643549</v>
+        <v>13.73243797695506</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>12.55356440070226</v>
+        <v>12.62328799520553</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>11.49180707544438</v>
+        <v>11.56166142315166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00871</t>
+          <t>X ≈ -0.008705</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.956301362470015</v>
+        <v>-1.905194909654853</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4499853409955819</v>
+        <v>-0.4131298512343662</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.307090535073804</v>
+        <v>-9.196444767087279</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.584536650196505</v>
+        <v>-3.520697710350845</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.649585879649912</v>
+        <v>-7.521469729552926</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.924994854354715</v>
+        <v>-1.845101104269233</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.966026584678382</v>
+        <v>-5.376276793185284</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1208816790997531</v>
+        <v>-1.100740371795752</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.00146765123322</v>
+        <v>-1.972584483777567</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.708809872102165</v>
+        <v>-3.677810177864721</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.354444715488427</v>
+        <v>-3.784185749650263</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-9.173057963315323</v>
+        <v>-9.021447837845898</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.853940516483625</v>
+        <v>-3.751314823861797</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3839512698863174</v>
+        <v>-0.3143449372157363</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.7909221933674573</v>
+        <v>0.8522935779715652</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.301228284453373</v>
+        <v>-2.211425937051963</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5871675484192025</v>
+        <v>-0.5142428148780951</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.620087130491989</v>
+        <v>-1.53716016779024</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.400355650314744</v>
+        <v>-1.320163398012774</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.6621118714600058</v>
+        <v>-1.131164270190709</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2856516135366647</v>
+        <v>-0.7624648117226442</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.213919668588225</v>
+        <v>-2.674123208013789</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.4600511664141678</v>
+        <v>-1.478733787814747</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.387914230019497</v>
+        <v>-2.844733344765494</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006827</t>
+          <t>X ≈ -0.006822</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.703214504259066</v>
+        <v>-3.023757576012557</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4200178341666643</v>
+        <v>0.07996091667877181</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3331904457908763</v>
+        <v>-0.01500698000478451</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.078676276177703</v>
+        <v>1.332870629055307</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.5488085792433</v>
+        <v>5.800023424378374</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.202648850388627</v>
+        <v>8.058519651219456</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.586368791701844</v>
+        <v>3.14539884094264</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.381216774319938</v>
+        <v>4.628095434249737</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.585803262303727</v>
+        <v>7.419875394303787</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>8.509931341303393</v>
+        <v>7.72586070454615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>9.478793941929368</v>
+        <v>8.688459136670453</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>8.511290214300075</v>
+        <v>7.721722712076172</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.392559667030945</v>
+        <v>7.000056745624939</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.174217698685503</v>
+        <v>6.781868180080849</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.133488314392217</v>
+        <v>4.752174268978969</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.729791771717466</v>
+        <v>5.347471282363898</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>6.291559254929297</v>
+        <v>5.90422515829772</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.186820203479627</v>
+        <v>5.802000340610476</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.402699001765832</v>
+        <v>6.020005501893941</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.670344846709582</v>
+        <v>8.277255274129573</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>9.518860893332366</v>
+        <v>9.117253453810015</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>11.52921659647485</v>
+        <v>11.11037300964228</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>12.49801010965154</v>
+        <v>12.07450289453813</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>11.73245614035073</v>
+        <v>11.30901546890106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004943</t>
+          <t>X ≈ -0.004939</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.985029065204628</v>
+        <v>-3.371622945856359</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8739511502118944</v>
+        <v>1.404356519730065</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.703335984505621</v>
+        <v>-3.09453353394467</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.378855682063602</v>
+        <v>-2.785188738827955</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1143492901916332</v>
+        <v>0.4581733528750149</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4384231379957271</v>
+        <v>0.1318996732519508</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.264430362403836</v>
+        <v>-2.680834627306872</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.124600175961298</v>
+        <v>2.153800650316896</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.167974675574037</v>
+        <v>2.19479595965737</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8659684722696213</v>
+        <v>0.9131902392123976</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.972822392895438</v>
+        <v>-1.880630307452613</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1757989192874305</v>
+        <v>-0.1142902092073612</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7657685503092182</v>
+        <v>0.8103425247883038</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.016456397017393</v>
+        <v>-0.4326832853596017</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.6489641412072018</v>
+        <v>-0.06517386963096072</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.731259735797842</v>
+        <v>-4.077688467540519</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.824597655207675</v>
+        <v>-3.189201581053794</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.974794843531427</v>
+        <v>-4.319160119229601</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.671791241704469</v>
+        <v>-2.055387418399611</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1265134317063641</v>
+        <v>0.6936981512452007</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.4030524297605211</v>
+        <v>0.6645567252512095</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.676376530815638</v>
+        <v>1.614351789483138</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.3912154357806656</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.704678362573219</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.00306</t>
+          <t>X ≈ -0.003056</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.472641220460538</v>
+        <v>3.30728745593386</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.015204435916736</v>
+        <v>-1.199464355027615</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.073692176585851</v>
+        <v>-1.249880377176375</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.0586979748998786</v>
+        <v>-0.1080627978586506</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.691239717262476</v>
+        <v>-1.834962727637247</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1185585555017568</v>
+        <v>-0.2560258558018162</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.278032346958469</v>
+        <v>-1.957451894017225</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.018163167275993</v>
+        <v>-2.699386996621499</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.899435748301293</v>
+        <v>-3.584978032477402</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.214710112384623</v>
+        <v>-3.89552340974479</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.327645135507247</v>
+        <v>-5.012327159526613</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.609048805680466</v>
+        <v>-5.291076562974609</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.276475295249774</v>
+        <v>-5.951929847383681</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.575897301985776</v>
+        <v>-5.711739219689584</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-5.778233236593948</v>
+        <v>-5.910292856161853</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.907318536963231</v>
+        <v>-5.317676304980942</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.969479838753259</v>
+        <v>-6.382420971896067</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.296685477070774</v>
+        <v>-3.703036201170505</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.080562314138959</v>
+        <v>-3.487100954132458</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.430555555555443</v>
+        <v>-2.560765027499748</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6589411497387019</v>
+        <v>-0.7784963457088381</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.660822131307228</v>
+        <v>-1.784574865257468</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-5.55271363149177</v>
+        <v>-5.696146664403322</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-7.480506822612085</v>
+        <v>-7.167327754835902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001176</t>
+          <t>X ≈ -0.001172</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.621637467449041</v>
+        <v>-0.4097023615410222</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.481243089989206</v>
+        <v>2.680445181343892</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.71357250498869</v>
+        <v>3.90428380371376</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.999989523626965</v>
+        <v>3.191535796023715</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.634544462076711</v>
+        <v>2.855573647015888</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.294459265906994</v>
+        <v>1.521110428468596</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.812169877523139</v>
+        <v>3.031014001562141</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9042655635517036</v>
+        <v>-0.6719501079649461</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.00861628290064</v>
+        <v>-1.771955586862688</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.313184108594008</v>
+        <v>-4.067639743937384</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.65868329709901</v>
+        <v>-3.413093993268724</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.617694910661854</v>
+        <v>-6.355486503308839</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.599956911436699</v>
+        <v>-6.337808279903363</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.293135083251762</v>
+        <v>-5.039252227178771</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.809028461036291</v>
+        <v>-4.558838164228149</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.063513634325084</v>
+        <v>-2.822897277250576</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.117627986901319</v>
+        <v>-4.102111799721634</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-6.138320215257323</v>
+        <v>-6.116911891830185</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.155913527421284</v>
+        <v>-5.139230529252401</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-4.968869731800851</v>
+        <v>-4.949308038134426</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.745786615894509</v>
+        <v>-4.504752337187625</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.588025196441329</v>
+        <v>-5.343957077222683</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.014399455246554</v>
+        <v>-2.779406028862759</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.70719903206291</v>
+        <v>-2.473558892773063</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007074</t>
+          <t>X ≈ 0.0007113</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.223351210929202</v>
+        <v>-1.36208174304344</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.542864037988615</v>
+        <v>-2.349802600005127</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.016646721893245</v>
+        <v>-1.828356682740264</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.38765454657031</v>
+        <v>-3.196364062328236</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7907936005114991</v>
+        <v>-0.5797739508485975</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.045769240394186</v>
+        <v>1.251153540211725</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.06291435648279275</v>
+        <v>0.1445065510355619</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6730451673648332</v>
+        <v>-0.7923440664694752</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.619471519297754</v>
+        <v>-1.7355462263059</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.218176116254185</v>
+        <v>-1.529045814424485</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7023863126054124</v>
+        <v>0.3858111804004807</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8960524993121766</v>
+        <v>-1.207052616251204</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.694259716278466</v>
+        <v>-2.005851955334677</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.56692498976858</v>
+        <v>-3.671699549167137</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.708407323671963</v>
+        <v>-3.020237270191117</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.783314270750289</v>
+        <v>-2.098564705396093</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.91740796489929</v>
+        <v>-2.234404898980401</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.682457387595036</v>
+        <v>-3.00016486950922</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.806268218062598</v>
+        <v>-1.926773955887086</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.599422442244261</v>
+        <v>-3.713612356445452</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.142622851242216</v>
+        <v>-4.256158524411447</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.548610910185111</v>
+        <v>-4.660951854241553</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.94380274040266</v>
+        <v>-4.057529773338452</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.689711076370791</v>
+        <v>-3.804414658140672</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002591</t>
+          <t>X ≈ 0.002595</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.507620191868533</v>
+        <v>1.404263605105179</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.389429451001035</v>
+        <v>-3.506503608937521</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.174539760376646</v>
+        <v>-1.583671829278316</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8466909818569519</v>
+        <v>0.7516564591041828</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.862968220446362</v>
+        <v>-2.938742672712024</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.503187685706202</v>
+        <v>-4.584740859739455</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.014768328538352</v>
+        <v>-1.387288009100573</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.115010993995874</v>
+        <v>-3.187678783090853</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.07278292168229</v>
+        <v>-2.840578640523546</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.715085578727034</v>
+        <v>-1.780351595737528</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.659878040740196</v>
+        <v>-2.421882401649228</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.244848662436105</v>
+        <v>-3.003569550283551</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.325281062136376</v>
+        <v>-1.379603577523248</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.243511341818959</v>
+        <v>-1.295247841014955</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.207320629636783</v>
+        <v>-2.258103501419427</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-3.441528872698285</v>
+        <v>-3.49928293907999</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.74635427416429</v>
+        <v>-1.80318802182429</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.375727934162043</v>
+        <v>-3.43934166064853</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.464482820010673</v>
+        <v>-3.529260677277691</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.801829268292643</v>
+        <v>-4.87146685507728</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.95478577485158</v>
+        <v>-6.025633818150304</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.506350586591779</v>
+        <v>-4.572427791791853</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.365721761573063</v>
+        <v>-6.438625862184416</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-6.136785052061043</v>
+        <v>-6.208647717854177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.004475</t>
+          <t>X ≈ 0.004478</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7688704965612274</v>
+        <v>-0.9256837502554163</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.630221560402582</v>
+        <v>-3.777774499806121</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.156838876093659</v>
+        <v>2.3448097121884</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.244232065021301</v>
+        <v>3.066568861645031</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.7151419195781727</v>
+        <v>0.5747970323964822</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5454422054055712</v>
+        <v>-0.6807731571100035</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.21344060214232</v>
+        <v>1.429836308052273</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.188558578579247</v>
+        <v>4.39355980517535</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.675036686390037</v>
+        <v>5.514853766997113</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.266064490080694</v>
+        <v>5.465441480678152</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.82150197594482</v>
+        <v>4.659973743172493</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.547289729086607</v>
+        <v>4.384577142597777</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.149535549136431</v>
+        <v>4.34261885684603</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.930578442557113</v>
+        <v>4.122098780878318</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.083241406418402</v>
+        <v>5.269871017962608</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>5.678301456039826</v>
+        <v>5.866780515700299</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.732613558992341</v>
+        <v>3.932438086993116</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.43922434579558</v>
+        <v>5.634505478313031</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.930709827567973</v>
+        <v>5.12837519858747</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>5.117753623188406</v>
+        <v>5.315221008555611</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.762959011291905</v>
+        <v>2.967620688964999</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.600047433910156</v>
+        <v>1.808742236581168</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.874822600392328</v>
+        <v>2.083216949063221</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.523518942283239</v>
+        <v>2.729406356489761</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006358</t>
+          <t>X ≈ 0.006361</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1779582663450796</v>
+        <v>0.3556843076962224</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.823858069540755</v>
+        <v>-2.779265315509399</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.408744223465902</v>
+        <v>-2.345077050549719</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.056311293862073</v>
+        <v>-4.00051327395483</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2494563400469758</v>
+        <v>-0.1250470144476665</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.381358459752065</v>
+        <v>-2.278889845577218</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.686459561187725</v>
+        <v>-2.578717627904744</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6463865500028305</v>
+        <v>-0.5165599552216307</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.530740874031174</v>
+        <v>-1.409636781034429</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4471275185887791</v>
+        <v>-0.3077057443351521</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.026929677760542</v>
+        <v>-1.902334217837357</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.405812516259139</v>
+        <v>1.56245120711452</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.434762665439926</v>
+        <v>-3.296767391697429</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.521730286799055</v>
+        <v>-5.386094484017377</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.994615014208492</v>
+        <v>-1.83721091670111</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.4609101516918983</v>
+        <v>0.6263204111046363</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.6034161005965615</v>
+        <v>-0.4464507736242211</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.173515795761602</v>
+        <v>-1.023008801106002</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.352741470039042</v>
+        <v>-2.215568124406929</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.235465116279066</v>
+        <v>-1.089755178288769</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.2456329260457224</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.936077093498966</v>
+        <v>1.108754100786861</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.675968539050821</v>
+        <v>1.852712381344027</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7255541955664384</v>
+        <v>-0.5705377122548398</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.008242</t>
+          <t>X ≈ 0.008245</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>186</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.036983615542944</v>
+        <v>-1.003709323224115</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3127830114879373</v>
+        <v>-0.2791100028745959</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6831611511189877</v>
+        <v>-0.6478067274505008</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.278679349076398</v>
+        <v>-7.242485631657495</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-9.791635788242864</v>
+        <v>-9.725962758347187</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.919862857557995</v>
+        <v>-6.854388254571724</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.629736068819689</v>
+        <v>-6.563344017669742</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.231820201369409</v>
+        <v>-4.165084949453977</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.728130000405656</v>
+        <v>-4.661423631598154</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.293998437810096</v>
+        <v>-2.226372334269655</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6355793737010629</v>
+        <v>-0.884798768699163</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9196791665023625</v>
+        <v>-1.167164974240066</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.706922465867713</v>
+        <v>1.450040593188206</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.890372738957339</v>
+        <v>2.295571439626912</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.306710317124335</v>
+        <v>3.039902220847083</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.6759639151328187</v>
+        <v>0.4182180960472124</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.608667413424705</v>
+        <v>-1.869901266699806</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.587424439297273</v>
+        <v>2.657136587353897</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.341182010831183</v>
+        <v>3.410662376880317</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.3024193548387117</v>
+        <v>0.3717017352354404</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.8344877630450611</v>
+        <v>0.9044243844737139</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.296167116004597</v>
+        <v>1.366212831666758</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.4956734652824295</v>
+        <v>0.5654187269445146</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.570269760422562</v>
+        <v>2.640124108129839</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>163</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.121027540150436</v>
+        <v>-2.087753247831607</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.217302562939118</v>
+        <v>1.250975571552459</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2217987938169657</v>
+        <v>-0.1864443701484788</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3275349220316386</v>
+        <v>-0.2913412046127348</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.07695912678628503</v>
+        <v>-0.01128609689060767</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.33999647359559</v>
+        <v>-2.27452187060932</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.497017025380131</v>
+        <v>-2.430624974230184</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8901455515441086</v>
+        <v>0.9568808034595406</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.155564381814692</v>
+        <v>2.222270750622194</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.772473571406735</v>
+        <v>0.8400996749471759</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.103893768656327</v>
+        <v>4.171220247243355</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.442954968528134</v>
+        <v>4.505919994744445</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.77681299876803</v>
+        <v>5.830563458384127</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.328462322702968</v>
+        <v>4.389775568000196</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4.283028016181042</v>
+        <v>4.342684992048483</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.718578863348434</v>
+        <v>6.778667783537372</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.197982101714842</v>
+        <v>7.267551537497368</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.252507888073524</v>
+        <v>5.322220036130147</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.014643320944025</v>
+        <v>3.084123686993159</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.428680981595122</v>
+        <v>4.49796336199185</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.725971370143178</v>
+        <v>5.795907991571831</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.036519381985208</v>
+        <v>5.106565097647369</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.311294548467338</v>
+        <v>5.381039810129423</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.848850141714202</v>
+        <v>5.918704489421479</v>
       </c>
     </row>
     <row r="27">
@@ -2347,240 +2347,240 @@
         <v>114</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.713626663579426</v>
+        <v>3.746900955898255</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.870787619273841</v>
+        <v>6.904460627887183</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.930153675271704</v>
+        <v>1.965508098940191</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.223729227430454</v>
+        <v>1.259922944849357</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.724788766751914</v>
+        <v>1.790461796647591</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.580383090580099</v>
+        <v>-1.514908487593829</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.486919898288662</v>
+        <v>-1.420527847138715</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.381656535998005</v>
+        <v>-4.314921284082573</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.591515947355369</v>
+        <v>-2.524809578547867</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.620411267180728</v>
+        <v>-1.552785163640287</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.218522045537433</v>
+        <v>-2.151195566950406</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.750623767799929</v>
+        <v>2.815928600461689</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.149646924072002</v>
+        <v>1.690310245154926</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.805483095493848</v>
+        <v>2.336788837279116</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.3921658915442165</v>
+        <v>-0.06997898392140911</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.7671600237466905</v>
+        <v>-1.224783288287853</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9012537178956137</v>
+        <v>-0.8316842821130876</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.760623098903146</v>
+        <v>-2.690910950846522</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-4.29888590088364</v>
+        <v>-4.229405534834505</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-5.866228070175481</v>
+        <v>-5.796945689778752</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.023463566892744</v>
+        <v>-1.953526945464091</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.099418622535296</v>
+        <v>-2.029372906873135</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.701836438509311</v>
+        <v>-2.632091176847226</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.023391812865491</v>
+        <v>-0.9535374651582131</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01389</t>
+          <t>X ≈ 0.0139</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>104</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.977907393783987</v>
+        <v>5.011181686102816</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8119948164196487</v>
+        <v>0.8456678250329901</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.209422883356424</v>
+        <v>3.244777307024911</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.573869570500392</v>
+        <v>0.6100632879192958</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.172218986009007</v>
+        <v>1.237892015904684</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.315698264345166</v>
+        <v>2.381172867331436</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.5901697345634176</v>
+        <v>0.6565617857133645</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6501779776869867</v>
+        <v>-0.5834427257715546</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.525856577825209</v>
+        <v>-2.459150209017707</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.214147453054217</v>
+        <v>-5.146521349513776</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.940701252839268</v>
+        <v>-4.873374774252241</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.360139860139853</v>
+        <v>-2.280440981010869</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.523092617088544</v>
+        <v>-2.443636114935984</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.744449428122898</v>
+        <v>-2.660149656880506</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.441842205621739</v>
+        <v>-2.359239088430506</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.846782156000359</v>
+        <v>-1.777389277389283</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.019337388610815</v>
+        <v>-0.9497679528282887</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.124320804706066</v>
+        <v>-1.054608656649442</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.05334081976418048</v>
+        <v>0.122821185813315</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.201923076923073</v>
+        <v>1.271205457319802</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.6587226679251188</v>
+        <v>0.7286592893537716</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.544306073820977</v>
+        <v>1.614351789483138</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.819081240303106</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.7816014394961712</v>
+        <v>0.8514557872034487</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01577</t>
+          <t>X ≈ 0.01578</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>53</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.824131406417514</v>
+        <v>-3.790857114098685</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.312517135076028</v>
+        <v>-2.278844126462687</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.788285101017728</v>
+        <v>3.823639524686214</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.2143677795573</v>
+        <v>1.250561496976204</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8157624388296369</v>
+        <v>0.8814354687253143</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.909720838088823</v>
+        <v>2.975195441075094</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2033924752194238</v>
+        <v>0.2697845263693708</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.831631615953263</v>
+        <v>1.898366867868695</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.907104335825238</v>
+        <v>-1.840397967017736</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.707608191157583</v>
+        <v>-2.639982087617142</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.200166718561874</v>
+        <v>-6.132840239974847</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.299181950125345</v>
+        <v>-6.371586976578456</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.423673168612545</v>
+        <v>-7.501416154575331</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.871445073986465</v>
+        <v>-3.982245681065166</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-3.530376313023766</v>
+        <v>-4.640388978645724</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.048523810572199</v>
+        <v>-0.979130931961123</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.182617504721122</v>
+        <v>-1.113048068938596</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.287600920816402</v>
+        <v>-1.217888772759778</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.8153146949456058</v>
+        <v>0.8847950609947404</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.662735849056602</v>
+        <v>6.732018229453331</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>8.006327892888841</v>
+        <v>8.076264514317494</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.043580384416039</v>
+        <v>6.1136261000782</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.431563098067919</v>
+        <v>4.501308359730004</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>10.01599911729007</v>
+        <v>10.08585346499735</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>51</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.654513562613545</v>
+        <v>-4.621239270294716</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>10.69658543254602</v>
+        <v>10.73025844115936</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.374532027283415</v>
+        <v>3.409886450951902</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.260829913360631</v>
+        <v>-1.224636195941727</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3346846153407483</v>
+        <v>0.4003576452364257</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.438935085377985</v>
+        <v>-1.373460482391714</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2510169037064927</v>
+        <v>-0.1846248525565457</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.490355862950537</v>
+        <v>-2.423620611035105</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.472728829523135</v>
+        <v>1.539435198330636</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.620462046204622</v>
+        <v>4.688088149745063</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9875316278565123</v>
+        <v>-0.9202051492694849</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.654943096119567</v>
+        <v>2.722614074733499</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4303324360930034</v>
+        <v>-0.3613323058480447</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.573257874578374</v>
+        <v>-4.503979809745651</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-3.271404799890213</v>
+        <v>-3.201338793600748</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.849654130692258</v>
+        <v>-0.780084694909732</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.183054243595251</v>
+        <v>3.252534609644385</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.370098039215684</v>
+        <v>3.439380419612412</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.866113316492239</v>
+        <v>0.9360499379208918</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.7901582608496582</v>
+        <v>0.8602039765118192</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.064933427331816</v>
+        <v>1.134678688993901</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.94977640178876</v>
+        <v>3.019630749496038</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>26.3258785942492</v>
+        <v>26.35915288656803</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>17.41927450817635</v>
+        <v>17.45294751678969</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>15.97957404409021</v>
+        <v>16.0149284677587</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.26578073089701</v>
+        <v>15.30197444831592</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.90051094587292</v>
+        <v>14.9661839757686</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.23053270173693</v>
+        <v>12.2960073047232</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.31480942682573</v>
+        <v>14.38120147797567</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.607683352735734</v>
+        <v>2.674418604651166</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.363485132044076</v>
+        <v>8.430191500851578</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.006866131247129</v>
+        <v>5.074192609834157</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.603281009285084</v>
+        <v>3.672281139530043</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.95335276967926</v>
+        <v>12.02263083451199</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.437278673499144</v>
+        <v>8.507344679788609</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.04110217182874</v>
+        <v>6.110671607611266</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>11.65040447001914</v>
+        <v>11.72011661807576</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>14.72367049009386</v>
+        <v>14.79315085614299</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>12.05357142857143</v>
+        <v>12.12285380896816</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>11.51037101957348</v>
+        <v>11.58030764100213</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>11.50446167959303</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.709191130413</v>
+        <v>11.77893639207508</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.918964076858892</v>
+        <v>5.988818424566169</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>17.75445002282063</v>
+        <v>17.78772431513946</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.27641736531917</v>
+        <v>10.31009037393251</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.4081454726616</v>
+        <v>12.44349989633009</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.551495016611291</v>
+        <v>4.587688734030195</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.75765380301587</v>
+        <v>7.823326832911548</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.944818416022613</v>
+        <v>8.010293019008884</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.7433808553971</v>
+        <v>10.80977290654705</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.893397638450068</v>
+        <v>6.9601328903655</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.93491370347266</v>
+        <v>7.001620072280161</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.7325068641318</v>
+        <v>9.800132967672241</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.57829470267575</v>
+        <v>13.64562118126278</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9865134865134308</v>
+        <v>-0.9188425078994982</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.111004705000575</v>
+        <v>-2.042004574755616</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.81049562682221</v>
+        <v>4.879773691654933</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.151564387784909</v>
+        <v>4.221630394074374</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.318053008834816</v>
+        <v>8.387445887445892</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>8.183959314685893</v>
+        <v>8.253528750468419</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.078975898590713</v>
+        <v>8.148688046647337</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.295099061522372</v>
+        <v>8.364579427571506</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.162860476746133</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.7960853052877539</v>
+        <v>0.8660219267164067</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.422726893212037</v>
+        <v>-6.352681177549876</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.576523155301338</v>
+        <v>-2.506777893639253</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.9189640768587637</v>
+        <v>0.9888184245660412</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.962242230612837</v>
+        <v>9.995516522931666</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>9.62706671596851</v>
+        <v>9.660739724581852</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.157063221579349</v>
+        <v>5.192417645247836</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.473572938689216</v>
+        <v>7.50976665610812</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.047697093059114</v>
+        <v>1.113370122954791</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.2348617060659</v>
+        <v>1.30033630905217</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.492298604314946</v>
+        <v>3.558690655464893</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.183440928493269</v>
+        <v>0.250176180408701</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.805346036787093</v>
+        <v>-2.738639667979591</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.579181447556522</v>
+        <v>-3.511555344016081</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2745191501381896</v>
+        <v>-0.2071926715511623</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.583916083916129</v>
+        <v>-3.516245105302197</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.708407302403273</v>
+        <v>-4.639407172158315</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.929764113437628</v>
+        <v>-4.860486048604905</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-2.558392322171869</v>
+        <v>-2.488326315882404</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-8.023938333156529</v>
+        <v>-7.954545454545453</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-5.127728997002407</v>
+        <v>-5.058159561219881</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.202409382794691</v>
+        <v>-2.132697234738067</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-5.016589250165843</v>
+        <v>-4.947108884116709</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.82954545454546</v>
+        <v>-4.760263074148732</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.6878601970626548</v>
+        <v>0.7577968184913075</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.6119051414200456</v>
+        <v>0.6819508570822066</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.8866803079022176</v>
+        <v>0.9564255695643027</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.91378000268181</v>
+        <v>22.94745301129515</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.089464153980224</v>
+        <v>6.124818577648711</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.375670840787066</v>
+        <v>5.41186455820597</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.681906636544618</v>
+        <v>-2.61623360664894</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-2.494742023537832</v>
+        <v>-2.429267420551561</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.424699536715892</v>
+        <v>4.491091587865839</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.146144891197217</v>
+        <v>4.212880143112649</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.187660956219851</v>
+        <v>4.254367325027353</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.10613323775816</v>
+        <v>11.17375934129861</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.3804925048735</v>
+        <v>11.44781898346053</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.409090909090914</v>
+        <v>3.476761887704846</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.28459969060377</v>
+        <v>2.353599820848729</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.755550571877102</v>
+        <v>9.824828636709825</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.404311640532057</v>
+        <v>1.474377646821523</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.999371690153495</v>
+        <v>2.068764568764571</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.557585688312201</v>
+        <v>9.627155124094728</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.452602272216922</v>
+        <v>9.522314420273545</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.668725435148794</v>
+        <v>9.738205801197928</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.16346153846154</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.620261129463586</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>9.236613766128606</v>
+        <v>9.306659481790767</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>17.20369662491844</v>
+        <v>17.27344188658053</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>9.435447593342268</v>
+        <v>9.505301941049545</v>
       </c>
     </row>
   </sheetData>
@@ -3180,83 +3180,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02849</t>
+          <t>X &gt; -0.02848</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3345</v>
+        <v>3349</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02210240337549862</v>
+        <v>-0.02281627120183316</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.07445716335896435</v>
+        <v>0.07361963612684974</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.07169494835529377</v>
+        <v>-0.07239667001159233</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02608936037872667</v>
+        <v>-0.02686412184054632</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1368595314499572</v>
+        <v>-0.138159424299225</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3194864138486793</v>
+        <v>-0.3205653118494567</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3023402289913903</v>
+        <v>-0.3034602655095995</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2664612470857506</v>
+        <v>-0.2676319154082734</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2972291536702087</v>
+        <v>-0.2983629411392457</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1311855613349664</v>
+        <v>-0.1325376920278671</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2564708890881064</v>
+        <v>-0.2576676774098274</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2801004476607716</v>
+        <v>-0.2812771574511359</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2550537429710005</v>
+        <v>-0.256290289041381</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2501814010679837</v>
+        <v>-0.251430323145442</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1460759563671132</v>
+        <v>-0.1474668576911782</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2190779186927756</v>
+        <v>-0.2203672109838379</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1266441629820321</v>
+        <v>-0.1280479564956565</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.03480676756448986</v>
+        <v>-0.0363236629546364</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.09935722845624895</v>
+        <v>-0.1007924098933017</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1334353538369655</v>
+        <v>-0.1348258808618468</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.09143816288086981</v>
+        <v>-0.09289385916834192</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.08976347181116751</v>
+        <v>-0.0912240432189293</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1856086304955511</v>
+        <v>-0.1869484693321652</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2437521307004502</v>
+        <v>-0.2450253667575453</v>
       </c>
     </row>
     <row r="7">
@@ -3266,243 +3266,243 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3331</v>
+        <v>3335</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1124021482146205</v>
+        <v>0.1113863588729771</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1809804431599034</v>
+        <v>0.1798720667704998</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.01042982315597385</v>
+        <v>0.009479804383893509</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.000451097555043134</v>
+        <v>-0.001410691134800857</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1101500349372628</v>
+        <v>-0.1117613347348083</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3241744603157457</v>
+        <v>-0.3255256508390261</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3335947377074788</v>
+        <v>-0.3349594494024331</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2964098650712614</v>
+        <v>-0.2978284857695996</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3274891656247831</v>
+        <v>-0.3288703328371128</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2173116282875966</v>
+        <v>-0.2188492445019676</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.314391558431609</v>
+        <v>-0.3158056833899394</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3369685952695178</v>
+        <v>-0.3383653215066147</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2772011656315598</v>
+        <v>-0.2787051127114424</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3013186289609635</v>
+        <v>-0.3028015806064914</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1640900176899009</v>
+        <v>-0.1657585327882813</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2398984736449705</v>
+        <v>-0.2414588602144647</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1465208701981311</v>
+        <v>-0.1481981880628354</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05386369214529196</v>
+        <v>-0.05565624719122297</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.08962173327031309</v>
+        <v>-0.09136582478087263</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.124625187406302</v>
+        <v>-0.1263225911516415</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1101620166764192</v>
+        <v>-0.111894704285902</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1081668657806816</v>
+        <v>-0.1099053737911078</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1755627711476322</v>
+        <v>-0.1772129741462294</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2336284521972445</v>
+        <v>-0.2352124171559069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02472</t>
+          <t>X &gt; -0.02471</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3316</v>
+        <v>3320</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1743362162917279</v>
+        <v>0.173092461799861</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2747054762495722</v>
+        <v>0.2733288111386258</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1698219142900896</v>
+        <v>0.1685180688190755</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1621493502872156</v>
+        <v>0.1608281694450824</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.02366365523257485</v>
+        <v>0.0215897858914289</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2221196249406319</v>
+        <v>-0.2238934057107969</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2580764331888474</v>
+        <v>-0.2598362376799628</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2194474996052023</v>
+        <v>-0.2212648485862445</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2208095885460395</v>
+        <v>-0.2226249480668159</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1666780350531027</v>
+        <v>-0.1685875739337277</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2353773567157873</v>
+        <v>-0.2371956718511541</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2868225524475534</v>
+        <v>-0.2885904070592176</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2217007417561803</v>
+        <v>-0.2235888265890935</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3050442752481075</v>
+        <v>-0.3068414949603095</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.1361776134783454</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1828924957208002</v>
+        <v>-0.1848412004661952</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1185642225653041</v>
+        <v>-0.1205963729804225</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.05510855999716568</v>
+        <v>-0.05722209852929439</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.06189323855930695</v>
+        <v>-0.06399200099986757</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.09789156626506212</v>
+        <v>-0.099941446318077</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.08090001731370933</v>
+        <v>-0.08299144330207042</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1086822880281488</v>
+        <v>-0.1107443064738831</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.2077734244774021</v>
+        <v>-0.2097073038856863</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2657679582954131</v>
+        <v>-0.2676359644184245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02284</t>
+          <t>X &gt; -0.02283</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3287</v>
+        <v>3291</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1325251199289639</v>
+        <v>0.1310297725064729</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1762576278067556</v>
+        <v>0.1746930215113025</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.05281640028294987</v>
+        <v>0.0513328845978549</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.02106173655599974</v>
+        <v>0.01958242173784441</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03576286878369217</v>
+        <v>0.03308082514282518</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2743300603119465</v>
+        <v>-0.2766300911236641</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3038346409708907</v>
+        <v>-0.3061365769560922</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2624347217420109</v>
+        <v>-0.2648012320588435</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2036170571053546</v>
+        <v>-0.2060542860294063</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1725002765615002</v>
+        <v>-0.1750129151892281</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2139130895320847</v>
+        <v>-0.216364290892237</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2633506233081775</v>
+        <v>-0.2657565687100742</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1574397738735343</v>
+        <v>-0.1600282833305613</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2698804726622157</v>
+        <v>-0.2723447140230491</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.09167416977408038</v>
+        <v>-0.09438692194298426</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1460701214491706</v>
+        <v>-0.1486906041316445</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.07998378532278139</v>
+        <v>-0.0826923359042766</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.01503303811495016</v>
+        <v>-0.01782696700153963</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.05414586123404064</v>
+        <v>-0.05688381792081287</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.0921072622303214</v>
+        <v>-0.09479197468672851</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.07017609288852356</v>
+        <v>-0.07291466795788892</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1279347288546049</v>
+        <v>-0.1306083824433273</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2303292032679209</v>
+        <v>-0.2328671142606211</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3185951391001609</v>
+        <v>-0.3210309481820985</v>
       </c>
     </row>
     <row r="10">
@@ -3512,243 +3512,243 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3257</v>
+        <v>3259</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1837620953165953</v>
+        <v>0.1842062239651696</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.275546019525585</v>
+        <v>0.2621809662669961</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1336749767145875</v>
+        <v>0.1215811928926271</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1997360035767315</v>
+        <v>0.1882291332283188</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1263961717581878</v>
+        <v>0.1442649731966057</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2492928162565633</v>
+        <v>-0.2485674369830946</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2414345735233496</v>
+        <v>-0.2402881435139506</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2276359262132459</v>
+        <v>-0.2263447541274601</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1380866458113204</v>
+        <v>-0.1368736880828791</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1301388973216717</v>
+        <v>-0.128503931633773</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2050167870578008</v>
+        <v>-0.2034881446192145</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2829344103433939</v>
+        <v>-0.2812043893687388</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1351347976741764</v>
+        <v>-0.1328739500287099</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2159593996328724</v>
+        <v>-0.2135270119241994</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.06066551336115111</v>
+        <v>-0.05796394059957066</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.09039153284096813</v>
+        <v>-0.08800122436485935</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.02244824833931602</v>
+        <v>-0.02002561922802926</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.0440825051314846</v>
+        <v>0.04652221860085604</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.002640447175394911</v>
+        <v>0.004985590036547194</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.0680389451088601</v>
+        <v>-0.06575439557629892</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.0408997955010264</v>
+        <v>-0.03833123085562562</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.09848194515605968</v>
+        <v>-0.09583621325316471</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2043403963781998</v>
+        <v>-0.2017822757601522</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2927118738407799</v>
+        <v>-0.2900576548623093</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01907</t>
+          <t>X &gt; -0.01906</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3226</v>
+        <v>3229</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1128244070570901</v>
+        <v>0.1437682711834185</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2086833751713826</v>
+        <v>0.2089914728336026</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2023731113610552</v>
+        <v>0.2034699970204059</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2142887847655146</v>
+        <v>0.1849793744242874</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1437422907992314</v>
+        <v>0.1437104837540346</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2989723185202848</v>
+        <v>-0.2852765177063361</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1911594732227329</v>
+        <v>-0.1773761120252075</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1437046793432302</v>
+        <v>-0.160712366073021</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.03889395648098315</v>
+        <v>0.02170110099250167</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.007352042393776514</v>
+        <v>-0.02432410470343171</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.007086657864689982</v>
+        <v>-0.009970605112521014</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09972269854913662</v>
+        <v>-0.1166209713367579</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.001467655704544768</v>
+        <v>-0.01819505094614726</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.08090469103056819</v>
+        <v>-0.09751206673615798</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.1131453107259048</v>
+        <v>0.09650906697647343</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.04656259448725564</v>
+        <v>0.02983963827337277</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1164854955881864</v>
+        <v>0.09972334697203422</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1537637345170566</v>
+        <v>0.1369856840947961</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.07893422975870834</v>
+        <v>0.06216755373110772</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.05611455108358854</v>
+        <v>-0.07280701026209613</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.007473174154732476</v>
+        <v>-0.009154876678209689</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.04991754642495039</v>
+        <v>-0.06648053201770665</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1594174843995333</v>
+        <v>-0.175950825970034</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3098907632793555</v>
+        <v>-0.3262724925688048</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01719</t>
+          <t>X &gt; -0.01718</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3190</v>
+        <v>3194</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1864016328544409</v>
+        <v>0.2172736084099753</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1625586213234271</v>
+        <v>0.1625217011615945</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1100184984212618</v>
+        <v>0.093513230848707</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.06773889734115812</v>
+        <v>0.05142978600654402</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03161542880044266</v>
+        <v>0.04446186226571314</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3558584632078805</v>
+        <v>-0.3601037075522271</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2381773431863081</v>
+        <v>-0.2426362227851087</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1870764725917766</v>
+        <v>-0.191625009055997</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.002906666485003484</v>
+        <v>-0.00768411683083059</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.02143142271928156</v>
+        <v>0.01655619531741337</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.06417847235591267</v>
+        <v>0.05926989612753175</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1031370253731225</v>
+        <v>-0.1078630943000576</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.008868548893246953</v>
+        <v>0.003905833089213218</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.06896865889211767</v>
+        <v>-0.07385570017675747</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.04090480666576468</v>
+        <v>0.03582244616834629</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.02939045187957845</v>
+        <v>0.02436923892264531</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.07032599773695836</v>
+        <v>0.06523937661203405</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1404813518357386</v>
+        <v>0.1352951895043688</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.09366825445781757</v>
+        <v>0.08855567014736465</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.01369755792109828</v>
+        <v>-0.01866321059764431</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.0880632928498386</v>
+        <v>0.08292169882418676</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.06223551280304207</v>
+        <v>0.05711678418805377</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.05156456641289964</v>
+        <v>-0.05652079549478373</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.1714971860162464</v>
+        <v>-0.1763126247227547</v>
       </c>
     </row>
     <row r="13">
@@ -3758,1145 +3758,1145 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3138</v>
+        <v>3142</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2036880276141915</v>
+        <v>0.2369623199330206</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2483795595035758</v>
+        <v>0.2820525681169173</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1874813995592746</v>
+        <v>0.2052237691650731</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.001878439201178139</v>
+        <v>-0.001240854899386079</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.03087487851826864</v>
+        <v>0.04283571908705142</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4296438887091085</v>
+        <v>-0.434965426249569</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2970213549479936</v>
+        <v>-0.3025947764348942</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2403978397793338</v>
+        <v>-0.2460755353551747</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.07305728577866688</v>
+        <v>0.06698309962036575</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1425807635741521</v>
+        <v>0.1363340091030665</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1814693058503067</v>
+        <v>0.1751981356970091</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.07919597074883455</v>
+        <v>-0.08516936214267901</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1806997785717144</v>
+        <v>0.1742753382247528</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.0735579537548432</v>
+        <v>0.06724252241156137</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.3235741961583045</v>
+        <v>0.3168684893124194</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2065381326140567</v>
+        <v>0.2000394545646955</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2504805796804419</v>
+        <v>0.2439081296660888</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2409170109133996</v>
+        <v>0.2534136356435539</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1897856666767339</v>
+        <v>0.2022871743702197</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.07757797581157888</v>
+        <v>0.09014883508670835</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1582083780125529</v>
+        <v>0.170820181896346</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.196927337907205</v>
+        <v>0.1903940678154967</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1085903931445316</v>
+        <v>0.1021944258008176</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.05171469144499241</v>
+        <v>0.04537930480616126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01342</t>
+          <t>X &gt; -0.01341</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3072</v>
+        <v>3076</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4009109357757197</v>
+        <v>0.4341852280945488</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1951015272116052</v>
+        <v>0.2287745358249467</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.275452809567895</v>
+        <v>0.3108072332363818</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.03208865949906681</v>
+        <v>-0.01404846796572912</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.106243724421283</v>
+        <v>0.1352839572877684</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2385973912196775</v>
+        <v>-0.2275558074557296</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1837101882741976</v>
+        <v>-0.1909663283447856</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.04208568509724842</v>
+        <v>0.03449624942631857</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2966394696054238</v>
+        <v>0.2887213205464505</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3518631966161649</v>
+        <v>0.3437670609987933</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3533549213156917</v>
+        <v>0.3452880946602122</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.02826803426868452</v>
+        <v>0.02058088050343088</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1556125194361968</v>
+        <v>0.1476074982005429</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.05090922166613154</v>
+        <v>0.04300592133768077</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.3528630890835629</v>
+        <v>0.3444764196440815</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.2205723796880577</v>
+        <v>0.2124308279027716</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.2033596674195763</v>
+        <v>0.1952178206454747</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.2608193962235745</v>
+        <v>0.2720709928149887</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2364612417536307</v>
+        <v>0.2476963106884398</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1828673602080642</v>
+        <v>0.1941199900102433</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2118808918150563</v>
+        <v>0.2232111961863907</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.3181412172071916</v>
+        <v>0.3098083796765678</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1569620383205788</v>
+        <v>0.1488700008777144</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.1330637792397624</v>
+        <v>0.1249878468213339</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01154</t>
+          <t>X &gt; -0.01153</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2993</v>
+        <v>2997</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4759449953116146</v>
+        <v>0.5092192876304438</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2403710742927885</v>
+        <v>0.2740440829061299</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2946945145891178</v>
+        <v>0.3300489382576046</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.002046758783684766</v>
+        <v>0.01550129331685923</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.09764526290099695</v>
+        <v>0.1445182576885884</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1614938763361948</v>
+        <v>-0.1333229931330351</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.08484874152636479</v>
+        <v>-0.07525839681089508</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2872046293314838</v>
+        <v>0.2964710789122051</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3811581806449595</v>
+        <v>0.371169818448962</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3916647388585375</v>
+        <v>0.3815283165094385</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2861625419911249</v>
+        <v>0.2762056184274257</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.04015624854505262</v>
+        <v>-0.04973156565031189</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1200975261016026</v>
+        <v>0.1101166661583903</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.01845222718382189</v>
+        <v>0.008563730624565835</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2457234776120529</v>
+        <v>0.2354169403067914</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.06091015169194947</v>
+        <v>0.05094217810596291</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.01337864493883245</v>
+        <v>0.003445500385168998</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.2084952621880021</v>
+        <v>0.2182607124890481</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2111383257938471</v>
+        <v>0.2208654274763475</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1511928595261978</v>
+        <v>0.1609490470633972</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.228662074313128</v>
+        <v>0.2384317776190983</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.3063453700839815</v>
+        <v>0.2959636088075257</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.1670592475997523</v>
+        <v>0.1569026552981754</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.177949328159464</v>
+        <v>0.1677592701736046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009652</t>
+          <t>X &gt; -0.009647</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2892</v>
+        <v>2896</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2434043674450805</v>
+        <v>0.2766786597639097</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.05740688603086141</v>
+        <v>-0.02373387741751998</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.01944411987644656</v>
+        <v>0.01591030379204028</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3704221861584287</v>
+        <v>-0.3534011039668528</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3231790801546381</v>
+        <v>-0.2768204424935092</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3917899549736532</v>
+        <v>-0.364768345743208</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3886158029152966</v>
+        <v>-0.380703283929094</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.02824231828973467</v>
+        <v>-0.02066561673075284</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.00140299188018389</v>
+        <v>-0.01355450906836353</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.06678475334163636</v>
+        <v>-0.07901814256553052</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.04800321573382149</v>
+        <v>-0.06021202921443347</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4105560187572621</v>
+        <v>-0.4223328235027353</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3776122787436691</v>
+        <v>-0.389680994721239</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.406253141650744</v>
+        <v>-0.4183372882742802</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1824424125896584</v>
+        <v>-0.1949829615676251</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.222319661972648</v>
+        <v>-0.2346866319988337</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3014196487738516</v>
+        <v>-0.3137140722035667</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.233810727968887</v>
+        <v>-0.2256961898059657</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2247983693173552</v>
+        <v>-0.1962543574774784</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3280386740331522</v>
+        <v>-0.2995064394790461</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2290812380135065</v>
+        <v>-0.2003521548457954</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1807484155735253</v>
+        <v>-0.1726427141147511</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2655261674982228</v>
+        <v>-0.2778711428132326</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2171750260852718</v>
+        <v>-0.2296109361284664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007769</t>
+          <t>X &gt; -0.007764</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2784</v>
+        <v>2787</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3287377793814414</v>
+        <v>0.3620120717002706</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04217754941585383</v>
+        <v>-0.008504540802512395</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3408525082993066</v>
+        <v>0.3762069319677934</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2457367112604061</v>
+        <v>-0.2295276450160557</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.03896502327765461</v>
+        <v>0.006518908884132202</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3323121787045551</v>
+        <v>-0.3068723031600129</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2110438329331146</v>
+        <v>-0.1853256332262063</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.02464854998243737</v>
+        <v>0.02157627358215564</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03739261990505582</v>
+        <v>0.06306345549685943</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.03570760040339138</v>
+        <v>0.06173116918459698</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.08026391141183353</v>
+        <v>0.08543315755539282</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.07063137435630296</v>
+        <v>-0.08602010855354081</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2427547177968563</v>
+        <v>-0.2582069770045834</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4071183004691861</v>
+        <v>-0.4224044451689224</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.2202022464414384</v>
+        <v>-0.2359421086109634</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1416723447212433</v>
+        <v>-0.1573760527915198</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2903346009427921</v>
+        <v>-0.3058713621384328</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1800327640779003</v>
+        <v>-0.1744046312841476</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.1791948541062567</v>
+        <v>-0.1522981014967186</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.3150789379260814</v>
+        <v>-0.2669801734052868</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2268866975837369</v>
+        <v>-0.17836784210823</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1018753928272744</v>
+        <v>-0.07480942605052121</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.257979939092003</v>
+        <v>-0.2309052194888181</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1329653155878177</v>
+        <v>-0.1273330952452767</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.005885</t>
+          <t>X &gt; -0.00588</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.494116994852746</v>
+        <v>0.5478321318510524</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.06738820670217649</v>
+        <v>-0.01335976083838375</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3412704389815886</v>
+        <v>0.3976777939042151</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3725228742115689</v>
+        <v>-0.3152762255385255</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3982981288697118</v>
+        <v>-0.3114440565763701</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.852400962109634</v>
+        <v>-0.7659873044412535</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.418175430640467</v>
+        <v>-0.3681246675768932</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3195139313080304</v>
+        <v>-0.231241772707321</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.428884324225784</v>
+        <v>-0.3406979870190341</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.426522785463888</v>
+        <v>-0.3588966819234471</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4323831811618604</v>
+        <v>-0.3867238322143578</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5387361882830106</v>
+        <v>-0.5145298394359372</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6592264115147373</v>
+        <v>-0.6565598308203562</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8206457186048937</v>
+        <v>-0.8177941236932256</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5122217315778173</v>
+        <v>-0.5097032269873907</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.4619340237997207</v>
+        <v>-0.4594967430252623</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.6493469930812594</v>
+        <v>-0.6466980069012038</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.5273156532173999</v>
+        <v>-0.5024056611572547</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.538207246244724</v>
+        <v>-0.4910505702672125</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.80519296254257</v>
+        <v>-0.7359105821458414</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7584729298155182</v>
+        <v>-0.6885363083868654</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7362985922437417</v>
+        <v>-0.6886820426952838</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.9537612144780141</v>
+        <v>-0.90625880636766</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.7801701222753792</v>
+        <v>-0.7549903782888876</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.004001</t>
+          <t>X &gt; -0.003997</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8454225681905712</v>
+        <v>0.8601712165069344</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.141218744499362</v>
+        <v>-0.1263367427390136</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6584944721962671</v>
+        <v>0.675970073810447</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1367320657525894</v>
+        <v>-0.1184503407443103</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4205686260209376</v>
+        <v>-0.3727744181795671</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.884869811059751</v>
+        <v>-0.8375393929783144</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2733711222668731</v>
+        <v>-0.1838261624083799</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5112091554075917</v>
+        <v>-0.4213044096054475</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.6325595398963557</v>
+        <v>-0.5427500179147842</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5278946488155398</v>
+        <v>-0.460268545275099</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3115644194572553</v>
+        <v>-0.2676752982251926</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5672018564395245</v>
+        <v>-0.5464247016731889</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7709907222460259</v>
+        <v>-0.7734564222971372</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8052880183372437</v>
+        <v>-0.8484833813454671</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5014968367049306</v>
+        <v>-0.5451275116970393</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.1270849483488732</v>
+        <v>-0.1711651589302505</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.4003077254635059</v>
+        <v>-0.4440873828882346</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.1784937559378719</v>
+        <v>-0.1982507288629662</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3708673250321937</v>
+        <v>-0.3663894810208674</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8782679738562038</v>
+        <v>-0.8498352666620903</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8495729580175606</v>
+        <v>-0.7963635015047288</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.9255280136601698</v>
+        <v>-0.8722094629138297</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.059249579204184</v>
+        <v>-1.006398420231534</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.053491572067422</v>
+        <v>-0.959631572514887</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002118</t>
+          <t>X &gt; -0.002114</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2232</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5911756018418757</v>
+        <v>0.6244498941607048</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.05663948403961427</v>
+        <v>-0.02296647542627284</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8261254382074483</v>
+        <v>0.8614798618759352</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1556446503318583</v>
+        <v>-0.1194509329129545</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2976004559007848</v>
+        <v>-0.2319274260051074</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9590289648234318</v>
+        <v>-0.8935543618371611</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.07937164890962123</v>
+        <v>-0.01297959775967428</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.2686007026461326</v>
+        <v>-0.2018654507307005</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3164102294055482</v>
+        <v>-0.2497038605980464</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1711060555669164</v>
+        <v>-0.1293636188140823</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1738627466120946</v>
+        <v>0.1893588192388691</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.07928118393234485</v>
+        <v>-0.08939058420912716</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2382018926005003</v>
+        <v>-0.2746339373537694</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3436161521777166</v>
+        <v>-0.3800245976340193</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.009155072961753774</v>
+        <v>-0.02832171014689067</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3355183021621784</v>
+        <v>0.324578522252942</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.1386444145322798</v>
+        <v>0.1279295174866348</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1232667332040194</v>
+        <v>0.1393518143924624</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1086387776992837</v>
+        <v>-0.06578331313601637</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.7280465949820822</v>
+        <v>-0.6850279644308657</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.8680211975284209</v>
+        <v>-0.7980845760997681</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.8543705184040036</v>
+        <v>-0.7843248027418426</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.624398219305391</v>
+        <v>-0.5546529576433059</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.4315223542727864</v>
+        <v>-0.3616680065655089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002342</t>
+          <t>X &gt; -0.0002304</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7517764192365632</v>
+        <v>0.7619868946651991</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3927061262626026</v>
+        <v>-0.3825065028748966</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4437694339304699</v>
+        <v>0.4568023833167842</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.573514015833247</v>
+        <v>-0.5597953608223065</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6858753537151543</v>
+        <v>-0.6425493961226252</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.257436082134767</v>
+        <v>-1.214692521766139</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4622698419075704</v>
+        <v>-0.4178152947253153</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1844259037134321</v>
+        <v>-0.139346577535072</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.09232814926237154</v>
+        <v>-0.04725210817098002</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3773882984869132</v>
+        <v>0.3944071145779589</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6813688437245276</v>
+        <v>0.6684667567398819</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7865361588765936</v>
+        <v>0.7439683654376381</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6042222879759862</v>
+        <v>0.5317374726705921</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3117995966859723</v>
+        <v>0.2396290261937679</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6471793765505325</v>
+        <v>0.5742139807004705</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7856184216057045</v>
+        <v>0.7431768265523999</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.7022603946307981</v>
+        <v>0.6905035403843769</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.9524266487536934</v>
+        <v>0.9714031296362862</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5597218055972277</v>
+        <v>0.6089594130682983</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1664764079147645</v>
+        <v>-0.1179003607200286</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3545271466945579</v>
+        <v>-0.3051165794474713</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.227539533641071</v>
+        <v>-0.1779168555773865</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.3079140373771025</v>
+        <v>-0.2587720923339134</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1301770407754574</v>
+        <v>-0.08079723895820479</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001649</t>
+          <t>X &gt; 0.001653</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.110567589464516</v>
+        <v>1.149572048244686</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.002119886902299584</v>
+        <v>-0.02352810339854017</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.89071553417903</v>
+        <v>0.873782188887823</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.06231222877489984</v>
+        <v>-0.0786927886387403</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6668164635597051</v>
+        <v>-0.6540042192698579</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.675824099356753</v>
+        <v>-1.664642823591635</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5348146333246575</v>
+        <v>-0.5204238428113328</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.09566592956092279</v>
+        <v>-0.0201921737919406</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1850845852224836</v>
+        <v>0.2608159662065859</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6672300356970666</v>
+        <v>0.7453853201102163</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6775509222191829</v>
+        <v>0.7200437646673521</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.09218625685692</v>
+        <v>1.099976995949888</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.021752292345944</v>
+        <v>0.9947790009500679</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.016388055736172</v>
+        <v>0.9533408430663428</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.256737392238435</v>
+        <v>1.230104244968793</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.252277058166776</v>
+        <v>1.261717898408548</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.178135402387156</v>
+        <v>1.224220326438939</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.612720331615613</v>
+        <v>1.696107014234272</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.9895149573771675</v>
+        <v>1.071662260704812</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4571342925659536</v>
+        <v>0.5382199554267402</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.3335981521531295</v>
+        <v>0.4158418546876064</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.5574032883570368</v>
+        <v>0.640115941297708</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.3525621478847327</v>
+        <v>0.4343985769490288</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5164289620934852</v>
+        <v>0.5986623621411198</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003533</t>
+          <t>X &gt; 0.003536</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.013378594249204</v>
+        <v>1.087373288652913</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8270126034144027</v>
+        <v>0.8270566541154594</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.396240710756835</v>
+        <v>1.473922191830567</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2848145071982273</v>
+        <v>-0.281474120985223</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1292509588889388</v>
+        <v>-0.09604344684597521</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9837530125488172</v>
+        <v>-0.9515195541216386</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4173334303171359</v>
+        <v>-0.3087251255771477</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6433976384500255</v>
+        <v>0.7533463782922638</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.9825327510917035</v>
+        <v>1.018214051644051</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.250364006988939</v>
+        <v>1.362200832792972</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.494473832555506</v>
+        <v>1.487340147330173</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.15378883411671</v>
+        <v>2.102112709630497</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.596250008965491</v>
+        <v>1.574631953273268</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.569557460510865</v>
+        <v>1.502473404451401</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.104656072219832</v>
+        <v>2.081966779000879</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.401208659154641</v>
+        <v>2.424411904277669</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.893980636647505</v>
+        <v>1.963550072430031</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.833773339955215</v>
+        <v>2.950245712282566</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.079747249155687</v>
+        <v>2.19526330679912</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.744402985074622</v>
+        <v>1.859330924086045</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.872844367121452</v>
+        <v>1.988928146710009</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.796889311478843</v>
+        <v>1.913082185300908</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.997037612289326</v>
+        <v>2.112874298828515</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.144976870035784</v>
+        <v>2.261089842468579</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005417</t>
+          <t>X &gt; 0.00542</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.4756913283316</v>
+        <v>1.612436188631825</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.983212442900758</v>
+        <v>2.028128433433984</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.198942690425106</v>
+        <v>1.246769797160958</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.200243881195021</v>
+        <v>-1.154739569373717</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3482852017995839</v>
+        <v>-0.2710178467990403</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.097450176807783</v>
+        <v>-1.022137964641615</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8403537620453321</v>
+        <v>-0.7621917141980106</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2762117783504152</v>
+        <v>-0.1961254854051191</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2346957133277812</v>
+        <v>-0.1546383034904153</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2919582155950451</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6314477352101733</v>
+        <v>0.6598264881509692</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.532918301210984</v>
+        <v>1.506780649430929</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9339315793722847</v>
+        <v>0.8526617345447889</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.9571121681755486</v>
+        <v>0.8192001188861866</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.332015515604411</v>
+        <v>1.250470098970375</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.551135715601724</v>
+        <v>1.526543631806788</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.417042021452801</v>
+        <v>1.450007718349077</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.157923267011661</v>
+        <v>2.250113927734134</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.340211843477313</v>
+        <v>1.430223764402342</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.8693609022556359</v>
+        <v>0.9579358643891922</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.641949966941894</v>
+        <v>1.733657116385501</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.847949798517334</v>
+        <v>1.940297030682615</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.028740002593437</v>
+        <v>2.120609784595928</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.046783625730995</v>
+        <v>2.138939489941393</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0073</t>
+          <t>X &gt; 0.007303</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>849</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.894460071388714</v>
+        <v>1.927734363707543</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.200550676322344</v>
+        <v>3.234223684935685</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.112550095002916</v>
+        <v>2.147904518671403</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4769759262793372</v>
+        <v>-0.4407822088604334</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3733125342811121</v>
+        <v>-0.3076395043854347</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7723143925521683</v>
+        <v>-0.7068397895658975</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3728475820505039</v>
+        <v>-0.306455530900557</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1824690505467998</v>
+        <v>-0.1157337986313678</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.09351360298697386</v>
+        <v>0.1602199717944757</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3747778405176589</v>
+        <v>0.4424039440580998</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.30465285156906</v>
+        <v>1.302630057497865</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.56510645641081</v>
+        <v>1.492813831072148</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.040255799201049</v>
+        <v>1.893684589538417</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.597808431802811</v>
+        <v>2.376005478625245</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.174448453071754</v>
+        <v>2.025117986294312</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.827223461468165</v>
+        <v>1.752394687177301</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.928701027625486</v>
+        <v>1.925797658031435</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.001573913061421</v>
+        <v>3.071286061118045</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.275412034768259</v>
+        <v>2.344892400817393</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.402385159010599</v>
+        <v>1.471667539407328</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.037041051543859</v>
+        <v>2.106977672972512</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.078871626054372</v>
+        <v>2.148917341716533</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.118075532230257</v>
+        <v>2.187820793892342</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.748847973880522</v>
+        <v>2.8187023215878</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.009184</t>
+          <t>X &gt; 0.009186</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>663</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.716856037858228</v>
+        <v>2.750130330177058</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.186191801409386</v>
+        <v>4.219864810022727</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.896867277172873</v>
+        <v>2.93222170084136</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.431194264731602</v>
+        <v>1.467387982150505</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.268931998504542</v>
+        <v>2.334605028400219</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9523372130150847</v>
+        <v>1.017811816001355</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.382478599758052</v>
+        <v>1.448870650907999</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9535480143898667</v>
+        <v>1.020283266305299</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.446191898961374</v>
+        <v>1.512898267768875</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.123484307740824</v>
+        <v>1.191110411281265</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.848971394405027</v>
+        <v>1.916297872992054</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.262195635689608</v>
+        <v>2.239052228942548</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.133770128009502</v>
+        <v>2.018145801184183</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.515731567352219</v>
+        <v>2.398570684136082</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.856800328314918</v>
+        <v>1.740427386555524</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.150201252747763</v>
+        <v>2.126688572471707</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.921084934164448</v>
+        <v>2.990654369946974</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.117760643257704</v>
+        <v>3.187472791314327</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.976417742841107</v>
+        <v>2.045898108890242</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.710972850678736</v>
+        <v>1.780255231075465</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.374408942434926</v>
+        <v>2.444345563863578</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.298453886792316</v>
+        <v>2.368499602454477</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.573229053274446</v>
+        <v>2.642974314936531</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.798946839194514</v>
+        <v>2.868801186901791</v>
       </c>
     </row>
     <row r="27">
@@ -4909,76 +4909,76 @@
         <v>500</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.294006084289052</v>
+        <v>4.327280376607881</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.154049693150696</v>
+        <v>5.187722701764038</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.913552416315554</v>
+        <v>3.948906839984041</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.004539979616425</v>
+        <v>2.040733697035328</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.03369250534935</v>
+        <v>3.099365535245028</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.025637994850157</v>
+        <v>2.091112597836428</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.647194173553103</v>
+        <v>2.71358622470305</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9742172172775696</v>
+        <v>1.040952469193002</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.214936469551198</v>
+        <v>1.2816428383587</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.237913807785752</v>
+        <v>1.305539911326193</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.1138667003991</v>
+        <v>1.181193178986128</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.551268093184262</v>
+        <v>1.500053337291121</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.9461381521422254</v>
+        <v>0.775297644936991</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.924781341107874</v>
+        <v>1.749437891996379</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.06585010207057</v>
+        <v>0.8920914071648198</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.6609101516919509</v>
+        <v>0.6101433496643054</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.526816457543028</v>
+        <v>1.596385893325554</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.421833041447755</v>
+        <v>2.491545189504379</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.637956204379563</v>
+        <v>1.707436570428698</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.8249999999999957</v>
+        <v>0.8942823803967244</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.281799591002041</v>
+        <v>1.351736212430694</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.405844535359435</v>
+        <v>1.475890251021596</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.680619701841565</v>
+        <v>1.75036496350365</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.8046783625731</v>
+        <v>1.874532710280377</v>
       </c>
     </row>
     <row r="28">
@@ -4991,158 +4991,158 @@
         <v>386</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.465413477970138</v>
+        <v>4.498687770288967</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.647033828958882</v>
+        <v>4.680706837572224</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.499323028955438</v>
+        <v>4.534677452623924</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.235142118863052</v>
+        <v>2.271335836281956</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.420259930738233</v>
+        <v>3.48593296063391</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.090628678111941</v>
+        <v>3.156103281098211</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.868150142957141</v>
+        <v>3.934542194107088</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.556003766172431</v>
+        <v>2.622739018087863</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.339121898378515</v>
+        <v>2.405828267186017</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.082082353242171</v>
+        <v>2.149708456782612</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.098043687540972</v>
+        <v>2.165370166128</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.197054241095692</v>
+        <v>1.11142696423039</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5906977376344571</v>
+        <v>0.5050607630073358</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.664677714164867</v>
+        <v>1.575971550643445</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.26481383264052</v>
+        <v>1.176226185879415</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.082671809723045</v>
+        <v>1.152064688334121</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.243914903138887</v>
+        <v>2.313484338921413</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.952402989634287</v>
+        <v>4.022115137690911</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.391324080027239</v>
+        <v>3.460804446076374</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.801165803108809</v>
+        <v>2.870448183505538</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.257965394110855</v>
+        <v>2.327902015539507</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.4410776959812</v>
+        <v>2.511123411643361</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.974920219976283</v>
+        <v>3.044665481638368</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.639911523194861</v>
+        <v>2.709765870902139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01483</t>
+          <t>X &gt; 0.01484</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>282</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.276408629584893</v>
+        <v>4.309682921903722</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.061374457696758</v>
+        <v>6.095047466310099</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.975030884069973</v>
+        <v>5.01038530773846</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.847810009039364</v>
+        <v>2.884003726458268</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.249324676312135</v>
+        <v>4.314997706207812</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.376418617940836</v>
+        <v>3.441893220927106</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.077050719102353</v>
+        <v>5.1434427702523</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.738425402205699</v>
+        <v>3.805160654121131</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.1332983576877</v>
+        <v>4.200004726495202</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.772890508755729</v>
+        <v>4.84051661229617</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.693892885411699</v>
+        <v>4.761219363998727</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.508927242969804</v>
+        <v>2.362328617794539</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.739045953560669</v>
+        <v>1.592523441397788</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.290738787916382</v>
+        <v>3.138229017248023</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.631807548879081</v>
+        <v>2.480085719667464</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.16303781126642</v>
+        <v>2.232430689877496</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.447383833429562</v>
+        <v>3.516953269212088</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.824669920880382</v>
+        <v>5.894382068937006</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.622353367500132</v>
+        <v>4.691833733549267</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.390957446808507</v>
+        <v>3.460239827205235</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.847757037810553</v>
+        <v>2.917693659239205</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.771801982167943</v>
+        <v>2.841847697830104</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.401187077728096</v>
+        <v>3.470932339390181</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.325245738459628</v>
+        <v>3.395100086166906</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>229</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.151206105166231</v>
+        <v>6.184480397485061</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.999436704059029</v>
+        <v>8.033109712672371</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.249692571850616</v>
+        <v>5.285046995519103</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.225855590535197</v>
+        <v>3.262049307954101</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.04399191904826</v>
+        <v>5.109664948943937</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.484431641225349</v>
+        <v>3.54990624421162</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.205015290830715</v>
+        <v>6.271407341980662</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.179735754482458</v>
+        <v>4.24647100639789</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.531295487627368</v>
+        <v>5.59800185643487</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.504184967687628</v>
+        <v>6.571811071228069</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.215225457510385</v>
+        <v>7.282551936097413</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.316044217790946</v>
+        <v>4.383715196404879</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.62823422201123</v>
+        <v>3.697234352256189</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.716921079099144</v>
+        <v>4.786199143931867</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.057989840061843</v>
+        <v>4.128055846351309</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>2.906324998853528</v>
+        <v>2.975717877464604</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.518956195534301</v>
+        <v>4.588525631316827</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.47074133839098</v>
+        <v>7.540453486447603</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>5.503458387785678</v>
+        <v>5.572938753834812</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.633733624454152</v>
+        <v>2.70301600485088</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.65385199274877</v>
+        <v>1.723788614177423</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.014578159813588</v>
+        <v>2.084623875475749</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>3.162715771710566</v>
+        <v>3.232461033372651</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.776730764319822</v>
+        <v>1.8465851120271</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>178</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.247226908855943</v>
+        <v>9.280501201174772</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.22665813578466</v>
+        <v>7.260331144398002</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.786957671698524</v>
+        <v>5.82231209536701</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.511366605696374</v>
+        <v>4.547560323115277</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.393287831908275</v>
+        <v>6.458960861803952</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.895059186488105</v>
+        <v>4.960533789474376</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.054777324096996</v>
+        <v>8.121169375246943</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.090829420151465</v>
+        <v>6.157564672066897</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.694143237983084</v>
+        <v>6.760849606790586</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.04390333283164</v>
+        <v>7.111529436372081</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.565453611182932</v>
+        <v>9.632780089769959</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.791977685236112</v>
+        <v>4.859648663850045</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.791081972366946</v>
+        <v>4.860082102611905</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.378713925377532</v>
+        <v>7.447991990210255</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6.157984933531246</v>
+        <v>6.228050939820712</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.944056219107686</v>
+        <v>4.013449097718762</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.057153536194718</v>
+        <v>6.126722971977244</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.637563378526409</v>
+        <v>7.707275526583032</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.168293283031254</v>
+        <v>6.237773649080388</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.422752808988761</v>
+        <v>2.49203518938549</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.879552399990807</v>
+        <v>1.94948902141946</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.365395097157183</v>
+        <v>2.435440812819344</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.763765769257297</v>
+        <v>3.833511030919382</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.440633418752881</v>
+        <v>1.510487766460159</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>143</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.067137335507944</v>
+        <v>5.100411627826773</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.731961820863617</v>
+        <v>4.765634829476959</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.29226135677748</v>
+        <v>3.327615780445967</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.879167344283623</v>
+        <v>1.915361061702527</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.311100356462383</v>
+        <v>4.37677338635806</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.099663570867762</v>
+        <v>3.165138173854032</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.522601634617928</v>
+        <v>6.588993685767875</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.943347688400067</v>
+        <v>7.010082940315499</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.285563054122001</v>
+        <v>6.352269422929503</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.008231139856072</v>
+        <v>9.075857243396513</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.68119180557281</v>
+        <v>10.74851828415984</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.206293706293707</v>
+        <v>6.273964684907639</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.081802487806563</v>
+        <v>5.150802618051522</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.259047075373608</v>
+        <v>6.328325140206331</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.600115836336307</v>
+        <v>5.670181842625773</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.796574487356288</v>
+        <v>4.865967365967364</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.061082191808765</v>
+        <v>6.130651627591291</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.655399475014192</v>
+        <v>6.725111623070816</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.0743198407432</v>
+        <v>4.143800206792335</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.06555944055943996</v>
+        <v>0.1348418209561686</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4776409684385143</v>
+        <v>-0.4077043470098616</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.1457046752195694</v>
+        <v>0.2157503908817304</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.819081240303106</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.344538502433231</v>
+        <v>0.4143928501405085</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>115</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.978052507292681</v>
+        <v>2.01132679961151</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.382007427430963</v>
+        <v>3.415680436044305</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.228513650151669</v>
+        <v>1.264707367570573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.919973695525712</v>
+        <v>1.985448298511983</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.494933650428216</v>
+        <v>5.561325701578163</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.95550943969225</v>
+        <v>7.022244691607682</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.127460287323586</v>
+        <v>6.194166656131088</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.831885746119376</v>
+        <v>8.899511849659817</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.97581023062601</v>
+        <v>10.04313670921304</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.957585892368499</v>
+        <v>8.025256870982432</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.833094673881355</v>
+        <v>6.902094804126314</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.611737862847001</v>
+        <v>6.681015927679724</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.9528066238097</v>
+        <v>6.022872630099165</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>3.939171021257174</v>
+        <v>4.00856389986825</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.54420776189086</v>
+        <v>5.613777197673386</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.308789563186878</v>
+        <v>6.378501711243501</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.046651856553488</v>
+        <v>3.116132222602623</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.625</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.787765626389259</v>
+        <v>-0.7178290049606062</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.744974970142046</v>
+        <v>1.815020685804207</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.889315354015487</v>
+        <v>2.959060615677572</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.235097015506895</v>
+        <v>-1.201822723188066</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8687518600926865</v>
+        <v>0.9024248687060279</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.5709486039934504</v>
+        <v>-0.5355941803249635</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.284741917186608</v>
+        <v>-1.248548199767704</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.447549273399098</v>
+        <v>4.513222303294775</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.195689496161975</v>
+        <v>2.261164099148246</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.300872144595758</v>
+        <v>6.367264195745705</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.680854084443055</v>
+        <v>9.747589336358487</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.722370149465689</v>
+        <v>9.789076518273191</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.82658351918406</v>
+        <v>13.8942096227245</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.1009427862994</v>
+        <v>14.16826926488643</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.60233668770255</v>
+        <v>12.67000766631648</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.4778454692154</v>
+        <v>11.54684559946036</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.25648865818105</v>
+        <v>11.32576672301377</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.378045224021783</v>
+        <v>9.448111230311248</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>8.753593078521227</v>
+        <v>8.822985957132303</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.83901157949424</v>
+        <v>9.908581015276766</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.73402816339896</v>
+        <v>9.803740311455584</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.291614740964938</v>
+        <v>6.361095107014073</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.820121951219512</v>
+        <v>2.889404331616241</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-1.381615043144301</v>
+        <v>-1.311678421715648</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>2.200966486578949</v>
+        <v>2.27101220224111</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>3.695253848183029</v>
+        <v>3.764999109845114</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.39980031379261</v>
+        <v>2.469654661499888</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.500208362272538</v>
+        <v>-1.466934069953709</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.284659239235701</v>
+        <v>-3.25098623062236</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.539602291877308</v>
+        <v>-2.503408574458405</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.790780097011677</v>
+        <v>5.856453126907354</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.079393985380783</v>
+        <v>3.144868588367054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.654353940283272</v>
+        <v>6.720745991433219</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.72362538172125</v>
+        <v>10.79036063363668</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.76514144674388</v>
+        <v>10.83184781555138</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.33913212293097</v>
+        <v>14.40675822647141</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.61349139004631</v>
+        <v>14.68081786863333</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.3343974865714</v>
+        <v>14.40206846518534</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>13.20990626808426</v>
+        <v>13.27890639832922</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.53927409473106</v>
+        <v>11.60855215956379</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>10.88034285569376</v>
+        <v>10.95040886198323</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>10.0261275429963</v>
+        <v>10.09552042160738</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.892033848847376</v>
+        <v>9.961603284629902</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.787050432752096</v>
+        <v>9.85676258080872</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>5.655347508727395</v>
+        <v>5.72482787477653</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-1.947185916244329</v>
+        <v>-1.877249294815677</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>1.150184919232878</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>1.07424357996441</v>
+        <v>1.144097927671687</v>
       </c>
     </row>
   </sheetData>
@@ -5824,83 +5824,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02849</t>
+          <t>X &lt; -0.02848</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.539602291877308</v>
+        <v>-2.503408574458405</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.892229372373997</v>
+        <v>2.957902402269674</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.77504615929384</v>
+        <v>11.84052076228011</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.00218002723981</v>
+        <v>11.06857207838976</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.274350019402391</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.76514144674388</v>
+        <v>10.83184781555138</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.986571399614888</v>
+        <v>10.05424237822882</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.862080181127745</v>
+        <v>8.931080311372703</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>3.633966044099552</v>
+        <v>3.704032050389017</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.645657037253173</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.807152465798623</v>
+        <v>-1.737440317741999</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.307521421770879</v>
+        <v>1.377001787820014</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.9513648083933575</v>
+        <v>1.02130142982201</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.498011006189394</v>
+        <v>5.567756267851479</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.320620391558613</v>
+        <v>8.39047473926589</v>
       </c>
     </row>
     <row r="7">
@@ -5913,240 +5913,240 @@
         <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.481350321413444</v>
+        <v>-5.448076029094615</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.22616439027464</v>
+        <v>-8.192491381661299</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.43694919171017</v>
+        <v>-2.401594768041683</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.150742504903327</v>
+        <v>-3.114548787484424</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.303264818506349</v>
+        <v>1.368937848402027</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.924164371272184</v>
+        <v>9.989638974258455</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.35611751632658</v>
+        <v>10.42250956747653</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.872743593699596</v>
+        <v>8.939478845615028</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.11907893583066</v>
+        <v>10.18578530463816</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.730785693735918</v>
+        <v>5.798411797276358</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.619602792176565</v>
+        <v>9.686929270763592</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.54532816581009</v>
+        <v>10.61299914442402</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.216017670214519</v>
+        <v>8.285017800459478</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.199480136288592</v>
+        <v>9.268758201121315</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.721271788817553</v>
+        <v>3.791337795107019</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>6.725970392655817</v>
+        <v>6.795363271266893</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>2.977418867181591</v>
+        <v>3.046988302964117</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.7420223802389927</v>
+        <v>-0.6723102321823688</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.678920059801257</v>
+        <v>0.7484004258503916</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.070783132530117</v>
+        <v>2.140065512926846</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.527582723532163</v>
+        <v>1.597519344960816</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.451627667889554</v>
+        <v>1.521673383551715</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>4.136041388588545</v>
+        <v>4.20578665025063</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.46973860353696</v>
+        <v>6.539592951244238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02472</t>
+          <t>X &lt; -0.02471</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>98</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.735345895546715</v>
+        <v>-6.702071603227886</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.13174589998696</v>
+        <v>-10.09807289137362</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-7.489813711011877</v>
+        <v>-7.45445928734339</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.203607024205034</v>
+        <v>-8.167413306786131</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.466835992902546</v>
+        <v>-3.401162963006868</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.883593926226688</v>
+        <v>4.949068529212958</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.151544120703278</v>
+        <v>6.217936171853225</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.852581311919408</v>
+        <v>4.91931656383484</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.894097376942042</v>
+        <v>4.960803745749544</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.099853802907305</v>
+        <v>3.167479906447745</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.415029396553258</v>
+        <v>5.482355875140286</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.176751819608967</v>
+        <v>7.244422798222899</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.031852437856521</v>
+        <v>5.10085256810148</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.871720116618071</v>
+        <v>7.940998181450794</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2.110748061254249</v>
+        <v>2.180814067543714</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>3.726216274140938</v>
+        <v>3.795609152752014</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.551306253461398</v>
+        <v>1.620875689243924</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.594493489164492</v>
+        <v>-0.5247813411078681</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3783703262326767</v>
+        <v>-0.3088899601835422</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.8290816326530646</v>
+        <v>0.8983640130497932</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.2858812236551103</v>
+        <v>0.355817845083763</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.230334331277803</v>
+        <v>1.300380046939964</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.566333987555858</v>
+        <v>4.636079249217943</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.531208974817993</v>
+        <v>6.60106332252527</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02284</t>
+          <t>X &lt; -0.02283</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>127</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.067822193152367</v>
+        <v>-4.034547900833537</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.190399282599849</v>
+        <v>-5.156726273986507</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.693091872670237</v>
+        <v>-2.65773744900175</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.61948361106024</v>
+        <v>-2.583289893641336</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.984753396084287</v>
+        <v>-2.919080366188609</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.076426964953995</v>
+        <v>5.141901567940266</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.878363982506265</v>
+        <v>5.944756033656212</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.812407762184556</v>
+        <v>4.879143014099988</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.279120677600893</v>
+        <v>3.345827046408395</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.505285266831464</v>
+        <v>2.572911370371905</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.567046108749949</v>
+        <v>3.634372587336976</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.862755354881344</v>
+        <v>4.930426333495276</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.163460986787904</v>
+        <v>2.232461117032862</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.091710474966142</v>
+        <v>5.160988539798865</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.4957713619130999</v>
+        <v>0.5658373682025655</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.878232986337629</v>
+        <v>1.947625864948705</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1693361425824094</v>
+        <v>0.2389055783649354</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.510450423119181</v>
+        <v>-1.440738275062557</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.5069256853842177</v>
+        <v>-0.4374453193350831</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.4675196850393775</v>
+        <v>0.5368020654361061</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.07568072395857683</v>
+        <v>-0.005744102529924078</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.42316737000511</v>
+        <v>1.493213085667271</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.060147260896684</v>
+        <v>4.129892522558769</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>6.346410646037675</v>
+        <v>6.416264993744953</v>
       </c>
     </row>
     <row r="10">
@@ -6156,243 +6156,243 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.307032798155859</v>
+        <v>-4.265847113431967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.238596283452445</v>
+        <v>-5.850623911781781</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.85664069658317</v>
+        <v>-3.538642960812766</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.844319360094801</v>
+        <v>-5.501596980255513</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.298761119641142</v>
+        <v>-4.58738745280278</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.531715595276474</v>
+        <v>3.473006406250562</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.39579213838168</v>
+        <v>3.32998853997028</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.117237492863119</v>
+        <v>3.051777095217204</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.247925532408047</v>
+        <v>1.206471824301715</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.111032796797851</v>
+        <v>1.062486965875287</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.65927741423166</v>
+        <v>2.594408243257341</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.291011536234464</v>
+        <v>4.20245129263953</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.255692292269615</v>
+        <v>1.192496772953227</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.945163506712966</v>
+        <v>2.858210349336822</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.2615384329612738</v>
+        <v>-0.3156562186839906</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3335216166601072</v>
+        <v>0.2787307032590007</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.074457427807289</v>
+        <v>-1.113048068938596</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.453326194221042</v>
+        <v>-2.475750407979902</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.600260356129986</v>
+        <v>-1.630928209445514</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.139331210191088</v>
+        <v>-0.1862207642573637</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.6825316191890423</v>
+        <v>-0.7287669322233938</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.5153986754868214</v>
+        <v>0.4532487415876361</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.701001867446656</v>
+        <v>2.614515906899875</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.535888553655901</v>
+        <v>4.425476106506785</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01907</t>
+          <t>X &lt; -0.01906</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.351370082999473</v>
+        <v>-2.855506799295839</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.385167597247218</v>
+        <v>-4.361011381865403</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.098960910440375</v>
+        <v>-4.547649611834458</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.86848601461336</v>
+        <v>-3.830808505434369</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.765487109031724</v>
+        <v>3.512938521654384</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.928791189743663</v>
+        <v>1.682788779562976</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.118321650608074</v>
+        <v>1.4045773348099</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.031651646071417</v>
+        <v>-1.728538657878573</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.209742375989784</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.467298002491475</v>
+        <v>-1.169193633552084</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3812676685017138</v>
+        <v>0.6684590794020409</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.275138443602451</v>
+        <v>-0.983803516554616</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.09924942621425714</v>
+        <v>0.3824191943003896</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-3.219256280908148</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-2.092281337669739</v>
+        <v>-1.797739297739298</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.290204819052718</v>
+        <v>-2.989857492917828</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.927103128765019</v>
+        <v>-3.623798725839542</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.647150178599155</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3324468085106318</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.407562111125614</v>
+        <v>-1.118105057410567</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.4196873795341816</v>
+        <v>-0.135749960618611</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.45083246779901</v>
+        <v>1.726026339165024</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.034465596615654</v>
+        <v>4.295696731444401</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01719</t>
+          <t>X &lt; -0.01718</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>224</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.007454739084125</v>
+        <v>-3.420582796251345</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.670011206109415</v>
+        <v>-2.648190283463194</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.32399738448126</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.144933554817278</v>
+        <v>-1.904374758033285</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.617346196984172</v>
+        <v>-1.795720786136123</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.92696127316546</v>
+        <v>3.992435876151731</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.261237998254295</v>
+        <v>2.327630049404242</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.536254781307164</v>
+        <v>1.602990033222596</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.100800582241632</v>
+        <v>-1.03409421343413</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.428207421582492</v>
+        <v>-1.360581318042051</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.046705297324294</v>
+        <v>-1.979378818737267</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3527722277722347</v>
+        <v>0.4204432063861674</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.218147562143479</v>
+        <v>-1.14914743189852</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1002186588921248</v>
+        <v>-0.03094059405940186</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.652007040786565</v>
+        <v>-1.581941034497099</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.503375562593753</v>
+        <v>-1.433982683982677</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.08389782817126</v>
+        <v>-2.014328392388734</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.081738387123679</v>
+        <v>-3.012026239067055</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-2.419186652763294</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.8928571428571388</v>
+        <v>-0.8235747624604102</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.328914694712246</v>
+        <v>-2.258978073283593</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.958441178926272</v>
+        <v>-1.888395463264111</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.3443802981584341</v>
+        <v>-0.274635036496349</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.36539264828739</v>
+        <v>1.435246995994667</v>
       </c>
     </row>
     <row r="13">
@@ -6405,1142 +6405,1142 @@
         <v>276</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.594984715103308</v>
+        <v>-2.931627255275934</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.10676984458285</v>
+        <v>-3.441816082600283</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.741416157044434</v>
+        <v>-2.913642960812773</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9281336579632296</v>
+        <v>-0.9294643637680622</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.293403442987277</v>
+        <v>-1.426416229781204</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.947912794568254</v>
+        <v>4.013387397554524</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.453025001864404</v>
+        <v>2.519417053014351</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.813459526020928</v>
+        <v>1.88019477793636</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.75513271220553</v>
+        <v>-1.688426343398028</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.528968122974959</v>
+        <v>-2.461342019434518</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.976630516509438</v>
+        <v>-2.909304037922411</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.00662694706015543</v>
+        <v>0.06104403155377724</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.936172317171845</v>
+        <v>-2.867172186926886</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.713485806906569</v>
+        <v>-1.644207742073846</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.538482027893323</v>
+        <v>-4.468416021603858</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.22140031762212</v>
+        <v>-3.152007439011044</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.716504842095958</v>
+        <v>-3.646935406313432</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.61874666869717</v>
+        <v>-3.751776110134614</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-3.174873898885373</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.766304347826086</v>
+        <v>-1.904995597942616</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.671823597403751</v>
+        <v>-2.808552596233561</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-3.110097493626071</v>
+        <v>-3.04005177796391</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.11068464598452</v>
+        <v>-2.040939384322435</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.461988304093566</v>
+        <v>-1.392133956386289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01342</t>
+          <t>X &lt; -0.01341</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>342</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.819048941982679</v>
+        <v>-4.070646540366063</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.974413199464884</v>
+        <v>-2.251485980747297</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.970863273694093</v>
+        <v>-3.252259675510174</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4776595023391366</v>
+        <v>-0.6352675004867336</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.717564855876311</v>
+        <v>-1.969633829614381</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.385051652174219</v>
+        <v>1.282718268178314</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9037307096245613</v>
+        <v>0.9701227607745082</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.124095072920241</v>
+        <v>-1.057359821004809</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.414940523932593</v>
+        <v>-3.348234155125091</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.897230745197653</v>
+        <v>-3.829604641657212</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.914416667586686</v>
+        <v>-3.847090188999658</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.166180758017489</v>
+        <v>-1.096902693184767</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-3.865928323585401</v>
+        <v>-3.795862317295935</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.687777894955275</v>
+        <v>-2.618385016344199</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.530326399599829</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.053020759721839</v>
+        <v>-3.14868804664723</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.836897596790024</v>
+        <v>-2.932796665722904</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.357456140350877</v>
+        <v>-2.454405666250501</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.608258888530123</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-3.561406926628862</v>
+        <v>-3.491361210966701</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.117041116871881</v>
+        <v>-2.047295855209796</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.900584795321635</v>
+        <v>-1.830730447614357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01154</t>
+          <t>X &lt; -0.01153</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>421</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.55647434692726</v>
+        <v>-3.757397229982082</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.886655410961161</v>
+        <v>-2.106465033277111</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.493914642164476</v>
+        <v>-2.720434529899421</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-0.7275359473916652</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.314790340518371</v>
+        <v>-1.638858041038084</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5311420450002657</v>
+        <v>0.3283523182002526</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.004757262409214036</v>
+        <v>-0.07337467872814329</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.652980154373267</v>
+        <v>-2.715652317334651</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.322364563284282</v>
+        <v>-3.25565819447678</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.385299500120063</v>
+        <v>-3.317673396579622</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.637006583715632</v>
+        <v>-2.569680105128604</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3094654161004868</v>
+        <v>-0.2417944374865542</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.433956634587631</v>
+        <v>-1.364956504342672</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.7074461470437896</v>
+        <v>-0.6381680822110667</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.314244684659286</v>
+        <v>-2.244178678369821</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.008284161104257</v>
+        <v>-0.9388912824931808</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.6684442059640716</v>
+        <v>-0.5988747701815456</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.058451994181695</v>
+        <v>-2.125516421870032</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.079858522461286</v>
+        <v>-2.146591865590253</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.655285035629447</v>
+        <v>-1.722779230977679</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.198485444627401</v>
+        <v>-2.265325398943709</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.749499882692817</v>
+        <v>-2.679454167030656</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.762135642576482</v>
+        <v>-1.692390380914397</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.838076981844949</v>
+        <v>-1.768222634137672</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009652</t>
+          <t>X &lt; -0.009647</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>522</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.491958217895004</v>
+        <v>-1.663445983488465</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1732125853082991</v>
+        <v>-0.01335976083838375</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2109021463860188</v>
+        <v>-0.4041911649715573</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.551495016611298</v>
+        <v>1.449160595502065</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.296366998217565</v>
+        <v>1.032868714180132</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.67437130588084</v>
+        <v>1.519255539378236</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.66486395245277</v>
+        <v>1.619296716070906</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3312479449741943</v>
+        <v>-0.3732004429678781</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4805715746080423</v>
+        <v>-0.4138652058005405</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1093688174385434</v>
+        <v>-0.04174271389810258</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2166889396361782</v>
+        <v>-0.1493624610491509</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.794293492766784</v>
+        <v>1.861964471380716</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.624000747562079</v>
+        <v>1.693000877807037</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.784323325840695</v>
+        <v>1.853601390673418</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5528730028339268</v>
+        <v>0.6229390091233924</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.7662536631423364</v>
+        <v>0.8356465417534125</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.204679052962881</v>
+        <v>1.274248488745407</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.8336877259601749</v>
+        <v>0.7877283956112464</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.7827837905864641</v>
+        <v>0.621940387222601</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.352969348659002</v>
+        <v>1.190465586503599</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.8097689396610477</v>
+        <v>0.647919418537569</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.5422430027923895</v>
+        <v>0.4965403466238882</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.008589050500568</v>
+        <v>1.078334312162653</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.7410768300060511</v>
+        <v>0.8109311777133286</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007769</t>
+          <t>X &lt; -0.007764</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.561445349412772</v>
+        <v>-1.696834671752335</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.06593818932274331</v>
+        <v>-0.08154291489704946</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.759829409599</v>
+        <v>-1.903502555196546</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6660947026395476</v>
+        <v>0.5921530197444795</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2387523065978385</v>
+        <v>-0.4373483291721172</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.049041237226561</v>
+        <v>0.9346100812569773</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.5240332738448501</v>
+        <v>0.4094589348045545</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.294524849157014</v>
+        <v>-0.4966959950348695</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5684661973835858</v>
+        <v>-0.6803206285284702</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5536580750299933</v>
+        <v>-0.6670727825523812</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7524849277884726</v>
+        <v>-0.7750762315606678</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.08520659151572829</v>
+        <v>-0.01753561290179562</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6830466694923913</v>
+        <v>0.7520467997373501</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.408062098205669</v>
+        <v>1.477340163038392</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5914021525437576</v>
+        <v>0.6614681588332232</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.2400899624174997</v>
+        <v>0.3094828410285757</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.8946398013916124</v>
+        <v>0.9642092371741384</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.4114065011633912</v>
+        <v>0.3861824134791405</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4063106347593148</v>
+        <v>0.2866163811542464</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.005348652931858</v>
+        <v>0.7889196043714932</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.6206268493221714</v>
+        <v>0.4041021430300731</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.06923597751475086</v>
+        <v>-0.05049205545549285</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.7568101780320404</v>
+        <v>0.6351750900859301</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.1794455470474077</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.005885</t>
+          <t>X &lt; -0.00588</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.765724459185911</v>
+        <v>-1.934146734165218</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1308304681399051</v>
+        <v>-0.05157327887039287</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.367364731420032</v>
+        <v>-1.547990235844459</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.925331907689575</v>
+        <v>0.7261948979170825</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.016696550549618</v>
+        <v>0.7167739194970792</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.557951761550321</v>
+        <v>2.248751761284417</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.091366203382506</v>
+        <v>0.914413488894688</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7591596043403541</v>
+        <v>0.455030849549118</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.132489906190237</v>
+        <v>0.8257397584688064</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.129862721641899</v>
+        <v>0.8943967601457459</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.147152580016872</v>
+        <v>0.9878564108219052</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.510732198392873</v>
+        <v>1.425479836422795</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.92865743234789</v>
+        <v>1.919117743234423</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.478508847534613</v>
+        <v>2.468257095285907</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.433973495386773</v>
+        <v>1.425004683456315</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.257825318787063</v>
+        <v>1.24917337690124</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.894939850859231</v>
+        <v>1.885474468421833</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.483094302709006</v>
+        <v>1.395524650351611</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.520430431183698</v>
+        <v>1.354676621776584</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.431451612903224</v>
+        <v>2.183370955493004</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.275347978098821</v>
+        <v>2.025933901776007</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.199392922456212</v>
+        <v>2.029617757448335</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.942118409851901</v>
+        <v>2.769927383066076</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.349381204950362</v>
+        <v>2.259068792754604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.004001</t>
+          <t>X &lt; -0.003997</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.196037817575466</v>
+        <v>-2.220968817285915</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2764173653191619</v>
+        <v>0.2375740577613641</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.822848252714152</v>
+        <v>-1.856732391707084</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.07442811623151613</v>
+        <v>0.02803170743523253</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7902609093179152</v>
+        <v>0.6659221194986387</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.958284458177168</v>
+        <v>1.828554268462788</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4246995367158348</v>
+        <v>0.1975280085879163</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.026574523166943</v>
+        <v>0.7949497588901835</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.333680404397633</v>
+        <v>1.100363864275479</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.073719608222241</v>
+        <v>0.8989778280319385</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5258794919871121</v>
+        <v>0.4137710641667098</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.171759894781474</v>
+        <v>1.117787528730481</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.691667442995261</v>
+        <v>1.698095161237291</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.778635400717334</v>
+        <v>1.887693902860512</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.016929238761222</v>
+        <v>1.126881200762497</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.07036544460048333</v>
+        <v>0.1812270549436903</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.7584711338020256</v>
+        <v>0.8686651541058481</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.2012569097605024</v>
+        <v>0.2504774276973976</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6851240725566967</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.965206185567013</v>
+        <v>1.885247472799186</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.898105060558287</v>
+        <v>1.753378922902982</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.092621394863571</v>
+        <v>1.946393848143906</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.431602121696791</v>
+        <v>2.284521342104476</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.419999273546182</v>
+        <v>2.169486366305094</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002118</t>
+          <t>X &lt; -0.002114</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.16994778304629</v>
+        <v>-1.228201522749771</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.04249923666419164</v>
+        <v>-0.02058644300575452</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.686455578461192</v>
+        <v>-1.746976294146108</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.07151892575654983</v>
+        <v>0.003511443430895156</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3396112090938317</v>
+        <v>0.2154088744092277</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.580311171381254</v>
+        <v>1.452231197789168</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.06678213597389515</v>
+        <v>-0.1911826596258663</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2903030000908942</v>
+        <v>0.1639583536051461</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3802918547331515</v>
+        <v>0.2535942287769259</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1106581246360037</v>
+        <v>0.03184174506417037</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5393523561478304</v>
+        <v>-0.5681851466375605</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.0621437386143171</v>
+        <v>-0.04322777838054037</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2419364714699626</v>
+        <v>0.3109366017149213</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4407477276624974</v>
+        <v>0.5100257924952203</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.2181835113748036</v>
+        <v>-0.1481175050853381</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8342959038168729</v>
+        <v>-0.8142347848230145</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4637638620532698</v>
+        <v>-0.4439502411282206</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.4347326151179089</v>
+        <v>-0.4647573315040248</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.0001229868588481509</v>
+        <v>-0.08079872368894314</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.164629005059027</v>
+        <v>1.081162111262998</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.432010561466178</v>
+        <v>1.295554547165764</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.407871562386468</v>
+        <v>1.271176446307791</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.9737727026868797</v>
+        <v>0.8389917537311149</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.6107697331314768</v>
+        <v>0.4768935871775071</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002342</t>
+          <t>X &lt; -0.0002304</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.071381679723402</v>
+        <v>-1.081120150974627</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4800793647316794</v>
+        <v>0.4642667986007325</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.7164870964154204</v>
+        <v>-0.7314830154949306</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.597676014748366</v>
+        <v>0.5765493945734903</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7521592975213096</v>
+        <v>0.690247728579827</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.528519937868467</v>
+        <v>1.46430476069186</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4515749996298126</v>
+        <v>0.3892304606448178</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.07499236856504865</v>
+        <v>0.01323890643443093</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.05052510014796496</v>
+        <v>-0.1118224220820423</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6866194640854459</v>
+        <v>-0.7081087905695256</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.100965431129886</v>
+        <v>-1.081919319473648</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.242318287772825</v>
+        <v>-1.184120558597137</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9893990379404229</v>
+        <v>-0.8916752069452301</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5909211382309678</v>
+        <v>-0.4933459622631133</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.043240807020332</v>
+        <v>-0.9450198861341121</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.234472343139188</v>
+        <v>-1.176510459029387</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.121459404525929</v>
+        <v>-1.103958222297287</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.462086903341756</v>
+        <v>-1.484091424397889</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9294471105375592</v>
+        <v>-0.9929075451941429</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.05831029716654967</v>
+        <v>-0.008196958446248459</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.316930987959168</v>
+        <v>0.2482213950633607</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.1442528398577068</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.252918870816643</v>
+        <v>0.1847334935243481</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.01063816853290689</v>
+        <v>-0.05695900242680096</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001649</t>
+          <t>X &lt; 0.001653</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1746</v>
+        <v>1752</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.096217723031245</v>
+        <v>-1.128142426814236</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.04104295214115439</v>
+        <v>-0.02082165189477792</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.939638337402414</v>
+        <v>-0.9195785176245366</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.09014597576749139</v>
+        <v>-0.0745607811604927</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.4850002782328247</v>
+        <v>0.4702667633828455</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.443195039399235</v>
+        <v>1.425597985842728</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3620765428819297</v>
+        <v>0.346397754786679</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.05443268821989733</v>
+        <v>-0.126034910088066</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3217738320993462</v>
+        <v>-0.3924322735589172</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7783945351522874</v>
+        <v>-0.8492913877680124</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7887733090392288</v>
+        <v>-0.8266754034699701</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.18176242891505</v>
+        <v>-1.186699650756694</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.110353875192629</v>
+        <v>-1.083667857464995</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.103920253425152</v>
+        <v>-1.044165850032094</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.330731094510618</v>
+        <v>-1.304129397897064</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.329283690953432</v>
+        <v>-1.335453511221424</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.259036366187722</v>
+        <v>-1.298722184035071</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.673144127502027</v>
+        <v>-1.744859816183904</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.081175720234938</v>
+        <v>-1.154487163208181</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5750000000000028</v>
+        <v>-0.6496811731340202</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4556503804101837</v>
+        <v>-0.5320244713299829</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.669212672878551</v>
+        <v>-0.7450903647138603</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.4749612941515693</v>
+        <v>-0.5509470730051902</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.631518659190931</v>
+        <v>-0.7072024495369789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003533</t>
+          <t>X &lt; 0.003536</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6879771152586756</v>
+        <v>-0.7333161315444627</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5676143200127086</v>
+        <v>-0.5659911030073346</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9774526690341077</v>
+        <v>-1.024329983713535</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.05730499610548634</v>
+        <v>0.05478726795450939</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.04170337403403579</v>
+        <v>-0.06315154067289086</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.5077631341397364</v>
+        <v>0.4852094069687425</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1454617644258391</v>
+        <v>0.07500098630673335</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5370913356631135</v>
+        <v>-0.6063083202651498</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7560763616181276</v>
+        <v>-0.7769171799413002</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9269392559669143</v>
+        <v>-0.9962152508875661</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.08444179307422</v>
+        <v>-1.077969404396818</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.507489631290014</v>
+        <v>-1.473295242515192</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.144456857454699</v>
+        <v>-1.131170442445026</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.125890443920916</v>
+        <v>-1.08459766839993</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.468763436095536</v>
+        <v>-1.454971181807828</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.662048541871926</v>
+        <v>-1.675931981687384</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.335845724100409</v>
+        <v>-1.378194442405857</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.941628497013781</v>
+        <v>-2.010613083876919</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.45718569076233</v>
+        <v>-1.527112373909112</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.242179980750727</v>
+        <v>-1.312438694975327</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.324074265521787</v>
+        <v>-1.394853605052496</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.27546567658662</v>
+        <v>-1.346502829228278</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.406127286110241</v>
+        <v>-1.476558113419422</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.502168310522364</v>
+        <v>-1.572509136761468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005417</t>
+          <t>X &lt; 0.00542</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2350</v>
+        <v>2356</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6981821908922043</v>
+        <v>-0.7566365871161764</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.926526650124849</v>
+        <v>-0.9427679724389009</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6116505319252781</v>
+        <v>-0.6306678238553403</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4306158957321742</v>
+        <v>0.4079730028810786</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.04699237142415313</v>
+        <v>0.01167412459071926</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3849924551814183</v>
+        <v>0.3490513071342463</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2709184891556902</v>
+        <v>0.2341834474624918</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.01665879727426045</v>
+        <v>-0.01983815210559214</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.002219472542350331</v>
+        <v>-0.03863582729132986</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2009071794517325</v>
+        <v>-0.2379059165204964</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3926496072516557</v>
+        <v>-0.4045147293382954</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7988621547943566</v>
+        <v>-0.7858959282524651</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5250482885357357</v>
+        <v>-0.4882895635713425</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5345406927904293</v>
+        <v>-0.4728330580729505</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.702187201871773</v>
+        <v>-0.665269327711087</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8028727151443533</v>
+        <v>-0.7906114489518359</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.7423392488634164</v>
+        <v>-0.7551805757684349</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.076978503543756</v>
+        <v>-1.114043294830935</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7085406109070576</v>
+        <v>-0.7462694863269093</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4964953271028065</v>
+        <v>-0.5345311789252989</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.8446772470770085</v>
+        <v>-0.8826003708673014</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.9380330156609773</v>
+        <v>-0.9758485106408301</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.020954096542098</v>
+        <v>-1.058205252873101</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.029364190618388</v>
+        <v>-1.066723656442882</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0073</t>
+          <t>X &lt; 0.007303</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6555455543576088</v>
+        <v>-0.6655766342975014</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.086339119388548</v>
+        <v>-1.095840378731921</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7627076865726607</v>
+        <v>-0.7732717311143915</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.0557292558319773</v>
+        <v>0.04361578570193814</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.02232711420075617</v>
+        <v>0.0004608444108313847</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1538695432590771</v>
+        <v>0.1318570917924617</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.02355374689665268</v>
+        <v>0.00142942972957627</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.03880481179666617</v>
+        <v>-0.06095528143949736</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.1303036878316988</v>
+        <v>-0.1523112676976979</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2217233716518336</v>
+        <v>-0.2439040344880681</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5298883763811659</v>
+        <v>-0.5292652201558639</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.614807522574516</v>
+        <v>-0.5917733798991094</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7684249546538879</v>
+        <v>-0.7221287983581561</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9509468142319335</v>
+        <v>-0.8816687493992106</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.8101405739201084</v>
+        <v>-0.7631130178535557</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.6972709598509894</v>
+        <v>-0.6735804648426011</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.730726310730681</v>
+        <v>-0.7298276989074495</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.085051439299036</v>
+        <v>-1.106513062922808</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.846090488227432</v>
+        <v>-0.8678548048626737</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.5583398209420025</v>
+        <v>-0.5804941450599372</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.7671100663188284</v>
+        <v>-0.7891658093422436</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.7810662554469516</v>
+        <v>-0.8031451437664217</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.794984351159215</v>
+        <v>-0.8169502115936211</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.003898635477583</v>
+        <v>-1.025584066675634</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.009184</t>
+          <t>X &lt; 0.009186</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2751</v>
+        <v>2755</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.679893411522805</v>
+        <v>-0.6869566235184195</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.032032394953042</v>
+        <v>-1.038686974844843</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7558565902574301</v>
+        <v>-0.7633185195726924</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4387025792200987</v>
+        <v>-0.4468277772263107</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6393321589990393</v>
+        <v>-0.6543066447219772</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3235485621383702</v>
+        <v>-0.3389362432481704</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4254033611094101</v>
+        <v>-0.4408717556499013</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3217922349677025</v>
+        <v>-0.3374990551538204</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4405256184210842</v>
+        <v>-0.4560595313531977</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.361335232967626</v>
+        <v>-0.3772122747254087</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5367358135133955</v>
+        <v>-0.552292257431624</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6348014765827941</v>
+        <v>-0.6295115856572409</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6007119564747114</v>
+        <v>-0.5741526003913933</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6921690391891175</v>
+        <v>-0.6654411369475639</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.5327006225671056</v>
+        <v>-0.5057927982293862</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.6046933278296081</v>
+        <v>-0.5993131898273063</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.7899348114925004</v>
+        <v>-0.8056416229669807</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8372891928649082</v>
+        <v>-0.8529676681558911</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5634951744303081</v>
+        <v>-0.5795199513104237</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.5002268602540809</v>
+        <v>-0.5163011643658635</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.6589411497387019</v>
+        <v>-0.6749497919202767</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.6407228456794272</v>
+        <v>-0.656790198742641</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.7077523911816854</v>
+        <v>-0.7236553557996857</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.7622427570197843</v>
+        <v>-0.7780988686670014</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2914</v>
+        <v>2918</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.7610038589024199</v>
+        <v>-0.7657195190121016</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9077290949009083</v>
+        <v>-0.9123155387388948</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7268698699909777</v>
+        <v>-0.7319950207378625</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4329134807576409</v>
+        <v>-0.4385860810729554</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.608579077034868</v>
+        <v>-0.6191165839782542</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4364590096234124</v>
+        <v>-0.4472004078097029</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5415530567132762</v>
+        <v>-0.5523136942029865</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2543385051877607</v>
+        <v>-0.2655541102192345</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2957954575405708</v>
+        <v>-0.3069533058940408</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2982518508374454</v>
+        <v>-0.3095696164330803</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2776271532461578</v>
+        <v>-0.2889249827132687</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.351592851592855</v>
+        <v>-0.3431204157840142</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2453148393107654</v>
+        <v>-0.2166348641792624</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4122911623120942</v>
+        <v>-0.3833842030819596</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.2641533190720864</v>
+        <v>-0.2350240625801305</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1961740372197553</v>
+        <v>-0.1876456876456842</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3441866235935578</v>
+        <v>-0.3557508588111915</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.4973450407440225</v>
+        <v>-0.508728408306844</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3636881943871302</v>
+        <v>-0.3752182362767442</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.2248971898560654</v>
+        <v>-0.2365868872281851</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3021565282986103</v>
+        <v>-0.3138577622355143</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3233735716364521</v>
+        <v>-0.3350686530879869</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.3711813273179487</v>
+        <v>-0.3827628199838458</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3924390018744006</v>
+        <v>-0.4040142396853597</v>
       </c>
     </row>
     <row r="28">
@@ -7632,161 +7632,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3028</v>
+        <v>3032</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5921541926360376</v>
+        <v>-0.5956604729604607</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6147413283977485</v>
+        <v>-0.6182704889190163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6261627388119635</v>
+        <v>-0.6298945990827605</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3702078292792734</v>
+        <v>-0.3743845908749819</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5201812968809989</v>
+        <v>-0.5279612232945965</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.47882690417444</v>
+        <v>-0.4866380590963573</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5763112790124509</v>
+        <v>-0.5841153574199112</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4090764238005846</v>
+        <v>-0.4171468695857925</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3817013054500507</v>
+        <v>-0.3898066231517987</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3475889690058054</v>
+        <v>-0.3558604641832659</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.350276725895732</v>
+        <v>-0.3585087229985788</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>-0.2240394470103979</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1554742203487152</v>
+        <v>-0.1447565236614565</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2915451895043688</v>
+        <v>-0.2806528597614744</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.2395170365530603</v>
+        <v>-0.2285575758504805</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2176142224845918</v>
+        <v>-0.2262759170653865</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3651110548128216</v>
+        <v>-0.3736042350061339</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.582385811551589</v>
+        <v>-0.5906141258346622</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5115986917628703</v>
+        <v>-0.5198930311518097</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.4370052770448538</v>
+        <v>-0.4453750636085445</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3668972087340165</v>
+        <v>-0.3754466541261365</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3901950686009599</v>
+        <v>-0.398730711404248</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.4588982908953056</v>
+        <v>-0.4673073081745542</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.4161935000424961</v>
+        <v>-0.4246757329913962</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01483</t>
+          <t>X &lt; 0.01484</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3132</v>
+        <v>3136</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4084270493779343</v>
+        <v>-0.4109547765098611</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5681297779910679</v>
+        <v>-0.5704924578698325</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4997588058010578</v>
+        <v>-0.5023628594186036</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3392426176998029</v>
+        <v>-0.3421278835835651</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.464568419206401</v>
+        <v>-0.4699968377108377</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3866246724862137</v>
+        <v>-0.3921355071113695</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5381584439312235</v>
+        <v>-0.5435628439967815</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4174199202226418</v>
+        <v>-0.4230107828448695</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4531527755029146</v>
+        <v>-0.458697388037308</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5093736718663848</v>
+        <v>-0.5149330396770324</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5029484816209191</v>
+        <v>-0.5084902727216516</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3049431484545977</v>
+        <v>-0.2923955516146535</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2338173044279301</v>
+        <v>-0.2210982083947499</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3727361636661541</v>
+        <v>-0.3598356656015369</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3124370676206141</v>
+        <v>-0.2994528483829626</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2715739247411619</v>
+        <v>-0.2775850104094388</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3867866007557907</v>
+        <v>-0.3926691496270323</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6003466908658268</v>
+        <v>-0.6059723152696534</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4928694252028336</v>
+        <v>-0.498612458542965</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3826530612244881</v>
+        <v>-0.3885201673739758</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3328734552499455</v>
+        <v>-0.3388658901497408</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3259997530898318</v>
+        <v>-0.3320128719866844</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.3832807130961911</v>
+        <v>-0.3891951257536022</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3764199771459289</v>
+        <v>-0.3823550448216722</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4633982137308479</v>
+        <v>-0.4652555816760469</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5948909334914774</v>
+        <v>-0.596614257468481</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4271633233458942</v>
+        <v>-0.4292192848003111</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3125566883140394</v>
+        <v>-0.3148176097351012</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4419181606010909</v>
+        <v>-0.4461779764935585</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3309052359108549</v>
+        <v>-0.3352903031880956</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5241305214209078</v>
+        <v>-0.5283431258920785</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3788833451711682</v>
+        <v>-0.383303704241186</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4758005822416322</v>
+        <v>-0.4800992071919268</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.54414208866595</v>
+        <v>-0.548424188565221</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5957426420933487</v>
+        <v>-0.5999396289451724</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.3877378486386931</v>
+        <v>-0.3922213627216991</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3364651019253557</v>
+        <v>-0.3411117176128187</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4141857950423642</v>
+        <v>-0.4187570992172596</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3658343061949267</v>
+        <v>-0.3705254175936759</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.2844703681953007</v>
+        <v>-0.2892152681017279</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4000005850634807</v>
+        <v>-0.4046153582388925</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6117614430398675</v>
+        <v>-0.6161230421075174</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4711347047113392</v>
+        <v>-0.4756567295086782</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2655613044841658</v>
+        <v>-0.2703277041632433</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1942355407419925</v>
+        <v>-0.1991409805517605</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2200732556666054</v>
+        <v>-0.2249558787182977</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.3031844412846141</v>
+        <v>-0.307942246527702</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2034849027330168</v>
+        <v>-0.2083772928553955</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3236</v>
+        <v>3240</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5289848607983529</v>
+        <v>-0.5302127278971867</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4181366994006481</v>
+        <v>-0.419523359973077</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3676341667962717</v>
+        <v>-0.3691780727416329</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3274098622935853</v>
+        <v>-0.3290509679855731</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4297501908397834</v>
+        <v>-0.4329305641866483</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3482714074913105</v>
+        <v>-0.351541585919648</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5198486909556621</v>
+        <v>-0.5229609852902612</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4119968440662376</v>
+        <v>-0.4152619850294244</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4452330645547704</v>
+        <v>-0.448456732635357</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4630975314725987</v>
+        <v>-0.4663522373501507</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6018926077055156</v>
+        <v>-0.6049606991992533</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3399617623755518</v>
+        <v>-0.3433724674848619</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3379394579594006</v>
+        <v>-0.3414289277020117</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4795316595082681</v>
+        <v>-0.4828636709824821</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.411499666804616</v>
+        <v>-0.4149610846224192</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2912476781477551</v>
+        <v>-0.2948201224063354</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4070719174184276</v>
+        <v>-0.4105127823750863</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4937746081512628</v>
+        <v>-0.4971177803046203</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.4136328113563081</v>
+        <v>-0.4170626591552775</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.2083333333333357</v>
+        <v>-0.212006152278974</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1775397112517396</v>
+        <v>-0.18128876444257</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2041616412928207</v>
+        <v>-0.2078851962331782</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2816292941423768</v>
+        <v>-0.2852413308499493</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1537888809374124</v>
+        <v>-0.1575660551517259</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3271</v>
+        <v>3275</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2436417457629361</v>
+        <v>-0.2448495391445178</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2285498812211202</v>
+        <v>-0.2297943697738987</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1938333504593857</v>
+        <v>-0.1951963588710228</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1615752616367416</v>
+        <v>-0.1630157966439825</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2666623064066727</v>
+        <v>-0.2693091285769214</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.214413656252944</v>
+        <v>-0.2171157701976654</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3619371842274575</v>
+        <v>-0.3645023928800839</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3798432672825243</v>
+        <v>-0.3824030301103036</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3514092249683571</v>
+        <v>-0.3540030280237971</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4686238164509362</v>
+        <v>-0.4711175209695497</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.542115946358571</v>
+        <v>-0.5445074249242694</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.346854637899412</v>
+        <v>-0.3495000766769891</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2959093798504568</v>
+        <v>-0.2986779075093438</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3469041206415895</v>
+        <v>-0.3496240034962383</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3170767271977226</v>
+        <v>-0.3198695189237597</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2832191560238186</v>
+        <v>-0.2860235003092129</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3382232007852153</v>
+        <v>-0.3409693778505556</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3640686979480421</v>
+        <v>-0.3667906837050054</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2519094854861237</v>
+        <v>-0.2547585515225137</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.0772900763358777</v>
+        <v>-0.08034403009427393</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.05259258981651982</v>
+        <v>-0.05570735071756161</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.07970389116057675</v>
+        <v>-0.08279147006476961</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1533656282317892</v>
+        <v>-0.1563505432118575</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.08880986732601315</v>
+        <v>-0.09187950346007767</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3299</v>
+        <v>3303</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.09194199575681949</v>
+        <v>-0.09304194205493843</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1399804494526364</v>
+        <v>-0.1410374456163694</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.08755160134872142</v>
+        <v>-0.08873321352035646</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1218145000245201</v>
+        <v>-0.1229857855519327</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1989465586478332</v>
+        <v>-0.2010990723091055</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1455386191640926</v>
+        <v>-0.1477488788704164</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2681648967999806</v>
+        <v>-0.2702615168608204</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3184101615930786</v>
+        <v>-0.3204593706426024</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2898470517648661</v>
+        <v>-0.2919302592448645</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.3824084047224972</v>
+        <v>-0.3844141704474069</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4227404940116699</v>
+        <v>-0.4246872798780572</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3522640150547076</v>
+        <v>-0.3543090021895807</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3112636605465937</v>
+        <v>-0.3134072818855884</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3032633853956028</v>
+        <v>-0.3054274639658345</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2792526790660688</v>
+        <v>-0.2814751959877881</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.210393144346753</v>
+        <v>-0.2126749219772464</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2660450064618018</v>
+        <v>-0.2682666746502775</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2925391219410471</v>
+        <v>-0.2947346533484492</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1794772096640145</v>
+        <v>-0.1818016399703382</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.09555706933090846</v>
+        <v>-0.09797646447778163</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.04539604800461916</v>
+        <v>-0.04790081116276923</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.133507176243107</v>
+        <v>-0.1359100515502689</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1739257527038873</v>
+        <v>-0.1762694190629333</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.0802564661628864</v>
+        <v>-0.08271827367360629</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006951619584526725</v>
+        <v>0.006071612379287217</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04388248986440857</v>
+        <v>-0.04471265508136213</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03593445576071019</v>
+        <v>-0.03681841508743133</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.04703890769828689</v>
+        <v>-0.04793190278233794</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1866698530356743</v>
+        <v>-0.1881698671097922</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1319406458110848</v>
+        <v>-0.1335011712969347</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2311104639732378</v>
+        <v>-0.2325772276610749</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3134636006692872</v>
+        <v>-0.3148415385469292</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3146488045302434</v>
+        <v>-0.3160249803693773</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4139366505125537</v>
+        <v>-0.4152188446945075</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4212782206640355</v>
+        <v>-0.4225441559381338</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3841553183658419</v>
+        <v>-0.3854750390482096</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3546695056501719</v>
+        <v>-0.3560598054526665</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3489469652954824</v>
+        <v>-0.3503518313576635</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3017643846100597</v>
+        <v>-0.3032468213858479</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2875928423200236</v>
+        <v>-0.2890749601275928</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3140939946881716</v>
+        <v>-0.3155494940510479</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3114204037290023</v>
+        <v>-0.312883296432183</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2273120005949565</v>
+        <v>-0.2288699246326544</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1423860911271007</v>
+        <v>-0.1440409728966898</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.03814043898296404</v>
+        <v>-0.03993794150760976</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1261290699195143</v>
+        <v>-0.1278245482594116</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1634247025988813</v>
+        <v>-0.1650680601703129</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1314560912084133</v>
+        <v>-0.1331411506308982</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3345</v>
+        <v>3349</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.007588808025928984</v>
+        <v>0.006839719308246117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.04475713365893341</v>
+        <v>0.04395484823008644</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01227724187877044</v>
+        <v>-0.01304948900268244</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.02608936037872667</v>
+        <v>-0.02686412184054632</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1963125635545921</v>
+        <v>-0.1975418471020802</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1410742818237054</v>
+        <v>-0.1423651336492711</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2131076293483218</v>
+        <v>-0.2143337057948074</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2962142967733357</v>
+        <v>-0.2973495974290756</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2972291536702087</v>
+        <v>-0.2983629411392457</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3693516822042753</v>
+        <v>-0.3704205347278275</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3755894120184209</v>
+        <v>-0.3766444769339188</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3694659525758652</v>
+        <v>-0.3705363065139125</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3444458764632543</v>
+        <v>-0.3455760033270963</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3097939196969008</v>
+        <v>-0.3109718533627586</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2951516868381958</v>
+        <v>-0.2963650113540766</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2787259950423149</v>
+        <v>-0.2799442142605741</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2758088407863184</v>
+        <v>-0.2770348456494176</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2735414736223731</v>
+        <v>-0.2747737374702908</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1889094672622207</v>
+        <v>-0.190237848175947</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1334353538369655</v>
+        <v>-0.1348258808618468</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.03170100636951645</v>
+        <v>-0.03322798804662597</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.08976347181116751</v>
+        <v>-0.0912240432189293</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09594933581534093</v>
+        <v>-0.09739623052620061</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.09427529960925796</v>
+        <v>-0.09572706875814418</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_6.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_6.xlsx
@@ -618,1641 +618,1641 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02754</t>
+          <t>X ≈ -0.02751</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-31.99179993544988</v>
+        <v>-30.2586380721032</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-25.23722723505686</v>
+        <v>-22.86881832261543</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-19.57654253493688</v>
+        <v>-16.47891093915897</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.090234936388867</v>
+        <v>-1.778838035880561</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.426561474107629</v>
+        <v>-2.053838214159285</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.861058297451919</v>
+        <v>5.751872687910584</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.200095326105519</v>
+        <v>4.962372792194202</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6.925622524236587</v>
+        <v>4.660635475553697</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.968933581173602</v>
+        <v>4.789449207566086</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.4281071294818</v>
+        <v>19.31954945018062</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.59163588999588</v>
+        <v>11.93336965808012</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.31793906576547</v>
+        <v>11.66131072870728</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.083240920932631</v>
+        <v>2.886480730121313</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.98593707918232</v>
+        <v>10.30942065811477</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4.209871460083129</v>
+        <v>1.96074914499318</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.803964945025101</v>
+        <v>10.19528816809265</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>4.672025063256157</v>
+        <v>2.418588436524097</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.568974081976265</v>
+        <v>2.286911812577785</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.346339649176066</v>
+        <v>2.501727574825829</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.160430965399897</v>
+        <v>2.716797983558408</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.433378888479076</v>
+        <v>2.150707967260367</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.35893577522544</v>
+        <v>2.076238523601759</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-2.506082501124894</v>
+        <v>-5.36965694189724</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>-5.533376452483438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02565</t>
+          <t>X ≈ -0.02563</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-13.54623108894411</v>
+        <v>-9.724995621092624</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-20.50522068670796</v>
+        <v>-16.18074453848882</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-35.19098939060284</v>
+        <v>-29.85555404337939</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-35.91027849948198</v>
+        <v>-36.66624289915046</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-29.62680936667498</v>
+        <v>-30.7369228942524</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-22.82012923922023</v>
+        <v>-18.15816689678191</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-16.96223031064244</v>
+        <v>-12.73634520909951</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-17.2439135156876</v>
+        <v>-13.04332252792052</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-23.8445154953282</v>
+        <v>-19.14186166823288</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.34343233027191</v>
+        <v>-7.491981974397518</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.71482157064202</v>
+        <v>-13.44913338242227</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-11.35521305253075</v>
+        <v>-7.501064580955628</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.47777644112369</v>
+        <v>-14.84374755352591</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5913661297060742</v>
+        <v>-2.632918546451315</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.713002006722135</v>
+        <v>-9.546790623201694</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-12.77283421783095</v>
+        <v>-15.22488214030895</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.257399926302099</v>
+        <v>-9.095815857087551</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.2909188489689356</v>
+        <v>-2.992113193673561</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.15010548831215</v>
+        <v>-9.019539525333684</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.965349314315482</v>
+        <v>-2.565373307807093</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.509149802039026</v>
+        <v>-9.377427737377786</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.07577839333082181</v>
+        <v>-3.209072326408879</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>7.014865341518615</v>
+        <v>3.281615815479078</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.941199376948553</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02377</t>
+          <t>X ≈ -0.02375</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.94648247781867</v>
+        <v>3.576498854626443</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.46679031677751</v>
+        <v>10.42985201290638</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.46701604371717</v>
+        <v>12.73436005721199</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16.18978526270378</v>
+        <v>19.24942047808864</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.282445047775873</v>
+        <v>1.225110674132893</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.760811135452677</v>
+        <v>4.932054842469434</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.994453988449088</v>
+        <v>4.142245562412569</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.719364048253304</v>
+        <v>3.840306685443835</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.10310938824319</v>
+        <v>-3.141689449976404</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.5605778768188827</v>
+        <v>-0.3787532133773652</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.601198248947981</v>
+        <v>-3.665384019630793</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.879837372818642</v>
+        <v>-3.942174478194559</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.436614614997062</v>
+        <v>-5.054158294621423</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.221631359253877</v>
+        <v>-1.742654150104663</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-4.878700573576744</v>
+        <v>-2.422933840141404</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-4.287310598294091</v>
+        <v>-1.863783945339648</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.422051063242549</v>
+        <v>-1.967756857793354</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.527890300523737</v>
+        <v>-2.10079775945664</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.8706482255910188</v>
+        <v>1.678793482422151</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.6843176924822529</v>
+        <v>-1.673551534948501</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-1.226531707361566</v>
+        <v>1.32728530628161</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.143485831989437</v>
+        <v>4.821824154546995</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.418531866594314</v>
+        <v>5.066778578430821</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.791774089589943</v>
+        <v>8.477612558505577</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02189</t>
+          <t>X ≈ -0.02186</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.28465945574056</v>
+        <v>-5.021713501515599</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-8.735407352201122</v>
+        <v>-8.277208296921309</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.103018263298047</v>
+        <v>-6.516274109687892</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-17.15603110161935</v>
+        <v>-16.14316471682298</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-11.2903297532096</v>
+        <v>-10.39606659389594</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.134636023752293</v>
+        <v>-1.203655333884655</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.012387970329279</v>
+        <v>-5.009918832727095</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.181353156383338</v>
+        <v>-2.298970604618958</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.251665808146143</v>
+        <v>-8.204890365357492</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.911662209164078</v>
+        <v>-5.982547772571706</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.527719312884592</v>
+        <v>-2.694953038255342</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.307507416495767</v>
+        <v>0.04781418473488941</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.925527415541261</v>
+        <v>-4.083088105727214</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.262560062152588</v>
+        <v>-7.353189454858857</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.803839928137073</v>
+        <v>-5.01312021737894</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.329524624755663</v>
+        <v>-7.477734052879136</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.464905762401386</v>
+        <v>-7.583415048206511</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.571389338196497</v>
+        <v>-7.718166263876569</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-6.357896334578349</v>
+        <v>-7.506397905659313</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.052087922214398</v>
+        <v>-4.267756010723645</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-3.595021590341453</v>
+        <v>-4.83593505063623</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-3.67193648840459</v>
+        <v>-4.912558631483776</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-3.398663635293317</v>
+        <v>-4.670543874630397</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-3.475467289719624</v>
+        <v>-4.834075753182745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02001</t>
+          <t>X ≈ -0.01998</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.536677875041917</v>
+        <v>4.49138186408905</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.987143442813824</v>
+        <v>7.453268527166678</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.692383758060565</v>
+        <v>-6.612575313015377</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5380115058354917</v>
+        <v>2.415215842699553</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.203946520199473</v>
+        <v>-1.06522620441946</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.702553284862262</v>
+        <v>2.296135956339562</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.011719799418991</v>
+        <v>-8.1212314633677</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.290577455053679</v>
+        <v>-8.426984754887357</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-17.20480681889667</v>
+        <v>-17.93446324657992</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-11.3417259702366</v>
+        <v>-12.30868894480379</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-21.03242598019021</v>
+        <v>-21.68044971110931</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-17.99586628354415</v>
+        <v>-18.74892924582635</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-12.47614612128163</v>
+        <v>-13.43536061527215</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-12.70060227899749</v>
+        <v>-13.68715017116118</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-16.68440865603356</v>
+        <v>-17.58802514656164</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-12.77160607299292</v>
+        <v>-13.81565315950864</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-12.90900601456134</v>
+        <v>-13.92331425807473</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-9.690362117395985</v>
+        <v>-10.84018235945528</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.14969976895496</v>
+        <v>-7.408571152927188</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.6933420317715928</v>
+        <v>-0.7529152259440792</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.178679485484814</v>
+        <v>-4.542862238306846</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.255486036895867</v>
+        <v>-4.619424490008107</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-2.982107321502788</v>
+        <v>-4.3773514879896</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.607866043613704</v>
+        <v>1.910792282007876</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01812</t>
+          <t>X ≈ -0.0181</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.564118788863318</v>
+        <v>-6.274552439483749</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.449690064845186</v>
+        <v>4.515366028043253</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.23781031566038</v>
+        <v>8.789550626008428</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12.37233324317421</v>
+        <v>13.7245278155375</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.200856113287855</v>
+        <v>10.6934123024262</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.543239035658097</v>
+        <v>5.325481360019602</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.778075138463791</v>
+        <v>4.536726363770448</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.660287110716894</v>
+        <v>1.47084585185236</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.703312121785018</v>
+        <v>1.599793629629332</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.754943483748086</v>
+        <v>-4.724127190170734</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.32866091827588</v>
+        <v>-7.220982024908054</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9158398072002925</v>
+        <v>-1.964261306890457</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.035058582630043</v>
+        <v>-3.075593086384764</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.256324489328279</v>
+        <v>-3.324245150209094</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.634596691580434</v>
+        <v>4.305122108776651</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.5290526533087743</v>
+        <v>-0.6755935425642576</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.246631956395873</v>
+        <v>1.992488482334743</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2912553904324682</v>
+        <v>-0.9120478496415814</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.345936555797522</v>
+        <v>-3.471799200658829</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-5.013815471069861</v>
+        <v>-6.033065654850233</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-8.411800081097198</v>
+        <v>-9.376973080805207</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-11.34561847376627</v>
+        <v>-12.23111806279334</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-11.07479417848312</v>
+        <v>-11.99144366598465</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-14.01118157543391</v>
+        <v>-14.93508585419284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01624</t>
+          <t>X ≈ -0.01622</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.9723789224630792</v>
+        <v>-0.09753308295731244</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.059901067561725</v>
+        <v>-3.831322368310097</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.656381218959503</v>
+        <v>-3.357190637828474</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.233951973054012</v>
+        <v>2.245016967825741</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1427184366378569</v>
+        <v>-1.515684303473527</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.163271679891253</v>
+        <v>2.126411727167486</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.380244076592277</v>
+        <v>1.336834735595517</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.09844333002065</v>
+        <v>2.779763489344454</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.519307080093789</v>
+        <v>-5.821321071701192</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.220787860731626</v>
+        <v>-8.362371282731729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.945471040935558</v>
+        <v>-9.840920799027728</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.479088218116843</v>
+        <v>-4.876970080197481</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.29034388106217</v>
+        <v>-11.2340108145255</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.599444457340077</v>
+        <v>-7.987549835003776</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-16.94584423765213</v>
+        <v>-15.66756163053612</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-10.59016571391028</v>
+        <v>-9.86280145520422</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-10.73047643292298</v>
+        <v>-9.969428222041394</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-7.001784767598139</v>
+        <v>-6.602931920257745</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-6.783451758087686</v>
+        <v>-6.390989027755346</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-6.593421817140403</v>
+        <v>-6.178856865482686</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-5.228175105266196</v>
+        <v>-4.994907949472974</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-7.995906776531342</v>
+        <v>-8.578233727613579</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.646582820701674</v>
+        <v>-10.09135068113439</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-13.5716211358739</v>
+        <v>-13.76549521091838</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01435</t>
+          <t>X ≈ -0.01434</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-8.954820490747018</v>
+        <v>-10.30315582741311</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.765131770087578</v>
+        <v>2.792027722474366</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.715605556340222</v>
+        <v>-5.088660031822812</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5956715358892808</v>
+        <v>1.732478310312288</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.265812473418919</v>
+        <v>-3.649349568421052</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.10151069003508</v>
+        <v>-9.432940207703908</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.505156993482672</v>
+        <v>-5.772887289327237</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-13.32242114123179</v>
+        <v>-13.50212988384382</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.26736186354076</v>
+        <v>-10.40649815962527</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.531303379249117</v>
+        <v>-9.716361758149262</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.75202480022449</v>
+        <v>-7.961874442244451</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.013771580013326</v>
+        <v>-5.267498448078598</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.417158306625844</v>
+        <v>1.056906418071549</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.196815020945486</v>
+        <v>0.8093063324737102</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.9698283849327183</v>
+        <v>-1.35811010144208</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.3774736422225473</v>
+        <v>-0.7990975953153878</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.513171622808798</v>
+        <v>2.075422427810281</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.6161322834370822</v>
+        <v>-1.035838937119095</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.9140537849457</v>
+        <v>-2.312327002850139</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.75553711256164</v>
+        <v>-5.08019368273208</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.270918605318506</v>
+        <v>-2.666513933102053</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-5.375036588012961</v>
+        <v>-5.725703987164543</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.073170255055864</v>
+        <v>-2.500065246940139</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-3.664861229113214</v>
+        <v>-4.155649701622025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01247</t>
+          <t>X ≈ -0.01245</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.412360043159232</v>
+        <v>-1.703897707764803</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.488603092052259</v>
+        <v>-1.279320133241328</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4191597281379558</v>
+        <v>-0.04122277485417669</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.135069158648172</v>
+        <v>-0.6320130011179756</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.215035008551034</v>
+        <v>0.3378171060818005</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.802438649545948</v>
+        <v>-3.236060135459319</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.580544439826916</v>
+        <v>-4.027533927063587</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-9.903966585626932</v>
+        <v>-9.304663951295439</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.839103340387943</v>
+        <v>-2.959742820601605</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.088770695525241</v>
+        <v>-1.264652353355999</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.966049882883759</v>
+        <v>2.739890309510791</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.688003679525785</v>
+        <v>2.463889927001006</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.569886278331261</v>
+        <v>1.354183373797035</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.349629282948264</v>
+        <v>1.106712497796437</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.481834135768686</v>
+        <v>4.166667549365265</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.338778719561688</v>
+        <v>5.974086653268586</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>7.470428501913048</v>
+        <v>7.119473619721454</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.31345593125603</v>
+        <v>1.999290233677755</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.265571715582816</v>
+        <v>0.9660208650794999</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.452516395221515</v>
+        <v>1.180484584657719</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.354207570317655</v>
+        <v>-0.6348123831598471</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.8350334213794426</v>
+        <v>0.5389870785710542</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1558624712503729</v>
+        <v>-0.4671137861597643</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.497619188453804</v>
+        <v>-1.879530298637292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01059</t>
+          <t>X ≈ -0.01057</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7.176918874773676</v>
+        <v>7.433282011259749</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.812311143275409</v>
+        <v>9.098734145989006</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>9.337429981943465</v>
+        <v>9.750793798425882</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.59313834810521</v>
+        <v>10.11311634491031</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>12.22567544310775</v>
+        <v>11.74712001773945</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.502971473788186</v>
+        <v>6.703566571451724</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.682844505112975</v>
+        <v>8.783568020108106</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>9.389816332199445</v>
+        <v>9.44148532324634</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11.40247330845087</v>
+        <v>11.48602342631427</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>13.58690005394632</v>
+        <v>13.56827249239591</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>9.922398762692815</v>
+        <v>10.0144317754318</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>10.63396390702911</v>
+        <v>10.69854625486036</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>14.44094860583568</v>
+        <v>14.38156256254</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12.24921076756534</v>
+        <v>12.22211777050075</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12.57638838415142</v>
+        <v>12.50552753142285</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>8.240853406457376</v>
+        <v>8.274488063606938</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>9.097446710454079</v>
+        <v>9.132849110727939</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>12.94795565354204</v>
+        <v>12.84209801446573</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>12.18105252872636</v>
+        <v>12.10066055387075</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>13.36371230475569</v>
+        <v>13.2791578944497</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>12.81980077185977</v>
+        <v>12.71686464339081</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>13.73243797695506</v>
+        <v>13.60692339315447</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>12.62328799520553</v>
+        <v>12.89369388826</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>11.56166142315166</v>
+        <v>11.77431585520888</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.008705</t>
+          <t>X ≈ -0.008689</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.905194909654853</v>
+        <v>-2.631214887790399</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4131298512343662</v>
+        <v>-1.103485753359948</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.196444767087279</v>
+        <v>-9.447039822576045</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.520697710350845</v>
+        <v>-3.827890415096206</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.521469729552926</v>
+        <v>-6.7620443080001</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.845101104269233</v>
+        <v>-2.171130082689011</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.376276793185284</v>
+        <v>-5.624581859005019</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.100740371795752</v>
+        <v>-1.488871592010625</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.972584483777567</v>
+        <v>-2.249626635467884</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.677810177864721</v>
+        <v>-3.93140349063512</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.784185749650263</v>
+        <v>-4.55030124598197</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-9.021447837845898</v>
+        <v>-10.16311681570703</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.751314823861797</v>
+        <v>-5.051629782701916</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3143449372157363</v>
+        <v>-1.742162504938428</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.8522935779715652</v>
+        <v>-0.6418896883035856</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.211425937051963</v>
+        <v>-3.643699008215563</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5142428148780951</v>
+        <v>-1.967418137783405</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.53716016779024</v>
+        <v>-2.991303956875612</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.320163398012774</v>
+        <v>-2.778137307642112</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.131164270190709</v>
+        <v>-2.564935642271024</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.7624648117226442</v>
+        <v>-2.240591827249062</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.674123208013789</v>
+        <v>-4.100883560254807</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.478733787814747</v>
+        <v>-2.96635046638287</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.844733344765494</v>
+        <v>-4.915244584351576</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006822</t>
+          <t>X ≈ -0.006807</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.023757576012557</v>
+        <v>-2.57505718148682</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07996091667877181</v>
+        <v>-1.530555396645852</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.01500698000478451</v>
+        <v>-1.494947100920314</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.332870629055307</v>
+        <v>0.4934471133356766</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.800023424378374</v>
+        <v>4.734249371258372</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>8.058519651219456</v>
+        <v>6.826807363487241</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.14539884094264</v>
+        <v>2.524247760229045</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.628095434249737</v>
+        <v>2.868685701048641</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>7.419875394303787</v>
+        <v>6.226228841674207</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7.72586070454615</v>
+        <v>6.082436134377581</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>8.688459136670453</v>
+        <v>7.648310478999406</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7.721722712076172</v>
+        <v>6.728692905903301</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.000056745624939</v>
+        <v>5.620092740922324</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.781868180080849</v>
+        <v>5.374245536421732</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.752174268978969</v>
+        <v>3.402928790182415</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.347471282363898</v>
+        <v>5.25890806923644</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.90422515829772</v>
+        <v>5.156996552078873</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.802000340610476</v>
+        <v>6.322580280336311</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.020005501893941</v>
+        <v>6.539135392173733</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.277255274129573</v>
+        <v>8.700826161117774</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>9.117253453810015</v>
+        <v>9.434705595689493</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>11.11037300964228</v>
+        <v>11.30983039706071</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>12.07450289453813</v>
+        <v>11.55747782026112</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>11.30901546890106</v>
+        <v>11.39969048058349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004939</t>
+          <t>X ≈ -0.004925</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.371622945856359</v>
+        <v>-2.266828491966486</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.404356519730065</v>
+        <v>2.475844567804728</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.09453353394467</v>
+        <v>-2.759733538708424</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.785188738827955</v>
+        <v>-2.355095481613745</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4581733528750149</v>
+        <v>0.3659249102388813</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1318996732519508</v>
+        <v>0.5187002196711319</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.680834627306872</v>
+        <v>-2.76352466807635</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.153800650316896</v>
+        <v>2.924552806325281</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.19479595965737</v>
+        <v>2.553271464343219</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9131902392123976</v>
+        <v>1.263101788475453</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.880630307452613</v>
+        <v>-1.464656858656902</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1142902092073612</v>
+        <v>1.259435963604119</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8103425247883038</v>
+        <v>1.650292349211362</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4326832853596017</v>
+        <v>0.4022422821735887</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.06517386963096072</v>
+        <v>1.22620982882237</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.077688467540519</v>
+        <v>-3.222464948759693</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.189201581053794</v>
+        <v>-1.824324131375363</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.319160119229601</v>
+        <v>-2.959707078726133</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.055387418399611</v>
+        <v>-0.7406972018742621</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.6936981512452007</v>
+        <v>1.981469947028828</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.6645567252512095</v>
+        <v>1.917768577414826</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.614351789483138</v>
+        <v>2.847886271740308</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>2.088037066893115</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>2.932027490307441</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.003056</t>
+          <t>X ≈ -0.003043</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.30728745593386</v>
+        <v>2.836396163500922</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.199464355027615</v>
+        <v>-1.525879485660795</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.249880377176375</v>
+        <v>-0.9646056582878089</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1080627978586506</v>
+        <v>0.2766158362837388</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.834962727637247</v>
+        <v>-0.9157541505053715</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2560258558018162</v>
+        <v>0.161948628622099</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.957451894017225</v>
+        <v>-1.559990751262653</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.699386996621499</v>
+        <v>-2.522488901302978</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.584978032477402</v>
+        <v>-3.05219935852061</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.89552340974479</v>
+        <v>-3.584913082970772</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.012327159526613</v>
+        <v>-4.6889270169562</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.291076562974609</v>
+        <v>-4.967860427388182</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.951929847383681</v>
+        <v>-5.62168175316647</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.711739219689584</v>
+        <v>-4.953947449586863</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-5.910292856161853</v>
+        <v>-5.175133186478121</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-5.317676304980942</v>
+        <v>-5.075901547043472</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-6.382420971896067</v>
+        <v>-6.101200085403626</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.703036201170505</v>
+        <v>-3.478160677341677</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.487100954132458</v>
+        <v>-3.265954653084677</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.560765027499748</v>
+        <v>-2.593902386609244</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7784963457088381</v>
+        <v>-0.8602166599508436</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.784574865257468</v>
+        <v>-1.85625278088559</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-5.696146664403322</v>
+        <v>-5.758955616963988</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-7.167327754835902</v>
+        <v>-7.305797579743171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001172</t>
+          <t>X ≈ -0.001161</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4097023615410222</v>
+        <v>-0.9327615479187941</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.680445181343892</v>
+        <v>1.81104474300728</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.90428380371376</v>
+        <v>3.542594140330316</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.191535796023715</v>
+        <v>2.577159334650055</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.855573647015888</v>
+        <v>2.301291406388543</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.521110428468596</v>
+        <v>1.338383700181076</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.031014001562141</v>
+        <v>3.156512580290936</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6719501079649461</v>
+        <v>-0.1377492439532446</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.771955586862688</v>
+        <v>-1.130652968593083</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.067639743937384</v>
+        <v>-3.048962123682372</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.413093993268724</v>
+        <v>-2.188059705866856</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.355486503308839</v>
+        <v>-5.239133549773968</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.337808279903363</v>
+        <v>-4.855923983266997</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.039252227178771</v>
+        <v>-3.984082120989079</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.558838164228149</v>
+        <v>-3.540799810629622</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.822897277250576</v>
+        <v>-1.4844399970086</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.102111799721634</v>
+        <v>-2.713280429714992</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-6.116911891830185</v>
+        <v>-4.72124318820952</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.139230529252401</v>
+        <v>-3.760257834680189</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-4.949308038134426</v>
+        <v>-3.549175406825256</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.504752337187625</v>
+        <v>-3.366614193878078</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.343957077222683</v>
+        <v>-3.818571593038612</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.779406028862759</v>
+        <v>-1.697906073275647</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.473558892773063</v>
+        <v>-1.108853606908134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007113</t>
+          <t>X ≈ 0.0007209</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.36208174304344</v>
+        <v>-1.277576854953885</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.349802600005127</v>
+        <v>-2.169210669067354</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.828356682740264</v>
+        <v>-1.809587324934867</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.196364062328236</v>
+        <v>-3.367990966156043</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5797739508485975</v>
+        <v>-0.7493420159789466</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.251153540211725</v>
+        <v>1.333898619401531</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1445065510355619</v>
+        <v>0.2226845834879754</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7923440664694752</v>
+        <v>-0.72347519464752</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.7355462263059</v>
+        <v>-1.88130438633933</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.529045814424485</v>
+        <v>-1.708765413944199</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3858111804004807</v>
+        <v>0.1708829794800693</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.207052616251204</v>
+        <v>-1.390594067966497</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.005851955334677</v>
+        <v>-2.182560519015531</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.671699549167137</v>
+        <v>-3.527796720237724</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.020237270191117</v>
+        <v>-2.919289773654839</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.098564705396093</v>
+        <v>-2.362079947378341</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.234404898980401</v>
+        <v>-2.145141808978487</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.00016486950922</v>
+        <v>-2.923170937400108</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.926773955887086</v>
+        <v>-1.744626839454028</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.713612356445452</v>
+        <v>-3.79344086400701</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.256158524411447</v>
+        <v>-4.36219476003523</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.660951854241553</v>
+        <v>-4.762799912865034</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.057529773338452</v>
+        <v>-4.522196081847383</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.804414658140672</v>
+        <v>-4.039724473394493</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002595</t>
+          <t>X ≈ 0.002603</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.404263605105179</v>
+        <v>0.7536183269057446</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.506503608937521</v>
+        <v>-3.466080996025859</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.583671829278316</v>
+        <v>-1.962940586434968</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7516564591041828</v>
+        <v>0.1915605200595962</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.938742672712024</v>
+        <v>-3.138956294748141</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.584740859739455</v>
+        <v>-4.514567707016795</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.387288009100573</v>
+        <v>-1.636447387450957</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.187678783090853</v>
+        <v>-3.465114561225619</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.840578640523546</v>
+        <v>-2.725074134503366</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.780351595737528</v>
+        <v>-1.377802168342178</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.421882401649228</v>
+        <v>-2.328457113889741</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.003569550283551</v>
+        <v>-2.90776214206921</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.379603577523248</v>
+        <v>-1.087706453647073</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.295247841014955</v>
+        <v>-1.335039247176496</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.258103501419427</v>
+        <v>-2.318101430748811</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-3.49928293907999</v>
+        <v>-2.98577506004186</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.80318802182429</v>
+        <v>-1.256105444862399</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.43934166064853</v>
+        <v>-2.919663472791164</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.529260677277691</v>
+        <v>-2.711578584317095</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.87146685507728</v>
+        <v>-3.421921480780298</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-6.025633818150304</v>
+        <v>-4.912013703989139</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.572427791791853</v>
+        <v>-3.454619037390408</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.438625862184416</v>
+        <v>-5.366700401493965</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-6.208647717854177</v>
+        <v>-5.533376452483438</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.004478</t>
+          <t>X ≈ 0.004484</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9256837502554163</v>
+        <v>-0.6138595651000145</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.777774499806121</v>
+        <v>-3.765697879251363</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.3448097121884</v>
+        <v>2.252954787788845</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.066568861645031</v>
+        <v>3.47109615076748</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5747970323964822</v>
+        <v>0.6553399564134494</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.6807731571100035</v>
+        <v>-1.37270273197295</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.429836308052273</v>
+        <v>0.7450336867290019</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.39355980517535</v>
+        <v>3.715040386612486</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.514853766997113</v>
+        <v>5.660037339387138</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.465441480678152</v>
+        <v>5.232256566645368</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.659973743172493</v>
+        <v>4.777736858250165</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.384577142597777</v>
+        <v>4.141945960889807</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.34261885684603</v>
+        <v>3.755983393539864</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.122098780878318</v>
+        <v>3.871670400381795</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.269871017962608</v>
+        <v>5.234877915971246</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>5.866780515700299</v>
+        <v>5.433283513880042</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.932438086993116</v>
+        <v>3.510415908390812</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.634505478313031</v>
+        <v>5.206626477355343</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.12837519858747</v>
+        <v>4.325079781974651</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>5.315221008555611</v>
+        <v>4.539929801439428</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.967620688964999</v>
+        <v>2.882295586266714</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.808742236581168</v>
+        <v>2.076974552976459</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.083216949063221</v>
+        <v>2.686836074427333</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.729406356489761</v>
+        <v>3.25783233872535</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006361</t>
+          <t>X ≈ 0.006366</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3556843076962224</v>
+        <v>-1.356597997159348</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.779265315509399</v>
+        <v>-3.489232618789231</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.345077050549719</v>
+        <v>-2.844283402336785</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.00051327395483</v>
+        <v>-4.40339680270975</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1250470144476665</v>
+        <v>0.0681663480634711</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.278889845577218</v>
+        <v>-2.625358525948194</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.578717627904744</v>
+        <v>-2.461677356565673</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5165599552216307</v>
+        <v>-0.3915469007974295</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.409636781034429</v>
+        <v>-1.68586672363702</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3077057443351521</v>
+        <v>-0.5753203830566278</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.902334217837357</v>
+        <v>-2.195774169340424</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.56245120711452</v>
+        <v>1.800351088721712</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.296767391697429</v>
+        <v>-2.623517547178778</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.386094484017377</v>
+        <v>-5.237860985345478</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.83721091670111</v>
+        <v>-1.648301657190849</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6263204111046363</v>
+        <v>0.3287392938288747</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.4464507736242211</v>
+        <v>-0.7256682005383865</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.023008801106002</v>
+        <v>-0.8543798430463028</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.215568124406929</v>
+        <v>-2.075947390516376</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.089755178288769</v>
+        <v>-0.9160719959531605</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.2456329260457224</v>
+        <v>0.9036895023081257</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.108754100786861</v>
+        <v>1.782965472887192</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.852712381344027</v>
+        <v>1.548667687171879</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.5705377122548398</v>
+        <v>-1.006324557010487</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.008245</t>
+          <t>X ≈ 0.008248</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>186</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.003709323224115</v>
+        <v>-0.2788811853089186</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2791100028745959</v>
+        <v>0.02299239426688615</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6478067274505008</v>
+        <v>-0.1677780479289979</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.242485631657495</v>
+        <v>-7.153213356170454</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-9.725962758347187</v>
+        <v>-9.545545805858978</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.854388254571724</v>
+        <v>-6.212659806205565</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.563344017669742</v>
+        <v>-6.461543261701813</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.165084949453977</v>
+        <v>-4.10981827295759</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.661423631598154</v>
+        <v>-4.510687476034988</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.226372334269655</v>
+        <v>-2.110222416537709</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.884798768699163</v>
+        <v>-0.769318166608123</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.167164974240066</v>
+        <v>-1.041154545449842</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.450040593188206</v>
+        <v>1.57559543875017</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.295571439626912</v>
+        <v>2.397612471185496</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.039902220847083</v>
+        <v>2.779381748996123</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.4182180960472124</v>
+        <v>0.6773586065258428</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.869901266699806</v>
+        <v>-1.553752405705254</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.657136587353897</v>
+        <v>2.580981080438448</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.410662376880317</v>
+        <v>3.322385319392197</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.3717017352354404</v>
+        <v>0.3259938260559068</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.9044243844737139</v>
+        <v>0.298271391730033</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.366212831666758</v>
+        <v>0.7571014909582132</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.5654187269445146</v>
+        <v>0.9993115052000761</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.640124108129839</v>
+        <v>2.986061099212179</v>
       </c>
     </row>
     <row r="26">
@@ -2262,79 +2262,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.087753247831607</v>
+        <v>-0.9959224491536105</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.250975571552459</v>
+        <v>1.210021430782135</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1864443701484788</v>
+        <v>-0.04467267110944562</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2913412046127348</v>
+        <v>-0.04682360757673365</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.01128609689060767</v>
+        <v>0.3026046223585652</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.27452187060932</v>
+        <v>-1.992312487282931</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.430624974230184</v>
+        <v>-2.157064266758915</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9568808034595406</v>
+        <v>1.170368530153986</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.222270750622194</v>
+        <v>2.516207003574756</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8400996749471759</v>
+        <v>1.121888451931312</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.171220247243355</v>
+        <v>4.433553513155161</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.505919994744445</v>
+        <v>4.771270203274248</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.830563458384127</v>
+        <v>6.094869144657856</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.389775568000196</v>
+        <v>4.644757107654428</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4.342684992048483</v>
+        <v>4.568885576276621</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.778667783537372</v>
+        <v>6.955527859437282</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.267551537497368</v>
+        <v>7.482326436120083</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.322220036130147</v>
+        <v>5.532480151777605</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.084123686993159</v>
+        <v>3.295586028047929</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.49796336199185</v>
+        <v>4.734152939353031</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.795907991571831</v>
+        <v>6.023036749730025</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.106565097647369</v>
+        <v>5.340537365350635</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.381039810129423</v>
+        <v>5.590972168231552</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.918704489421479</v>
+        <v>6.669852417412109</v>
       </c>
     </row>
     <row r="27">
@@ -2344,243 +2344,243 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.746900955898255</v>
+        <v>3.112974692089743</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.904460627887183</v>
+        <v>6.379465743404864</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.965508098940191</v>
+        <v>1.626229367460788</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.259922944849357</v>
+        <v>1.017662286858275</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.790461796647591</v>
+        <v>1.630595328238641</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.514908487593829</v>
+        <v>-1.724868952782323</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.420527847138715</v>
+        <v>-1.626841245879888</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.314921284082573</v>
+        <v>-4.574142545449902</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.524809578547867</v>
+        <v>-2.696942498739553</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.552785163640287</v>
+        <v>-1.734485781621629</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.151195566950406</v>
+        <v>-2.341504873185876</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.815928600461689</v>
+        <v>2.634345121077011</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.690310245154926</v>
+        <v>1.521762272454033</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.336788837279116</v>
+        <v>2.162019392500547</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.06997898392140911</v>
+        <v>-0.2717153952384805</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.224783288287853</v>
+        <v>-1.473920092534698</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8316842821130876</v>
+        <v>-2.454980510708658</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.690910950846522</v>
+        <v>-4.355613627151953</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-4.229405534834505</v>
+        <v>-5.925376580540117</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-5.796945689778752</v>
+        <v>-7.49948188921374</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.953526945464091</v>
+        <v>-2.762327521122288</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.029372906873135</v>
+        <v>-3.189306789272472</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.632091176847226</v>
+        <v>-3.846725752595759</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.9535374651582131</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.0139</t>
+          <t>X ≈ 0.01389</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>104</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.011181686102816</v>
+        <v>5.499376564763793</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8456678250329901</v>
+        <v>1.508782360679163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.244777307024911</v>
+        <v>3.083662865365689</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6100632879192958</v>
+        <v>1.526371896790643</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.237892015904684</v>
+        <v>1.269958375139062</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.381172867331436</v>
+        <v>2.357320437697972</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6565617857133645</v>
+        <v>0.6509545873522029</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5834427257715546</v>
+        <v>-0.6111967784441603</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.459150209017707</v>
+        <v>-2.367098324019082</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.146521349513776</v>
+        <v>-5.031664579739235</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.873374774252241</v>
+        <v>-4.763258488824462</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.280440981010869</v>
+        <v>-2.240897226234082</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.443636114935984</v>
+        <v>-2.413874116055368</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.660149656880506</v>
+        <v>-2.642963559040666</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.359239088430506</v>
+        <v>-2.383202713296207</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.777389277389283</v>
+        <v>-1.839534526753098</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.9497679528282887</v>
+        <v>-0.4109792451138361</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.054608656649442</v>
+        <v>-0.5221986604592814</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.122821185813315</v>
+        <v>0.6175627483519648</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.271205457319802</v>
+        <v>1.765536681663896</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.7286592893537716</v>
+        <v>1.196889884809934</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.614351789483138</v>
+        <v>2.07828375982556</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>2.322990022510396</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.8514557872034487</v>
+        <v>1.197392778285788</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01578</t>
+          <t>X ≈ 0.01577</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.790857114098685</v>
+        <v>-4.824408445132036</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.278844126462687</v>
+        <v>-3.262881755572245</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.823639524686214</v>
+        <v>4.918278448028779</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.250561496976204</v>
+        <v>-1.261398124849393</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8814354687253143</v>
+        <v>-1.605695347565039</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.975195441075094</v>
+        <v>0.4824021324060652</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2697845263693708</v>
+        <v>-0.4226624120127553</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.898366867868695</v>
+        <v>-0.6725915893283769</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.840397967017736</v>
+        <v>-6.214423952853799</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.639982087617142</v>
+        <v>-7.065466714166185</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.132840239974847</v>
+        <v>-10.559324731845</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.371586976578456</v>
+        <v>-10.7396719706534</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-7.501416154575331</v>
+        <v>-11.85456408810418</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.982245681065166</v>
+        <v>-8.391696383347238</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-4.640388978645724</v>
+        <v>-9.073850765232294</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.979130931961123</v>
+        <v>-5.446495245994846</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.113048068938596</v>
+        <v>-5.579126747478867</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.217888772759778</v>
+        <v>-4.546224942334106</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.8847950609947404</v>
+        <v>-1.248699910045367</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.732018229453331</v>
+        <v>4.617438662500184</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>8.076264514317494</v>
+        <v>5.966730484552755</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.1136261000782</v>
+        <v>3.985213447547309</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.501308359730004</v>
+        <v>2.324297825959576</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>10.08585346499735</v>
+        <v>7.928162009054979</v>
       </c>
     </row>
     <row r="30">
@@ -2590,79 +2590,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.621239270294716</v>
+        <v>-1.142125861225615</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>10.73025844115936</v>
+        <v>14.40603395689445</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.409886450951902</v>
+        <v>5.289270889485657</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.224636195941727</v>
+        <v>0.7891437821819522</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.4003576452364257</v>
+        <v>2.38586458640934</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.373460482391714</v>
+        <v>0.6472096738175139</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1846248525565457</v>
+        <v>1.654477883122041</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.423620611035105</v>
+        <v>-0.5460310788763678</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.539435198330636</v>
+        <v>3.489622739303165</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.688088149745063</v>
+        <v>6.577986578316157</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9202051492694849</v>
+        <v>0.860431571730004</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.722614074733499</v>
+        <v>2.735843452743197</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3613323058480447</v>
+        <v>-2.35670229599252</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.503979809745651</v>
+        <v>-6.652518711499987</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-3.201338793600748</v>
+        <v>-5.345846277742595</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-2.702477146227835</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.780084694909732</v>
+        <v>-2.899595855005508</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>4.782969856823883</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.252534609644385</v>
+        <v>1.136326324000485</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.439380419612412</v>
+        <v>0.7482938507017565</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.9360499379208918</v>
+        <v>-0.5915955970369282</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.8602039765118192</v>
+        <v>-2.661803054624976</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.134678688993901</v>
+        <v>-0.4662996012910554</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>3.019630749496038</v>
+        <v>2.620469701362751</v>
       </c>
     </row>
     <row r="31">
@@ -2675,322 +2675,322 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>26.35915288656803</v>
+        <v>26.34021001925125</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>17.45294751678969</v>
+        <v>17.57075968793687</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>16.0149284677587</v>
+        <v>16.31606558604529</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.30197444831592</v>
+        <v>15.71978380933506</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.9661839757686</v>
+        <v>15.4597439808435</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.2960073047232</v>
+        <v>12.76773726583425</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.38120147797567</v>
+        <v>14.83711388621661</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.674418604651166</v>
+        <v>3.171348359895759</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.430191500851578</v>
+        <v>8.977760022085043</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.3224370792351579</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.074192609834157</v>
+        <v>5.639919421579975</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.3423023307099413</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.672281139530043</v>
+        <v>4.225167882246339</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>12.02263083451199</v>
+        <v>12.50823647222766</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.507344679788609</v>
+        <v>8.984900925139094</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>1.014902292544292</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.110671607611266</v>
+        <v>6.601143367030282</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>11.72011661807576</v>
+        <v>12.15062159227566</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>14.79315085614299</v>
+        <v>15.19074667301732</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>12.12285380896816</v>
+        <v>12.54087448546116</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>11.58030764100213</v>
+        <v>11.97342998408043</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>11.50446167959303</v>
+        <v>11.90602661792908</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.77893639207508</v>
+        <v>12.21118012422361</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.988818424566169</v>
+        <v>6.334755415648509</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02143</t>
+          <t>X ≈ 0.02142</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>17.78772431513946</v>
+        <v>17.77904130691957</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.31009037393251</v>
+        <v>10.45185368303834</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.44349989633009</v>
+        <v>12.73779997523541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.587688734030195</v>
+        <v>5.058130398211588</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.823326832911548</v>
+        <v>8.347159012354069</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.010293019008884</v>
+        <v>8.492119438275559</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.80977290654705</v>
+        <v>11.27359736036141</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.9601328903655</v>
+        <v>7.434023112902452</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.001620072280161</v>
+        <v>7.555965432548184</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.800132967672241</v>
+        <v>10.33048728160909</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.64562118126278</v>
+        <v>14.15533587037874</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9188425078994982</v>
+        <v>-0.319727200677022</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.042004574755616</v>
+        <v>-1.434619318127794</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.879773691654933</v>
+        <v>5.410400588692987</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.221630394074374</v>
+        <v>4.728246206807931</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.387445887445892</v>
+        <v>8.818217439639653</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>8.253528750468419</v>
+        <v>8.726310207991197</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.148688046647337</v>
+        <v>8.593426102829596</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.364579427571506</v>
+        <v>8.783941969822109</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.162860476746133</v>
+        <v>-1.659312307614755</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.8660219267164067</v>
+        <v>1.313883585093222</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.352681177549876</v>
+        <v>-5.830586544962891</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.506777893639253</v>
+        <v>-2.074534161490725</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.9888184245660412</v>
+        <v>1.334755415648381</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02331</t>
+          <t>X ≈ 0.0233</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.995516522931666</v>
+        <v>11.42602530950692</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>9.660739724581852</v>
+        <v>11.12787186983233</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.192417645247836</v>
+        <v>6.868998039623101</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.50976665610812</v>
+        <v>9.28077556913253</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.113370122954791</v>
+        <v>2.866241462471045</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.30033630905217</v>
+        <v>3.075421672439845</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.558690655464893</v>
+        <v>5.180026180583319</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.250176180408701</v>
+        <v>1.792556102900953</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.738639667979591</v>
+        <v>-1.083694715732598</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.511555344016081</v>
+        <v>-1.984239418893438</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2071926715511623</v>
+        <v>1.292175324028555</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.516245105302197</v>
+        <v>-1.962463056775064</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.639407172158315</v>
+        <v>-3.077355174225836</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.860486048604905</v>
+        <v>-3.325589235658946</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-2.488326315882404</v>
+        <v>-0.9774405872409488</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-7.954545454545453</v>
+        <v>-6.398372723071198</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-5.058159561219881</v>
+        <v>-3.524196708463911</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.132697234738067</v>
+        <v>-3.657080813625512</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.947108884116709</v>
+        <v>-6.368428408841318</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.760263074148732</v>
+        <v>-6.075472057826211</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.7577968184913075</v>
+        <v>-0.5561871966155465</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.6819508570822066</v>
+        <v>2.294460103790733</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.9564255695643027</v>
+        <v>1.388669301712831</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-4.834075753182745</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0252</t>
+          <t>X ≈ 0.02518</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>4.790706605222795</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.94745301129515</v>
+        <v>21.21146643618559</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.124818577648711</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.41186455820597</v>
+        <v>2.697703468819064</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.61623360664894</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-2.429267420551561</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.491091587865839</v>
+        <v>1.783996922485095</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.212880143112649</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.254367325027353</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.17375934129861</v>
+        <v>9.144287226874638</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.44781898346053</v>
+        <v>17.74985557481224</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.476761887704846</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.353599820848729</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.824828636709825</v>
+        <v>16.11014744145707</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.474377646821523</v>
+        <v>7.094659726238611</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.068764568764571</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.627155124094728</v>
+        <v>15.88541666666661</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.522314420273545</v>
+        <v>15.75253256150501</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.738205801197928</v>
+        <v>15.96699478865084</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>7.280803398995815</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>9.306659481790767</v>
+        <v>15.5389742103738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>17.27344188658053</v>
+        <v>24.11594202898552</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>9.505301941049545</v>
+        <v>15.62046970136272</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1723 +3180,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02848</t>
+          <t>X &gt; -0.02845</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3349</v>
+        <v>3373</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02281627120183316</v>
+        <v>-0.0090578235169545</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.07361963612684974</v>
+        <v>0.1142646688806721</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.07239667001159233</v>
+        <v>-0.03438853783332974</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02686412184054632</v>
+        <v>0.008343020837926929</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.138159424299225</v>
+        <v>-0.07392385367020893</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3205653118494567</v>
+        <v>-0.2838916737555977</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3034602655095995</v>
+        <v>-0.3251476202877726</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2676319154082734</v>
+        <v>-0.2888983414212234</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2983629411392457</v>
+        <v>-0.2918533282799558</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1325376920278671</v>
+        <v>-0.1559784950031897</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2576676774098274</v>
+        <v>-0.2802684653531387</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2812771574511359</v>
+        <v>-0.3036835436176943</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.256290289041381</v>
+        <v>-0.2787343363533239</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.251430323145442</v>
+        <v>-0.2732400844075471</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1474668576911782</v>
+        <v>-0.1692866565722895</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2203672109838379</v>
+        <v>-0.211531078958231</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1280479564956565</v>
+        <v>-0.1205004930966496</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.0363236629546364</v>
+        <v>0.0008308746154526148</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1007924098933017</v>
+        <v>-0.003993962089239744</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1348258808618468</v>
+        <v>-0.008824451809871903</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.09289385916834192</v>
+        <v>0.03356801194993864</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.0912240432189293</v>
+        <v>0.0649001362997268</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1869484693321652</v>
+        <v>-0.059122187572477</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2450253667575453</v>
+        <v>-0.1444280158030082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.0266</t>
+          <t>X &gt; -0.02657</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3335</v>
+        <v>3360</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1113863588729771</v>
+        <v>0.1079792429210329</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1798720667704998</v>
+        <v>0.2031873114072908</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.009479804383893509</v>
+        <v>0.0292361024098966</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.001410691134800857</v>
+        <v>0.01525770945023197</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1117613347348083</v>
+        <v>-0.06626347072784</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3255256508390261</v>
+        <v>-0.3072443334882351</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3349594494024331</v>
+        <v>-0.3456052885503453</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2978284857695996</v>
+        <v>-0.3080483234511746</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3288703328371128</v>
+        <v>-0.3115131297579339</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2188492445019676</v>
+        <v>-0.2313302400292017</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3158056833899394</v>
+        <v>-0.3275236128545203</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3383653215066147</v>
+        <v>-0.3499766762189509</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2787051127114424</v>
+        <v>-0.290980704170039</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3028015806064914</v>
+        <v>-0.3141849027565868</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1657585327882813</v>
+        <v>-0.1775278665188225</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2414588602144647</v>
+        <v>-0.2517955581878937</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1481981880628354</v>
+        <v>-0.1303243490743498</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05565624719122297</v>
+        <v>-0.008014081394520645</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.09136582478087263</v>
+        <v>-0.0136887180356382</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1263225911516415</v>
+        <v>-0.01937001480385447</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.111894704285902</v>
+        <v>0.02537669664665998</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1099053737911078</v>
+        <v>0.05711817230123017</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1772129741462294</v>
+        <v>-0.03857547572538778</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2352124171559069</v>
+        <v>-0.123577917684905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02471</t>
+          <t>X &gt; -0.02469</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3320</v>
+        <v>3344</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.173092461799861</v>
+        <v>0.1550269695431012</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2733288111386258</v>
+        <v>0.2815793298278422</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1685180688190755</v>
+        <v>0.1722255289447716</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1608281694450824</v>
+        <v>0.190767281740186</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.0215897858914289</v>
+        <v>0.08048609589189937</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2238934057107969</v>
+        <v>-0.2218332207452036</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2598362376799628</v>
+        <v>-0.2863194516099199</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2212648485862445</v>
+        <v>-0.2471139971140062</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2226249480668159</v>
+        <v>-0.2214157683298268</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1685875739337277</v>
+        <v>-0.1965902795776771</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2371956718511541</v>
+        <v>-0.2647407909905581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2885904070592176</v>
+        <v>-0.3157609446173382</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2235888265890935</v>
+        <v>-0.2213502407759975</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3068414949603095</v>
+        <v>-0.3030904834087664</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1361776134783454</v>
+        <v>-0.1326988581136419</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1848412004661952</v>
+        <v>-0.1801539955940115</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1205963729804225</v>
+        <v>-0.08742726051925587</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.05722209852929439</v>
+        <v>0.006263904788639252</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.06399200099986757</v>
+        <v>0.02940147721459141</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.099941446318077</v>
+        <v>-0.007188180866045002</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.08299144330207042</v>
+        <v>0.07036619154629875</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1107443064738831</v>
+        <v>0.07274587803668453</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.2097073038856863</v>
+        <v>-0.05446155845842782</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2676359644184245</v>
+        <v>-0.1390996766277155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02283</t>
+          <t>X &gt; -0.0228</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3291</v>
+        <v>3316</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1310297725064729</v>
+        <v>0.1261363746147737</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1746930215113025</v>
+        <v>0.1958882456522772</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.0513328845978549</v>
+        <v>0.06615201664336468</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.01958242173784441</v>
+        <v>0.02983776138501071</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03308082514282518</v>
+        <v>0.07082099088864879</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2766300911236641</v>
+        <v>-0.265352179059434</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3061365769560922</v>
+        <v>-0.3237138485920141</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2648012320588435</v>
+        <v>-0.2816278026362085</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2060542860294063</v>
+        <v>-0.1967572450831128</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1750129151892281</v>
+        <v>-0.1950521124647651</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.216364290892237</v>
+        <v>-0.2360260713277356</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2657565687100742</v>
+        <v>-0.2851398411975126</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1600282833305613</v>
+        <v>-0.1805424526253105</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2723447140230491</v>
+        <v>-0.2909349397816641</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.09438692194298426</v>
+        <v>-0.1133603238866314</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1486906041316445</v>
+        <v>-0.1659375786480339</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.0826923359042766</v>
+        <v>-0.07154992978232855</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.01782696700153963</v>
+        <v>0.02405574031301683</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.05688381792081287</v>
+        <v>0.01547416233346155</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.09479197468672851</v>
+        <v>0.006882438529103752</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.07291466795788892</v>
+        <v>0.05975288177169347</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1306083824433273</v>
+        <v>0.03264509644974822</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2328671142606211</v>
+        <v>-0.0977048406758243</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3210309481820985</v>
+        <v>-0.2118584047892753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02095</t>
+          <t>X &gt; -0.02092</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3259</v>
+        <v>3283</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1842062239651696</v>
+        <v>0.1778814388585488</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2621809662669961</v>
+        <v>0.2810579641734279</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1215811928926271</v>
+        <v>0.1323171284828106</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1882291332283188</v>
+        <v>0.1924052550739788</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1442649731966057</v>
+        <v>0.1760318621338257</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2485674369830946</v>
+        <v>-0.2559205603846806</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2402881435139506</v>
+        <v>-0.2766091381209677</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2263447541274601</v>
+        <v>-0.2613499127594352</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1368736880828791</v>
+        <v>-0.1162612374775449</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.128503931633773</v>
+        <v>-0.1368774683028633</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2034881446192145</v>
+        <v>-0.2113094737314469</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2812043893687388</v>
+        <v>-0.2884866224511669</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1328739500287099</v>
+        <v>-0.1413149148390289</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2135270119241994</v>
+        <v>-0.2199466976258435</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.05796394059957066</v>
+        <v>-0.06410900604159764</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.08800122436485935</v>
+        <v>-0.09244099514220494</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.02002561922802926</v>
+        <v>0.003957700101310024</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.04652221860085604</v>
+        <v>0.1018788673731095</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.004985590036547194</v>
+        <v>0.09108237989171641</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.06575439557629892</v>
+        <v>0.04985017195137686</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.03833123085562562</v>
+        <v>0.1089632691519711</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.09583621325316471</v>
+        <v>0.08235320580759264</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2017822757601522</v>
+        <v>-0.05173966001164843</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2900576548623093</v>
+        <v>-0.1653968840774311</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01906</t>
+          <t>X &gt; -0.01904</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3229</v>
+        <v>3252</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1437682711834185</v>
+        <v>0.1367625848665028</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2089914728336026</v>
+        <v>0.2126881832838805</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2034699970204059</v>
+        <v>0.1966134586447055</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1849793744242874</v>
+        <v>0.1712161012558937</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1437104837540346</v>
+        <v>0.1878642729773503</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2852765177063361</v>
+        <v>-0.2802482824075696</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1773761120252075</v>
+        <v>-0.2018295280094478</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.160712366073021</v>
+        <v>-0.1835102202299339</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02170110099250167</v>
+        <v>0.05359247171130477</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.02432410470343171</v>
+        <v>-0.02084851511359176</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.009970605112521014</v>
+        <v>-0.006652847852386401</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1166209713367579</v>
+        <v>-0.1125106933845501</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.01819505094614726</v>
+        <v>-0.01458815693207072</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.09751206673615798</v>
+        <v>-0.09156929674036007</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.09650906697647343</v>
+        <v>0.1029393950519264</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.02983963827337277</v>
+        <v>0.03837683299290262</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.09972334697203422</v>
+        <v>0.1367207476731025</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1369856840947961</v>
+        <v>0.2061851090802591</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.06216755373110772</v>
+        <v>0.162573542104937</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.07280701026209613</v>
+        <v>0.05750260963120013</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.009154876678209689</v>
+        <v>0.1533072392415278</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.06648053201770665</v>
+        <v>0.1271733498943917</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.175950825970034</v>
+        <v>-0.01050535291837917</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3262724925688048</v>
+        <v>-0.1851883552178464</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01718</t>
+          <t>X &gt; -0.01716</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3194</v>
+        <v>3216</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2172736084099753</v>
+        <v>0.2085310366316122</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1625217011615945</v>
+        <v>0.1645238790515009</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.093513230848707</v>
+        <v>0.1004238634876415</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.05142978600654402</v>
+        <v>0.01949992534976275</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.04446186226571314</v>
+        <v>0.0702648547372462</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3601037075522271</v>
+        <v>-0.3429989873601116</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2426362227851087</v>
+        <v>-0.2548730641114645</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.191625009055997</v>
+        <v>-0.2020291314845863</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.00768411683083059</v>
+        <v>0.03628424979431344</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.01655619531741337</v>
+        <v>0.03180012677137967</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.05926989612753175</v>
+        <v>0.07410456830868384</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1078630943000576</v>
+        <v>-0.09178214174083621</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.003905833089213218</v>
+        <v>0.01967682362150924</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.07385570017675747</v>
+        <v>-0.05538262673884731</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.03582244616834629</v>
+        <v>0.05590003631619567</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.02436923892264531</v>
+        <v>0.04636903868944131</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.06523937661203405</v>
+        <v>0.1159472282552443</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1352951895043688</v>
+        <v>0.2187026422002845</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.08855567014736465</v>
+        <v>0.2032568190761737</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.01866321059764431</v>
+        <v>0.1256806125918075</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.08292169882418676</v>
+        <v>0.2599894816301074</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.05711678418805377</v>
+        <v>0.2655124328722493</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.05652079549478373</v>
+        <v>0.1236096281980323</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.1763126247227547</v>
+        <v>-0.0200775623188747</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.0153</t>
+          <t>X &gt; -0.01528</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3142</v>
+        <v>3159</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2369623199330206</v>
+        <v>0.2140535611066312</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2820525681169173</v>
+        <v>0.2366236688899335</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2052237691650731</v>
+        <v>0.1628119693993284</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.001240854899386079</v>
+        <v>-0.02065660248218393</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.04283571908705142</v>
+        <v>0.09888122131465593</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.434965426249569</v>
+        <v>-0.3875562557134202</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3025947764348942</v>
+        <v>-0.283593337800383</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2460755353551747</v>
+        <v>-0.2558316574064747</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.06698309962036575</v>
+        <v>0.1419770333730526</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1363340091030665</v>
+        <v>0.1832619090890972</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1751981356970091</v>
+        <v>0.253008159932044</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.08516936214267901</v>
+        <v>-0.005439719299545231</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1742753382247528</v>
+        <v>0.2227348151930144</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.06724252241156137</v>
+        <v>0.08774289743686836</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.3168684893124194</v>
+        <v>0.3396092211881765</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2000394545646955</v>
+        <v>0.2251669868223658</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2439081296660888</v>
+        <v>0.2979245630659122</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2534136356435539</v>
+        <v>0.3417900654545107</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2022871743702197</v>
+        <v>0.3222413120389547</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.09014883508670835</v>
+        <v>0.2394376990907858</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.170820181896346</v>
+        <v>0.3548071940621682</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.1903940678154967</v>
+        <v>0.4250862002504263</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1021944258008176</v>
+        <v>0.3079251513483783</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.04537930480616126</v>
+        <v>0.2279404199445523</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01341</t>
+          <t>X &gt; -0.01339</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3076</v>
+        <v>3092</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4341852280945488</v>
+        <v>0.4419491073649837</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2287745358249467</v>
+        <v>0.1812510713510704</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3108072332363818</v>
+        <v>0.2766051854672114</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01404846796572912</v>
+        <v>-0.05864497219668863</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1352839572877684</v>
+        <v>0.1801009699926297</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2275558074557296</v>
+        <v>-0.1915534339852911</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1909663283447856</v>
+        <v>-0.1646468000409058</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.03449624942631857</v>
+        <v>0.03120003120002934</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2887213205464505</v>
+        <v>0.3705500728073616</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3437670609987933</v>
+        <v>0.3977750998086833</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3452880946602122</v>
+        <v>0.4310149951020961</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.02058088050343088</v>
+        <v>0.1085828986914592</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1476074982005429</v>
+        <v>0.2046592985717766</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.04300592133768077</v>
+        <v>0.07210746724688022</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.3444764196440815</v>
+        <v>0.3763968003008031</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.2124308279027716</v>
+        <v>0.2473615945206973</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1952178206454747</v>
+        <v>0.2594082768635033</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.2720709928149887</v>
+        <v>0.3716416641519373</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2476963106884398</v>
+        <v>0.3793293059256158</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1941199900102433</v>
+        <v>0.3547078486969042</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2232111961863907</v>
+        <v>0.4202756660932181</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.3098083796765678</v>
+        <v>0.5583665827073503</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1488700008777144</v>
+        <v>0.3687709976243667</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.1249878468213339</v>
+        <v>0.3229276573782371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01153</t>
+          <t>X &gt; -0.01151</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2997</v>
+        <v>3012</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5092192876304438</v>
+        <v>0.4989437106884793</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2740440829061299</v>
+        <v>0.2200444632393115</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3300489382576046</v>
+        <v>0.2850468311596757</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.01550129331685923</v>
+        <v>-0.04341607368616707</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1445182576885884</v>
+        <v>0.1759119623939824</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1333229931330351</v>
+        <v>-0.1106900421798755</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.07525839681089508</v>
+        <v>-0.06204687634840411</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2964710789122051</v>
+        <v>0.279164546007344</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.371169818448962</v>
+        <v>0.4590040673202154</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3815283165094385</v>
+        <v>0.4419298794412185</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2762056184274257</v>
+        <v>0.3696902855560467</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.04973156565031189</v>
+        <v>0.04602494309227012</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1101166661583903</v>
+        <v>0.1741274506242192</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.008563730624565835</v>
+        <v>0.04462791796269272</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2354169403067914</v>
+        <v>0.2757255984664155</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.05094217810596291</v>
+        <v>0.0952573432923316</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.003445500385168998</v>
+        <v>0.0772020260571864</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.2182607124890481</v>
+        <v>0.3284106264487292</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2208654274763475</v>
+        <v>0.3637465287900454</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1609490470633972</v>
+        <v>0.3327748676620814</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.2384317776190983</v>
+        <v>0.4482992530587708</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.2959636088075257</v>
+        <v>0.5588813105728647</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.1569026552981754</v>
+        <v>0.3909724527049505</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.1677592701736046</v>
+        <v>0.3814258766615239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009647</t>
+          <t>X &gt; -0.00963</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2896</v>
+        <v>2908</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2766786597639097</v>
+        <v>0.2509481180958275</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.02373387741751998</v>
+        <v>-0.09748776750551258</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.01591030379204028</v>
+        <v>-0.05348057069578971</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3534011039668528</v>
+        <v>-0.4066483197432547</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2768204424935092</v>
+        <v>-0.2379139102868777</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.364768345743208</v>
+        <v>-0.3543911040153844</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.380703283929094</v>
+        <v>-0.3783962399080636</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.02066561673075284</v>
+        <v>-0.04851130022129269</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.01355450906836353</v>
+        <v>0.06464023880049297</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.07901814256553052</v>
+        <v>-0.0275129100179683</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.06021202921443347</v>
+        <v>0.02476142897177169</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4223328235027353</v>
+        <v>-0.3349455577412499</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.389680994721239</v>
+        <v>-0.3339788945061883</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4183372882742802</v>
+        <v>-0.3908806599822725</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1949829615676251</v>
+        <v>-0.1616538379254209</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2346866319988337</v>
+        <v>-0.1972598489059934</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3137140722035667</v>
+        <v>-0.2466588050314513</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.2256961898059657</v>
+        <v>-0.1191215222286388</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.1962543574774784</v>
+        <v>-0.0560055546378706</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2995064394790461</v>
+        <v>-0.1302319531033618</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2003521548457954</v>
+        <v>0.0095335031981989</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1726427141147511</v>
+        <v>0.09223881518479971</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2778711428132326</v>
+        <v>-0.05616751610444481</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2296109361284664</v>
+        <v>-0.02602273330028027</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007764</t>
+          <t>X &gt; -0.007748</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2787</v>
+        <v>2796</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3620120717002706</v>
+        <v>0.3663995689753961</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.008504540802512395</v>
+        <v>-0.05719028023237627</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3762069319677934</v>
+        <v>0.3227993421120061</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2295276450160557</v>
+        <v>-0.269602856696217</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.006518908884132202</v>
+        <v>0.02342464641694875</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3068723031600129</v>
+        <v>-0.2816175826951266</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1853256332262063</v>
+        <v>-0.1682486042360765</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.02157627358215564</v>
+        <v>0.009185535501316622</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.06306345549685943</v>
+        <v>0.157343346782632</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.06173116918459698</v>
+        <v>0.1288661118093373</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.08543315755539282</v>
+        <v>0.208025742131575</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.08602010855354081</v>
+        <v>0.05874370581102539</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2582069770045834</v>
+        <v>-0.1450028932623013</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4224044451689224</v>
+        <v>-0.336752059612067</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.2359421086109634</v>
+        <v>-0.1424169226026848</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1573760527915198</v>
+        <v>-0.05920506140860482</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.3058713621384328</v>
+        <v>-0.1777299619455377</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1744046312841476</v>
+        <v>-0.004069865332908762</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.1522981014967186</v>
+        <v>0.05303548840092276</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2669801734052868</v>
+        <v>-0.03270448057589448</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.17836784210823</v>
+        <v>0.09966727895288585</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.07480942605052121</v>
+        <v>0.260203659980661</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.2309052194888181</v>
+        <v>0.06040633598109935</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1273330952452767</v>
+        <v>0.169825924538678</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00588</t>
+          <t>X &gt; -0.005866</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2642</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5478321318510524</v>
+        <v>0.5378546558683439</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01335976083838375</v>
+        <v>0.02869095668196309</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3976777939042151</v>
+        <v>0.4287542823947419</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3152762255385255</v>
+        <v>-0.3140804098320658</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3114440565763701</v>
+        <v>-0.2511654397395944</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7659873044412535</v>
+        <v>-0.6959618074158271</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3681246675768932</v>
+        <v>-0.3251919956545635</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.231241772707321</v>
+        <v>-0.1574923696819894</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3406979870190341</v>
+        <v>-0.1964069810800879</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3588966819234471</v>
+        <v>-0.2181625723222069</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3867238322143578</v>
+        <v>-0.2256623159598874</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5145298394359372</v>
+        <v>-0.3300421294706624</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6565598308203562</v>
+        <v>-0.481045560811296</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8177941236932256</v>
+        <v>-0.6696413971552957</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5097032269873907</v>
+        <v>-0.3490721988210552</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.4594967430252623</v>
+        <v>-0.3691934876460579</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.6466980069012038</v>
+        <v>-0.4886867685919256</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.5024056611572547</v>
+        <v>-0.372845081999472</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.4910505702672125</v>
+        <v>-0.3250339230983172</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.7359105821458414</v>
+        <v>-0.5417747753604658</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6885363083868654</v>
+        <v>-0.4444644018864139</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6886820426952838</v>
+        <v>-0.3838699651178743</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.90625880636766</v>
+        <v>-0.6097484742305284</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.7549903782888876</v>
+        <v>-0.4847536143072304</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003997</t>
+          <t>X &gt; -0.003984</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2447</v>
+        <v>2443</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8601712165069344</v>
+        <v>0.7663163613202997</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1263367427390136</v>
+        <v>-0.1706473849526873</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.675970073810447</v>
+        <v>0.6884796513671247</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1184503407443103</v>
+        <v>-0.147824986465487</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3727744181795671</v>
+        <v>-0.3014319070526241</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8375393929783144</v>
+        <v>-0.794904805119593</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1838261624083799</v>
+        <v>-0.1265721832059654</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4213044096054475</v>
+        <v>-0.408547216192602</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5427500179147842</v>
+        <v>-0.4203881561268616</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.460268545275099</v>
+        <v>-0.3388222562349057</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2676752982251926</v>
+        <v>-0.124737259063977</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5464247016731889</v>
+        <v>-0.4595166036916467</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7734564222971372</v>
+        <v>-0.6546584319101498</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8484833813454671</v>
+        <v>-0.7569540669000503</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5451275116970393</v>
+        <v>-0.477390300950006</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.1711651589302505</v>
+        <v>-0.1367739130404004</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.4440873828882346</v>
+        <v>-0.3798894557823118</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.1982507288629662</v>
+        <v>-0.1621264830029006</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3663894810208674</v>
+        <v>-0.2911751459896834</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8498352666620903</v>
+        <v>-0.7473112877450205</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7963635015047288</v>
+        <v>-0.6368853445310947</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.8722094629138297</v>
+        <v>-0.6471198591558505</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.006398420231534</v>
+        <v>-0.8295025973101815</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.959631572514887</v>
+        <v>-0.7630751205775184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002114</t>
+          <t>X &gt; -0.002102</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6244498941607048</v>
+        <v>0.5645161290322562</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.02296647542627284</v>
+        <v>-0.03853356381446815</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8614798618759352</v>
+        <v>0.8496294771510975</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1194509329129545</v>
+        <v>-0.189201293085695</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2319274260051074</v>
+        <v>-0.2415451474707524</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8935543618371611</v>
+        <v>-0.8881829700440917</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.01297959775967428</v>
+        <v>0.01316358915176608</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.2018654507307005</v>
+        <v>-0.202471139971145</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2497038605980464</v>
+        <v>-0.1638279445727449</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1293636188140823</v>
+        <v>-0.02237943979209689</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1893588192388691</v>
+        <v>0.3201994783406121</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.08939058420912716</v>
+        <v>-0.02002396679041851</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2746339373537694</v>
+        <v>-0.1704517559386147</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3800245976340193</v>
+        <v>-0.3478132025500855</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.02832171014689067</v>
+        <v>-0.01943423349286633</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.324578522252942</v>
+        <v>0.3447133720353648</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.1279295174866348</v>
+        <v>0.177848372891475</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1393518143924624</v>
+        <v>0.1611347120427027</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.06578331313601637</v>
+        <v>-0.001180917310612983</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6850279644308657</v>
+        <v>-0.5672976900569964</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7980845760997681</v>
+        <v>-0.6151140527763417</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7843248027418426</v>
+        <v>-0.5292484108111211</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.5546529576433059</v>
+        <v>-0.3489584350168897</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3616680065655089</v>
+        <v>-0.125262553803509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002304</t>
+          <t>X &gt; -0.0002203</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7619868946651991</v>
+        <v>0.7677180994756085</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3825065028748966</v>
+        <v>-0.2895477625974294</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4568023833167842</v>
+        <v>0.4841557014339131</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5597953608223065</v>
+        <v>-0.5646359497069753</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6425493961226252</v>
+        <v>-0.5866443940659352</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.214692521766139</v>
+        <v>-1.190359875288948</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4178152947253153</v>
+        <v>-0.4134337739314091</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.139346577535072</v>
+        <v>-0.2112548258592923</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.04725210817098002</v>
+        <v>-0.03261597702712038</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3944071145779589</v>
+        <v>0.388371067307304</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6684667567398819</v>
+        <v>0.6606060819116379</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7439683654376381</v>
+        <v>0.6882837623287799</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5317374726705921</v>
+        <v>0.46543376062737</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2396290261937679</v>
+        <v>0.1456804363809212</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.5742139807004705</v>
+        <v>0.4584653805471248</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7431768265523999</v>
+        <v>0.5929556149770434</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6905035403843769</v>
+        <v>0.5702158532452088</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.9714031296362862</v>
+        <v>0.823743141362641</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6089594130682983</v>
+        <v>0.5089795214752613</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1179003607200286</v>
+        <v>-0.1626142856384476</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3051165794474713</v>
+        <v>-0.2416961764839556</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.1779168555773865</v>
+        <v>-0.08284026465168637</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.2587720923339134</v>
+        <v>-0.1658869698246264</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.08079723895820479</v>
+        <v>0.00822480340353593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001653</t>
+          <t>X &gt; 0.001662</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.149572048244686</v>
+        <v>1.150514066113232</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.02352810339854017</v>
+        <v>0.06224862631790273</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.873782188887823</v>
+        <v>0.9134510346549618</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.0786927886387403</v>
+        <v>-0.03996199447816906</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6540042192698579</v>
+        <v>-0.556194021460783</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.664642823591635</v>
+        <v>-1.66279832159988</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5204238428113328</v>
+        <v>-0.5324892387664093</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.0201921737919406</v>
+        <v>-0.115388021525213</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2608159662065859</v>
+        <v>0.3133832467629887</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7453853201102163</v>
+        <v>0.7808696576808316</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7200437646673521</v>
+        <v>0.7522623136810722</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.099976995949888</v>
+        <v>1.077365076417962</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.9947790009500679</v>
+        <v>0.9610305095126961</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9533408430663428</v>
+        <v>0.8332058400121483</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.230104244968793</v>
+        <v>1.090643661981652</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.261717898408548</v>
+        <v>1.146017994606261</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.224220326438939</v>
+        <v>1.078420285484519</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.696107014234272</v>
+        <v>1.525012947745253</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.071662260704812</v>
+        <v>0.9307629045928678</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5382199554267402</v>
+        <v>0.5169286657339853</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4158418546876064</v>
+        <v>0.5294934433327185</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.640115941297708</v>
+        <v>0.7930576949473078</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.4343985769490288</v>
+        <v>0.6494367828192438</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5986623621411198</v>
+        <v>0.7658361459417549</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003536</t>
+          <t>X &gt; 0.003544</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1339</v>
+        <v>1326</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.087373288652913</v>
+        <v>1.247792433566055</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8270566541154594</v>
+        <v>0.9270352984609858</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.473922191830567</v>
+        <v>1.618448981000533</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.281474120985223</v>
+        <v>-0.09670770882565449</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.09604344684597521</v>
+        <v>0.07683594748220202</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9515195541216386</v>
+        <v>-0.9638352369388699</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3087251255771477</v>
+        <v>-0.2619112611476453</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7533463782922638</v>
+        <v>0.7056233852640972</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.018214051644051</v>
+        <v>1.058103193151794</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.362200832792972</v>
+        <v>1.309955889549222</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.487340147330173</v>
+        <v>1.507340604752358</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.102112709630497</v>
+        <v>2.054111943694238</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.574631953273268</v>
+        <v>1.463171922051856</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.502473404451401</v>
+        <v>1.364638459421137</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.081966779000879</v>
+        <v>1.92612040039598</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.424411904277669</v>
+        <v>2.158712370745498</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.963550072430031</v>
+        <v>1.650607964491122</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.950245712282566</v>
+        <v>2.614394423366932</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.19526330679912</v>
+        <v>1.823493661678633</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.859330924086045</v>
+        <v>1.482333113409062</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.988928146710009</v>
+        <v>1.863196175519455</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.913082185300908</v>
+        <v>1.834154933265367</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.112874298828515</v>
+        <v>2.123980210346978</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.261089842468579</v>
+        <v>2.309760802418523</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.00542</t>
+          <t>X &gt; 0.005425</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.612436188631825</v>
+        <v>1.730442951738745</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.028128433433984</v>
+        <v>2.143669826016037</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.246769797160958</v>
+        <v>1.453947475536893</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.154739569373717</v>
+        <v>-1.021693894646091</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2710178467990403</v>
+        <v>-0.07314657335182773</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.022137964641615</v>
+        <v>-0.8578325530411419</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.7621917141980106</v>
+        <v>-0.5229710624489954</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1961254854051191</v>
+        <v>-0.07459583730770447</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1546383034904153</v>
+        <v>-0.1349908447610702</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2919582155950451</v>
+        <v>0.2930631214131836</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6598264881509692</v>
+        <v>0.6594600945862581</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.506780649430929</v>
+        <v>1.512821642939826</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8526617345447889</v>
+        <v>0.8687393183327359</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8192001188861866</v>
+        <v>0.7146672154683671</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.250470098970375</v>
+        <v>1.068294377839429</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.526543631806788</v>
+        <v>1.309749481784692</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.450007718349077</v>
+        <v>1.168435534591197</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.250113927734134</v>
+        <v>1.942334261221781</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.430223764402342</v>
+        <v>1.174934297157449</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.9579358643891922</v>
+        <v>0.6896228609567459</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.733657116385501</v>
+        <v>1.598985217177571</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.940297030682615</v>
+        <v>1.771201698525459</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.120609784595928</v>
+        <v>1.978054615955784</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.138939489941393</v>
+        <v>2.063964478190826</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007303</t>
+          <t>X &gt; 0.007307</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.927734363707543</v>
+        <v>2.494887926051184</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.234223684935685</v>
+        <v>3.538547327158568</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.147904518671403</v>
+        <v>2.518319813778128</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4407822088604334</v>
+        <v>-0.1842816816303312</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3076395043854347</v>
+        <v>-0.1081399389629638</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7068397895658975</v>
+        <v>-0.4201395099871519</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.306455530900557</v>
+        <v>-0.04288857966417936</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1157337986313678</v>
+        <v>0.003890859693896687</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1602199717944757</v>
+        <v>0.2490530636335748</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4424039440580998</v>
+        <v>0.5081012167143513</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.302630057497865</v>
+        <v>1.366502702596534</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.492813831072148</v>
+        <v>1.44162063089194</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.893684589538417</v>
+        <v>1.733528044507992</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.376005478625245</v>
+        <v>2.188693748608294</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.025117986294312</v>
+        <v>1.741005955234378</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.752394687177301</v>
+        <v>1.552677360081809</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.925797658031435</v>
+        <v>1.637473070896981</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.071286061118045</v>
+        <v>2.634885502681527</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.344892400817393</v>
+        <v>1.97995120796768</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.471667539407328</v>
+        <v>1.087241611068315</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.106977672972512</v>
+        <v>1.77116152571751</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.148917341716533</v>
+        <v>1.768288631177583</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.187820793892342</v>
+        <v>2.084383843581172</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.8187023215878</v>
+        <v>2.82426117055703</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.009186</t>
+          <t>X &gt; 0.009189</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.750130330177058</v>
+        <v>3.278962477286704</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.219864810022727</v>
+        <v>4.532306016395424</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.93222170084136</v>
+        <v>3.277611914503844</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.467387982150505</v>
+        <v>1.785659490808065</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.334605028400219</v>
+        <v>2.559576613077546</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.017811816001355</v>
+        <v>1.21725984426304</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.448870650907999</v>
+        <v>1.771503169361651</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.020283266305299</v>
+        <v>1.166732650990518</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.512898267768875</v>
+        <v>1.59451163563714</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.191110411281265</v>
+        <v>1.248235252861591</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.916297872992054</v>
+        <v>1.970245379909699</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.239052228942548</v>
+        <v>2.143438537882169</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.018145801184183</v>
+        <v>1.778171607837699</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.398570684136082</v>
+        <v>2.129637696329631</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.740427386555524</v>
+        <v>1.447483314444575</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.126688572471707</v>
+        <v>1.800107889202486</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.990654369946974</v>
+        <v>2.539552005012524</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.187472791314327</v>
+        <v>2.65012292295085</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.045898108890242</v>
+        <v>1.600478951546762</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.780255231075465</v>
+        <v>1.302427155159968</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.444345563863578</v>
+        <v>2.187510408577197</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.368499602454477</v>
+        <v>2.05412572552531</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.642974314936531</v>
+        <v>2.391106419476152</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.868801186901791</v>
+        <v>2.778524412608917</v>
       </c>
     </row>
     <row r="27">
@@ -4906,79 +4906,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.327280376607881</v>
+        <v>4.675195054067615</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.187722701764038</v>
+        <v>5.617407030244934</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.948906839984041</v>
+        <v>4.362712928353353</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.040733697035328</v>
+        <v>2.384172115683747</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.099365535245028</v>
+        <v>3.296732787465601</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.091112597836428</v>
+        <v>2.265547581582496</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.71358622470305</v>
+        <v>3.054623985191363</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.040952469193002</v>
+        <v>1.165545125941158</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.2816428383587</v>
+        <v>1.293474035625266</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.305539911326193</v>
+        <v>1.289501748326721</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.181193178986128</v>
+        <v>1.165697158970659</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.500053337291121</v>
+        <v>1.285154808459758</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.775297644936991</v>
+        <v>0.3682824929891808</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.749437891996379</v>
+        <v>1.308167243437261</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.8920914071648198</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.6101433496643054</v>
+        <v>0.1162812053757989</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.596385893325554</v>
+        <v>0.9251780980781987</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.491545189504379</v>
+        <v>1.708707860309843</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.707436570428698</v>
+        <v>1.046835108012111</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.8942823803967244</v>
+        <v>0.1815812337098208</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.351736212430694</v>
+        <v>0.9347780148942206</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.475890251021596</v>
+        <v>0.9807412786468888</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.75036496350365</v>
+        <v>1.345988977342316</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.874532710280377</v>
+        <v>1.507566475556267</v>
       </c>
     </row>
     <row r="28">
@@ -4988,161 +4988,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.498687770288967</v>
+        <v>5.130842659644507</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.680706837572224</v>
+        <v>5.395139905573288</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.534677452623924</v>
+        <v>5.160853966947016</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.271335836281956</v>
+        <v>2.782737482424501</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.48593296063391</v>
+        <v>3.782689546406807</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.156103281098211</v>
+        <v>3.429419070772234</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.934542194107088</v>
+        <v>4.420051344253807</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.622739018087863</v>
+        <v>2.839620696763554</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.405828267186017</v>
+        <v>2.457345524815004</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.149708456782612</v>
+        <v>2.171498111228324</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.165370166128</v>
+        <v>2.188631085016326</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.11142696423039</v>
+        <v>0.8916409672797201</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5050607630073358</v>
+        <v>0.03185089064528057</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.575971550643445</v>
+        <v>1.059127033293805</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.176226185879415</v>
+        <v>0.6320746922250748</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.152064688334121</v>
+        <v>0.5800899172663563</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.313484338921413</v>
+        <v>1.911057692307693</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.022115137690911</v>
+        <v>3.477468294152878</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.460804446076374</v>
+        <v>3.08039685050651</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.870448183505538</v>
+        <v>2.421891311229196</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.327902015539507</v>
+        <v>2.013100462899033</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.511123411643361</v>
+        <v>2.197005298456702</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.044665481638368</v>
+        <v>2.860530773574254</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.709765870902139</v>
+        <v>2.59963636802938</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01484</t>
+          <t>X &gt; 0.01483</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.309682921903722</v>
+        <v>4.993958637743056</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.095047466310099</v>
+        <v>6.838644136533965</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.01038530773846</v>
+        <v>5.932382090391513</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.884003726458268</v>
+        <v>3.249387557088518</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.314997706207812</v>
+        <v>4.715989695734827</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.441893220927106</v>
+        <v>3.827627134485525</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.1434427702523</v>
+        <v>5.820001568245836</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.805160654121131</v>
+        <v>4.121352901840702</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.200004726495202</v>
+        <v>4.24928181152481</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.84051661229617</v>
+        <v>4.846958539301987</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.761219363998727</v>
+        <v>4.770761498157192</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.362328617794539</v>
+        <v>2.055155153441994</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.592523441397788</v>
+        <v>0.9402630359912223</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.138229017248023</v>
+        <v>2.434189253303749</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.480085719667464</v>
+        <v>1.752034871418694</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.232430689877496</v>
+        <v>1.478807567902159</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.516953269212088</v>
+        <v>2.773528554778551</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.894382068937006</v>
+        <v>4.963058877294543</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.691833733549267</v>
+        <v>3.995163802735348</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.460239827205235</v>
+        <v>2.665680173639153</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.917693659239205</v>
+        <v>2.316264391903552</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.841847697830104</v>
+        <v>2.241101869948267</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.470932339390181</v>
+        <v>3.060188766826556</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.395100086166906</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="30">
@@ -5152,79 +5152,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.184480397485061</v>
+        <v>7.233235340854918</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.033109712672371</v>
+        <v>9.142500918944151</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.285046995519103</v>
+        <v>6.163668886018087</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.262049307954101</v>
+        <v>4.278163238934006</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.109664948943937</v>
+        <v>6.157777512627774</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.54990624421162</v>
+        <v>4.590573187591374</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.271407341980662</v>
+        <v>7.243767037427624</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.24647100639789</v>
+        <v>5.214708662984521</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.59800185643487</v>
+        <v>6.635741020944486</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.571811071228069</v>
+        <v>7.56382745675964</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.282551936097413</v>
+        <v>8.267096954122593</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.383715196404879</v>
+        <v>4.973273620340947</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.697234352256189</v>
+        <v>3.858381502890175</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.786199143931867</v>
+        <v>4.903250889732931</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.128055846351309</v>
+        <v>4.221096507847875</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>2.975717877464604</v>
+        <v>3.058262595633053</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.588525631316827</v>
+        <v>4.678520114942529</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.540453486447603</v>
+        <v>7.131842906332651</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>5.572938753834812</v>
+        <v>5.191132719685328</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.70301600485088</v>
+        <v>2.220542272670855</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.723788614177423</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.084623875475749</v>
+        <v>1.843322036460762</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>3.232461033372651</v>
+        <v>3.228023542813752</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.8465851120271</v>
+        <v>2.023978473292544</v>
       </c>
     </row>
     <row r="31">
@@ -5237,404 +5237,404 @@
         <v>178</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.280501201174772</v>
+        <v>9.585864892001126</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.260331144398002</v>
+        <v>7.663980402665977</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.82231209536701</v>
+        <v>6.409286300774397</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.547560323115277</v>
+        <v>5.258224884089074</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.458960861803952</v>
+        <v>7.217303615498118</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.960533789474376</v>
+        <v>5.698259567864923</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.121169375246943</v>
+        <v>8.813792080771876</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.157564672066897</v>
+        <v>6.832893983731964</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.760849606790586</v>
+        <v>7.519482111293179</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.111529436372081</v>
+        <v>7.840749051828027</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.632780089769959</v>
+        <v>10.34762093794073</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.859648663850045</v>
+        <v>5.601765240452671</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.860082102611905</v>
+        <v>5.604191558756106</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.447991990210255</v>
+        <v>8.149253586708461</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6.228050939820712</v>
+        <v>6.908439986946313</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>4.013449097718762</v>
+        <v>4.676447916380496</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.126722971977244</v>
+        <v>6.807204376163874</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.707275526583032</v>
+        <v>7.791638706756459</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.237773649080388</v>
+        <v>6.330123280270954</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.49203518938549</v>
+        <v>2.634095200190266</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.94948902141946</v>
+        <v>2.066650698809532</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.435440812819344</v>
+        <v>3.10880661260844</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.833511030919382</v>
+        <v>4.26575476306791</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.510487766460159</v>
+        <v>1.856424757542499</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.02049</t>
+          <t>X &gt; 0.02048</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>143</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.100411627826773</v>
+        <v>5.485151049667181</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.765634829476959</v>
+        <v>5.23924421396331</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.327615780445967</v>
+        <v>3.98455011207173</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.915361061702527</v>
+        <v>2.697703468819064</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.37677338635806</v>
+        <v>5.199923106497508</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.165138173854032</v>
+        <v>3.967967823606699</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.588993685767875</v>
+        <v>7.339552478040645</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.010082940315499</v>
+        <v>7.729076479076483</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.352269422929503</v>
+        <v>7.162560944316134</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.075857243396513</v>
+        <v>9.838731671319024</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.74851828415984</v>
+        <v>11.49985557481224</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.273964684907639</v>
+        <v>7.05660695367429</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.150802618051522</v>
+        <v>5.941714836223518</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.328325140206331</v>
+        <v>7.08236966367928</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.670181842625773</v>
+        <v>6.400215281794225</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.865967365967364</v>
+        <v>5.572630411725015</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.130651627591291</v>
+        <v>6.857638888888879</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.725111623070816</v>
+        <v>6.724754783727278</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.143800206792335</v>
+        <v>4.16143923309528</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.1348418209561686</v>
+        <v>0.2093590114875994</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4077043470098616</v>
+        <v>-0.3580854898931349</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.2157503908817304</v>
+        <v>0.9556408770404659</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.4143928501405085</v>
+        <v>0.7603298412228483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02237</t>
+          <t>X &gt; 0.02236</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>115</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.01132679961151</v>
+        <v>2.491856030510085</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.415680436044305</v>
+        <v>3.970087125840706</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>1.853324058431888</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.264707367570573</v>
+        <v>2.122990825140903</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>4.43363958159329</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.985448298511983</v>
+        <v>2.866435256556883</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.561325701578163</v>
+        <v>6.381698071910378</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.022244691607682</v>
+        <v>7.80091555953625</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.194166656131088</v>
+        <v>7.066775503703113</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.899511849659817</v>
+        <v>9.718999870552736</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.04313670921304</v>
+        <v>10.85330385067431</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.025256870982432</v>
+        <v>8.852583965168535</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.902094804126314</v>
+        <v>7.737691847717763</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.681015927679724</v>
+        <v>7.489457786284653</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.022872630099165</v>
+        <v>6.807303404399597</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.00856389986825</v>
+        <v>4.782400526667537</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.613777197673386</v>
+        <v>6.402658045977013</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.378501711243501</v>
+        <v>6.269773940815412</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.116132222602623</v>
+        <v>3.035960305892218</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.6643398543994792</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7178290049606062</v>
+        <v>-0.7651736124985078</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.815020685804207</v>
+        <v>2.607939727615182</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.959060615677572</v>
+        <v>3.3913043478261</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02425</t>
+          <t>X &gt; 0.02424</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.201822723188066</v>
+        <v>-1.103602337866697</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.9024248687060279</v>
+        <v>1.089515216673341</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.5355941803249635</v>
+        <v>-0.1651788852182392</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.248548199767704</v>
+        <v>-0.7575810840264623</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.513222303294775</v>
+        <v>5.064421751483955</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.261164099148246</v>
+        <v>2.782330967238131</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.367264195745705</v>
+        <v>6.865297735493222</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.747589336358487</v>
+        <v>10.21891387745046</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.789076518273191</v>
+        <v>10.34684278713457</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.8942096227245</v>
+        <v>14.42884007240303</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.16826926488643</v>
+        <v>14.70107508700737</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.67000766631648</v>
+        <v>13.20498093741412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.54684559946036</v>
+        <v>12.09008881996335</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.32576672301377</v>
+        <v>11.84185475853024</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.448111230311248</v>
+        <v>9.940188181523219</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>8.822985957132303</v>
+        <v>9.281980005220944</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.908581015276766</v>
+        <v>10.39761178861787</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.803740311455584</v>
+        <v>10.26472768345627</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.361095107014073</v>
+        <v>6.820653325236208</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.889404331616241</v>
+        <v>3.376703184929333</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-1.311678421715648</v>
+        <v>-0.8492779018172598</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>2.27101220224111</v>
+        <v>2.734096161593314</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>3.764999109845114</v>
+        <v>4.197242841993642</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.469654661499888</v>
+        <v>2.815591652582228</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02614</t>
+          <t>X &gt; 0.02613</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.466934069953709</v>
+        <v>-2.114055299539174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.25098623062236</v>
+        <v>-2.359962135243045</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.503408574458405</v>
+        <v>-1.349915578799987</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.856453126907354</v>
+        <v>6.945954852529248</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.144868588367054</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.720745991433219</v>
+        <v>7.736377874866051</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.79036063363668</v>
+        <v>11.71717171717171</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.83184781555138</v>
+        <v>11.84510062685582</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.40675822647141</v>
+        <v>15.33476341735076</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.68081786863333</v>
+        <v>14.17842700338367</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.40206846518534</v>
+        <v>13.90184504891238</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>13.27890639832922</v>
+        <v>12.78695293146161</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.60855215956379</v>
+        <v>11.11014744145707</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>10.95040886198323</v>
+        <v>10.42799305957201</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>10.09552042160738</v>
+        <v>9.560725649820242</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.961603284629902</v>
+        <v>9.456845238095234</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.85676258080872</v>
+        <v>9.323961132933633</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>5.72482787477653</v>
+        <v>5.252709074365129</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-1.877249294815677</v>
+        <v>-2.243006124813775</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>1.144097927671687</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1723 +5824,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02848</t>
+          <t>X &lt; -0.02845</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-5.217104992385899</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.503408574458405</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.957902402269674</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.84052076228011</v>
+        <v>11.38860274424162</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.06857207838976</v>
+        <v>12.02209216058033</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>10.28860028860028</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.83184781555138</v>
+        <v>11.84510062685582</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>3.906191988779341</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>9.892712717669383</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.05424237822882</v>
+        <v>11.04470219176952</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.931080311372703</v>
+        <v>9.929810074318745</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>9.681576012885635</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>3.704032050389017</v>
+        <v>4.713707345286302</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>6.703582792677381</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>3.742559523809518</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.737440317741999</v>
+        <v>-0.6760388670663602</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.377001787820014</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.02130142982201</v>
+        <v>2.042708160900517</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>1.967545638945232</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.567756267851479</v>
+        <v>6.496894409937887</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.39047473926589</v>
+        <v>9.191898272791285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.0266</t>
+          <t>X &lt; -0.02657</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.448076029094615</v>
+        <v>-5.349855643773246</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.192491381661299</v>
+        <v>-8.005401033693985</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.401594768041683</v>
+        <v>-2.031179472934959</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.114548787484424</v>
+        <v>-2.623581671743182</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.368937848402027</v>
+        <v>1.920137296591207</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.989638974258455</v>
+        <v>10.51080584234834</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.42250956747653</v>
+        <v>10.92054310722405</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.939478845615028</v>
+        <v>9.410803386707002</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.18578530463816</v>
+        <v>10.74355157349954</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.798411797276358</v>
+        <v>6.333042246954889</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.686929270763592</v>
+        <v>10.21973509288453</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.61299914442402</v>
+        <v>11.14797241552166</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.285017800459478</v>
+        <v>8.828261020962465</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.268758201121315</v>
+        <v>9.784846236637783</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.791337795107019</v>
+        <v>4.283414746318989</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>6.795363271266893</v>
+        <v>7.254357319355535</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>3.046988302964117</v>
+        <v>3.536019076305223</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.6723102321823688</v>
+        <v>-0.2113228601816814</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.7484004258503916</v>
+        <v>1.207958644072527</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.140065512926846</v>
+        <v>2.627364366239938</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.597519344960816</v>
+        <v>2.059919864859204</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.521673383551715</v>
+        <v>1.984757342903919</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>4.20578665025063</v>
+        <v>4.638030382399158</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.539592951244238</v>
+        <v>6.885529942326578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02471</t>
+          <t>X &lt; -0.02469</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.702071603227886</v>
+        <v>-6.067879253363124</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.09807289137362</v>
+        <v>-9.344089119370025</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-7.45445928734339</v>
+        <v>-6.558379180857564</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.167413306786131</v>
+        <v>-8.160882389766797</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.401162963006868</v>
+        <v>-3.385935479361073</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.949068529212958</v>
+        <v>5.86190721754609</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.217936171853225</v>
+        <v>7.087027225515392</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.91931656383484</v>
+        <v>5.77200577200577</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.960803745749544</v>
+        <v>5.899934681689878</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.167479906447745</v>
+        <v>4.093782176369523</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.482355875140286</v>
+        <v>6.386219211175877</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.244422798222899</v>
+        <v>8.129839276906608</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.10085256810148</v>
+        <v>4.994745139253808</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.940998181450794</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2.180814067543714</v>
+        <v>2.044154675733623</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>3.795609152752014</v>
+        <v>3.615559704654302</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.620875689243924</v>
+        <v>1.491477272727273</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.5247813411078681</v>
+        <v>-0.6616088526363484</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3088899601835422</v>
+        <v>-0.4471466254905749</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.8983640130497932</v>
+        <v>1.78764183977043</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.355817845083763</v>
+        <v>0.2100963282886781</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.300380046939964</v>
+        <v>1.145034816434411</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.636079249217943</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.60106332252527</v>
+        <v>6.277035357928376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02283</t>
+          <t>X &lt; -0.0228</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>127</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.034547900833537</v>
+        <v>-3.936327515512168</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.156726273986507</v>
+        <v>-4.969635926019194</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.65773744900175</v>
+        <v>-2.287322153895026</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.583289893641336</v>
+        <v>-2.092322777900094</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.919080366188609</v>
+        <v>-2.367880917999429</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.141901567940266</v>
+        <v>5.663068436030152</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.944756033656212</v>
+        <v>6.442789573403729</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.879143014099988</v>
+        <v>5.350467555191962</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.345827046408395</v>
+        <v>3.903593315269774</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.572911370371905</v>
+        <v>3.107541820050436</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.634372587336976</v>
+        <v>4.167178409457918</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.930426333495276</v>
+        <v>5.465399604592918</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.232461117032862</v>
+        <v>2.775704337535849</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.160988539798865</v>
+        <v>5.677076575315333</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.5658373682025655</v>
+        <v>1.057914319414536</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.947625864948705</v>
+        <v>2.406619913037346</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2389055783649354</v>
+        <v>0.7279363517060418</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.440738275062557</v>
+        <v>-0.9797509030618698</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.4374453193350831</v>
+        <v>0.02211289888705181</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.5368020654361061</v>
+        <v>1.024100918749198</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.005744102529924078</v>
+        <v>0.456656417368464</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.493213085667271</v>
+        <v>1.956297045019475</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.129892522558769</v>
+        <v>4.562136254707298</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>6.416264993744953</v>
+        <v>6.762201984827293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02095</t>
+          <t>X &lt; -0.02092</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.265847113431967</v>
+        <v>-4.167626728110598</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.850623911781781</v>
+        <v>-5.663533563814468</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.538642960812766</v>
+        <v>-3.168227665706041</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.501596980255513</v>
+        <v>-5.010629864514272</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.58738745280278</v>
+        <v>-4.036188004613599</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.473006406250562</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.32998853997028</v>
+        <v>4.075663589151752</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.051777095217204</v>
+        <v>3.770743145743133</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.206471824301715</v>
+        <v>1.398672055427255</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.062486965875287</v>
+        <v>1.22762056020791</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.594408243257341</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.20245129263953</v>
+        <v>4.348273620340947</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.192496772953227</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.858210349336822</v>
+        <v>2.985147441457066</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3156562186839906</v>
+        <v>-0.1970069404279897</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.2787307032590007</v>
+        <v>0.3642970783916724</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.113048068938596</v>
+        <v>-0.9895833333333286</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.475750407979902</v>
+        <v>-2.372467438494937</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.630928209445514</v>
+        <v>-1.53300521134917</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1862207642573637</v>
+        <v>-0.06841876629017918</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.7287669322233938</v>
+        <v>-0.6358632676709135</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.4532487415876361</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.614515906899875</v>
+        <v>2.657608695652179</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.425476106506785</v>
+        <v>4.370469701362708</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01906</t>
+          <t>X &lt; -0.01904</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.855506799295839</v>
+        <v>-2.757286413974469</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.52675345910243</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.361011381865403</v>
+        <v>-3.734327142145837</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-4.547649611834458</v>
+        <v>-3.803169131529977</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.830808505434369</v>
+        <v>-3.555167062205228</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.512938521654384</v>
+        <v>3.931609475730021</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.682788779562976</v>
+        <v>2.089407044649136</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.4045773348099</v>
+        <v>1.784486601240516</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.728538657878573</v>
+        <v>-1.752505955043958</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.977876821991039</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.169193633552084</v>
+        <v>-1.229202016810795</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6684590794020409</v>
+        <v>0.5884568664142478</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.983803516554616</v>
+        <v>-1.049995460460607</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3824191943003896</v>
+        <v>0.2724511063785329</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-3.027504322626939</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.797739297739298</v>
+        <v>-1.942640094383201</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.989857492917828</v>
+        <v>-3.093640924956375</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.623798725839542</v>
+        <v>-3.750085239542052</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-2.488502593548112</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>-0.1796753107928026</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.118105057410567</v>
+        <v>-1.270680021597613</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.135749960618611</v>
+        <v>-0.2987221247047316</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.726026339165024</v>
+        <v>1.515592988845896</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.295696731444401</v>
+        <v>3.971255041676848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01718</t>
+          <t>X &lt; -0.01716</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.420582796251345</v>
+        <v>-3.322362410929976</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.648190283463194</v>
+        <v>-2.246683343550153</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.739262907996796</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.904374758033285</v>
+        <v>-1.010079203721318</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.795720786136123</v>
+        <v>-1.285637343820653</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.992435876151731</v>
+        <v>4.157639874512228</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.327630049404242</v>
+        <v>2.481500593557051</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.602990033222596</v>
+        <v>1.736051515787196</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.03409421343413</v>
+        <v>-1.219720015057334</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.360581318042051</v>
+        <v>-1.575242875915436</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.979378818737267</v>
+        <v>-2.184065130033574</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4204432063861674</v>
+        <v>0.1825247216625385</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.14914743189852</v>
+        <v>-1.372896030149469</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.03094059405940186</v>
+        <v>-0.2995441884988779</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.581941034497099</v>
+        <v>-1.862755839106399</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.433982683982677</v>
+        <v>-1.741980454647972</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.014328392388734</v>
+        <v>-2.286389500734217</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.012026239067055</v>
+        <v>-3.300330874618282</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-2.645340013111273</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.8235747624604102</v>
+        <v>-1.109167664968588</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.258978073283593</v>
+        <v>-2.557669435071794</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.888395463264111</v>
+        <v>-2.192303322665843</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.274635036496349</v>
+        <v>-0.6270829343037647</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.435246995994667</v>
+        <v>0.9728926088517014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.0153</t>
+          <t>X &lt; -0.01528</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.931627255275934</v>
+        <v>-2.665433745654454</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.441816082600283</v>
+        <v>-2.560463388375865</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.913642960812773</v>
+        <v>-2.060771525355172</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9294643637680622</v>
+        <v>-0.3539397236691997</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.426416229781204</v>
+        <v>-1.333723215881207</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.013387397554524</v>
+        <v>3.752787854905606</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.519417053014351</v>
+        <v>2.253480490560207</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.88019477793636</v>
+        <v>1.948560047151588</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.688426343398028</v>
+        <v>-2.148863155840353</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.461342019434518</v>
+        <v>-2.94491465105969</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.909304037922411</v>
+        <v>-3.729017664624379</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.06104403155377724</v>
+        <v>-0.8365855345886288</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.867172186926886</v>
+        <v>-3.359928356264753</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.644207742073846</v>
+        <v>-1.847599037416174</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.468416021603858</v>
+        <v>-4.642429475639254</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.152007439011044</v>
+        <v>-3.376900104706912</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.646935406313432</v>
+        <v>-3.832893192488264</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.751776110134614</v>
+        <v>-3.965777297649865</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.174873898885373</v>
+        <v>-3.399202394447748</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.904995597942616</v>
+        <v>-2.128277921219755</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.808552596233561</v>
+        <v>-3.047835098656826</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-3.04005177796391</v>
+        <v>-3.475110296668447</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.040939384322435</v>
+        <v>-2.527250459277397</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.392133956386289</v>
+        <v>-1.985164101454181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01341</t>
+          <t>X &lt; -0.01339</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.070646540366063</v>
+        <v>-4.107598479523027</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.251485980747297</v>
+        <v>-1.528646558164752</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.252259675510174</v>
+        <v>-2.635295654374602</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6352675004867336</v>
+        <v>0.04618831730390838</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.969633829614381</v>
+        <v>-1.780133873559471</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.282718268178314</v>
+        <v>1.225802581441457</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9701227607745082</v>
+        <v>0.7156208541090194</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.057359821004809</v>
+        <v>-1.013801013801022</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.348234155125091</v>
+        <v>-3.734874953119757</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.829604641657212</v>
+        <v>-4.24602616343882</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.847090188999658</v>
+        <v>-4.543591718635042</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-1.686270539203214</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-2.516262371753697</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.096902693184767</v>
+        <v>-1.339995008685385</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-3.795862317295935</v>
+        <v>-4.016451384872433</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.618385016344199</v>
+        <v>-2.8853467962522</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.704326923076927</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.14868804664723</v>
+        <v>-3.407011598039098</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.932796665722904</v>
+        <v>-3.192549370893325</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.454405666250501</v>
+        <v>-2.693062640934052</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-2.975606857414505</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-3.491361210966701</v>
+        <v>-3.905470234070641</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.047295855209796</v>
+        <v>-2.522234609191131</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.830730447614357</v>
+        <v>-2.399473318580306</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01153</t>
+          <t>X &lt; -0.01151</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.757397229982082</v>
+        <v>-3.65756925684623</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.106465033277111</v>
+        <v>-1.484386098376682</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.720434529899421</v>
+        <v>-2.156391637992421</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7275359473916652</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.638858041038084</v>
+        <v>-1.386826055657693</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3283523182002526</v>
+        <v>0.394237480734823</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.07337467872814329</v>
+        <v>-0.1688259700129748</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.715652317334651</v>
+        <v>-2.56191346678586</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.25565819447678</v>
+        <v>-3.594077364526349</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.317673396579622</v>
+        <v>-3.694073175290931</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.569680105128604</v>
+        <v>-3.18981959920167</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2417944374865542</v>
+        <v>-0.9141973773388656</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.364956504342672</v>
+        <v>-1.797070933304724</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.6381680822110667</v>
+        <v>-0.8852121873132361</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.244178678369821</v>
+        <v>-2.495440815137975</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.9388912824931808</v>
+        <v>-1.238081111863544</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.5988747701815456</v>
+        <v>-0.8779244006187241</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.125516421870032</v>
+        <v>-2.402919874689836</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.146591865590253</v>
+        <v>-2.420476209028976</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.722779230977679</v>
+        <v>-1.973871202485078</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.265325398943709</v>
+        <v>-2.541315703865813</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.679454167030656</v>
+        <v>-3.080515348790932</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.692390380914397</v>
+        <v>-2.140825179057806</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.768222634137672</v>
+        <v>-2.30296417334727</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009647</t>
+          <t>X &lt; -0.00963</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.663445983488465</v>
+        <v>-1.50558969107356</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.01335976083838375</v>
+        <v>0.5713922246827536</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4041911649715573</v>
+        <v>0.1612333008366988</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.449160595502065</v>
+        <v>1.90626957682651</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.032868714180132</v>
+        <v>1.178364234192365</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.519255539378236</v>
+        <v>1.628923171477936</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.619296716070906</v>
+        <v>1.581504710647081</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3732004429678781</v>
+        <v>-0.2187428355652727</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4138652058005405</v>
+        <v>-0.6515615894325677</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.04174271389810258</v>
+        <v>-0.326117757549099</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1493624610491509</v>
+        <v>-0.6146304064961683</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.861964471380716</v>
+        <v>1.351778293238141</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.693000877807037</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.853601390673418</v>
+        <v>1.670895105008469</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.6229390091233924</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.8356465417534125</v>
+        <v>0.615465302690744</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.274248488745407</v>
+        <v>1.072332554517132</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.7877283956112464</v>
+        <v>0.5656166736545885</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.621940387222601</v>
+        <v>0.4062471250994406</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.190465586503599</v>
+        <v>0.994665345859346</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.647919418537569</v>
+        <v>0.4272208444786116</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.4965403466238882</v>
+        <v>0.1651424346728732</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.078334312162653</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.8109311777133286</v>
+        <v>0.4335538135122405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007764</t>
+          <t>X &lt; -0.007748</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.696834671752335</v>
+        <v>-1.702135930564587</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.08154291489704946</v>
+        <v>0.2821269584589601</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.903502555196546</v>
+        <v>-1.504766127244515</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5921530197444795</v>
+        <v>0.9129063450388841</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4373483291721172</v>
+        <v>-0.2013114614037264</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9346100812569773</v>
+        <v>0.9690840867013222</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4094589348045545</v>
+        <v>0.3285615798781905</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4966959950348695</v>
+        <v>-0.4400373797591755</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6803206285284702</v>
+        <v>-0.9303464917133937</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6670727825523812</v>
+        <v>-0.9536004598848251</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7750762315606678</v>
+        <v>-1.299603466918818</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.01753561290179562</v>
+        <v>-0.6488283889326212</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.7520467997373501</v>
+        <v>0.2455530639411734</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.477340163038392</v>
+        <v>1.079235540375151</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.6614681588332232</v>
+        <v>0.2425216530805088</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.3094828410285757</v>
+        <v>-0.1235313605573296</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.9642092371741384</v>
+        <v>0.5453857547655829</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.3861824134791405</v>
+        <v>-0.05117686662476473</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2866163811542464</v>
+        <v>-0.1458336502981652</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.7889196043714932</v>
+        <v>0.3778718055799928</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.4041021430300731</v>
+        <v>-0.03501319039116169</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.05049205545549285</v>
+        <v>-0.5738542285752004</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.6351750900859301</v>
+        <v>0.133458772931931</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.1794455470474077</v>
+        <v>-0.4923587375862866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00588</t>
+          <t>X &lt; -0.005866</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>776</v>
+        <v>801</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.934146734165218</v>
+        <v>-1.869764274578998</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.05157327887039287</v>
+        <v>-0.06644919656881143</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.547990235844459</v>
+        <v>-1.502854994898591</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7261948979170825</v>
+        <v>0.8320318270280183</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7167739194970792</v>
+        <v>0.7513275620115536</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.248751761284417</v>
+        <v>2.101107197394455</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.914413488894688</v>
+        <v>0.7540343756686099</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.455030849549118</v>
+        <v>0.1994260421226599</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8257397584688064</v>
+        <v>0.45219889687543</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8943967601457459</v>
+        <v>0.4052110720680844</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9878564108219052</v>
+        <v>0.4277581965350876</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.425479836422795</v>
+        <v>0.775395967407114</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.919117743234423</v>
+        <v>1.283475135848981</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.468257095285907</v>
+        <v>1.909148689896519</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.425004683456315</v>
+        <v>0.8524624728054704</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.24917337690124</v>
+        <v>0.9143907113504781</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.885474468421833</v>
+        <v>1.434730024968793</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.395524650351611</v>
+        <v>1.177001974738523</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.354676621776584</v>
+        <v>1.141776311746966</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.183370955493004</v>
+        <v>1.980582482149273</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.025933901776007</v>
+        <v>1.787669815974532</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.029617757448335</v>
+        <v>1.712507294019247</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.769927383066076</v>
+        <v>2.33067361450361</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.259068792754604</v>
+        <v>1.794002785008161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003997</t>
+          <t>X &lt; -0.003984</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>971</v>
+        <v>1000</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.220968817285915</v>
+        <v>-1.95216947164937</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2375740577613641</v>
+        <v>0.4403221575785636</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.856732391707084</v>
+        <v>-1.756375076064614</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.02803170743523253</v>
+        <v>0.1968726280081583</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6659221194986387</v>
+        <v>0.6756383426917765</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.828554268462788</v>
+        <v>1.788203143842026</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.1975280085879163</v>
+        <v>0.05066358915175329</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7949497588901835</v>
+        <v>0.7457431457431341</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.100363864275479</v>
+        <v>0.8736720554272424</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8989778280319385</v>
+        <v>0.5776205602079045</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4137710641667098</v>
+        <v>0.04985557481224134</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.117787528730481</v>
+        <v>0.8732736203409459</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.698095161237291</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.887693902860512</v>
+        <v>1.610147441457066</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.126881200762497</v>
+        <v>0.9279930595720103</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1812270549436903</v>
+        <v>0.08929707839166667</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.8686651541058481</v>
+        <v>0.7854166666666629</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.2504774276973976</v>
+        <v>0.3525325615050576</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7669947886508339</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.885247472799186</v>
+        <v>1.981581233709818</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.753378922902982</v>
+        <v>1.814136732329082</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.946393848143906</v>
+        <v>1.9389742103738</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.284521342104476</v>
+        <v>2.282608695652179</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.169486366305094</v>
+        <v>2.020469701362714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002114</t>
+          <t>X &lt; -0.002102</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1186</v>
+        <v>1217</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.228201522749771</v>
+        <v>-1.095644672645669</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.02058644300575452</v>
+        <v>0.08901745659369453</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.746976294146108</v>
+        <v>-1.611855116686442</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.003511443430895156</v>
+        <v>0.2106497757146713</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2154088744092277</v>
+        <v>0.3899576582341879</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.452231197789168</v>
+        <v>1.493902849541726</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1911826596258663</v>
+        <v>-0.2378610010121776</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1639583536051461</v>
+        <v>0.1596890030031943</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2535942287769259</v>
+        <v>0.170223779565184</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.03184174506417037</v>
+        <v>-0.1682298917230654</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5681851466375605</v>
+        <v>-0.7998568327473237</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.04322777838054037</v>
+        <v>-0.1725768315900282</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3109366017149213</v>
+        <v>0.1094086187488443</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5100257924952203</v>
+        <v>0.4363594381702924</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1481175050853381</v>
+        <v>-0.163625675021251</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8142347848230145</v>
+        <v>-0.8348606866042232</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4439502411282206</v>
+        <v>-0.445725486168179</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.4647573315040248</v>
+        <v>-0.3321017852492503</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.08079872368894314</v>
+        <v>0.0466989792835335</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.081162111262998</v>
+        <v>1.165147379971124</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.295554547165764</v>
+        <v>1.337226296831957</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.271176446307791</v>
+        <v>1.262063774876673</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.8389917537311149</v>
+        <v>0.8483441106069805</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4768935871775071</v>
+        <v>0.3575280415434889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002304</t>
+          <t>X &lt; -0.0002203</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1448</v>
+        <v>1483</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.081120150974627</v>
+        <v>-1.06605376960993</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4642667986007325</v>
+        <v>0.3976687134795682</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.7314830154949306</v>
+        <v>-0.6866593010947923</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5765493945734903</v>
+        <v>0.6353292233462255</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.690247728579827</v>
+        <v>0.7331072973998189</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.46430476069186</v>
+        <v>1.465356078214562</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.3892304606448178</v>
+        <v>0.372706599904447</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.01323890643443093</v>
+        <v>0.1060659433221645</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1118224220820423</v>
+        <v>-0.06414759464005471</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.7081087905695256</v>
+        <v>-0.6873626047752524</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.081919319473648</v>
+        <v>-1.050683508745713</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.184120558597137</v>
+        <v>-1.087077020252444</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8916752069452301</v>
+        <v>-0.7859205874672099</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.4933459622631133</v>
+        <v>-0.359845815454598</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.9450198861341121</v>
+        <v>-0.772276663961371</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.176510459029387</v>
+        <v>-0.9527123619319937</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.103958222297287</v>
+        <v>-0.8543001236232826</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.484091424397889</v>
+        <v>-1.122045995474025</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9929075451941429</v>
+        <v>-0.6378602349499687</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.008196958446248459</v>
+        <v>0.3184659268993073</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.2482213950633607</v>
+        <v>0.4927611423088649</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>0.3501677370090022</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.1847334935243481</v>
+        <v>0.3915095722536606</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.05695900242680096</v>
+        <v>0.09450881127504829</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001653</t>
+          <t>X &lt; 0.001662</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1752</v>
+        <v>1792</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.128142426814236</v>
+        <v>-1.103602337866697</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.02082165189477792</v>
+        <v>-0.04477316448002711</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9195785176245366</v>
+        <v>-0.881185490345338</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.0745607811604927</v>
+        <v>-0.05539666073859451</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.4702667633828455</v>
+        <v>0.4777008842752792</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.425597985842728</v>
+        <v>1.44418918115101</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.346397754786679</v>
+        <v>0.3472153132896949</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.126034910088066</v>
+        <v>-0.03733977022792345</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3924322735589172</v>
+        <v>-0.3788891917887867</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8492913877680124</v>
+        <v>-0.8649978241932033</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8266754034699701</v>
+        <v>-0.839888014931347</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.186699650756694</v>
+        <v>-1.140781036658495</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.083667857464995</v>
+        <v>-1.028679289078589</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.044165850032094</v>
+        <v>-0.9099418442572258</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.304129397897064</v>
+        <v>-1.145667654713698</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.335453511221424</v>
+        <v>-1.198202921608328</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.298722184035071</v>
+        <v>-1.078869047619044</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.744859816183904</v>
+        <v>-1.434967438494937</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.154487163208181</v>
+        <v>-0.8298802113491632</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6496811731340202</v>
+        <v>-0.3920794805758874</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.5320244713299829</v>
+        <v>-0.3456846962423441</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.7450903647138603</v>
+        <v>-0.5324543610547678</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.5509470730051902</v>
+        <v>-0.4562305900621126</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.7072024495369789</v>
+        <v>-0.6183695843515764</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003536</t>
+          <t>X &lt; 0.003544</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2079</v>
+        <v>2117</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7333161315444627</v>
+        <v>-0.8196220332749107</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5659911030073346</v>
+        <v>-0.5710605717994355</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.024329983713535</v>
+        <v>-1.048866763450413</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.05478726795450939</v>
+        <v>-0.01738820960124343</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.06315154067289086</v>
+        <v>-0.07863861609055789</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4852094069687425</v>
+        <v>0.5280985425609472</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.07500098630673335</v>
+        <v>0.04200068896344078</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.6063083202651498</v>
+        <v>-0.5659855400788061</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7769171799413002</v>
+        <v>-0.7414080576735955</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9962152508875661</v>
+        <v>-0.9452931597355132</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.077969404396818</v>
+        <v>-1.070899142168891</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.473295242515192</v>
+        <v>-1.415353090371653</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.131170442445026</v>
+        <v>-1.040107637808596</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.08459766839993</v>
+        <v>-0.9777127380422286</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.454971181807828</v>
+        <v>-1.329210530413818</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.675931981687384</v>
+        <v>-1.476456346265863</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.378194442405857</v>
+        <v>-1.107970201543061</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.010613083876919</v>
+        <v>-1.665984207507684</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.527112373909112</v>
+        <v>-1.120865390848458</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.312438694975327</v>
+        <v>-0.8590422901446928</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.394853605052496</v>
+        <v>-1.048593546367186</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.346502829228278</v>
+        <v>-0.9820461013881214</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.476558113419422</v>
+        <v>-1.210778172557546</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.572509136761468</v>
+        <v>-1.37291716684701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.00542</t>
+          <t>X &lt; 0.005425</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2356</v>
+        <v>2390</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7566365871161764</v>
+        <v>-0.7972024352653406</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9427679724389009</v>
+        <v>-0.9379301514133047</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6306678238553403</v>
+        <v>-0.6718704633746526</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4079730028810786</v>
+        <v>0.3826958331117183</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.01167412459071926</v>
+        <v>0.005478662053064909</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3490513071342463</v>
+        <v>0.3107726960072341</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2341834474624918</v>
+        <v>0.1228904448648507</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.01983815210559214</v>
+        <v>-0.07494938658894057</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.03863582729132986</v>
+        <v>-0.006795390315659233</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2379059165204964</v>
+        <v>-0.2363669136960596</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4045147293382954</v>
+        <v>-0.3996849431493246</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7858959282524651</v>
+        <v>-0.7778755647823274</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4882895635713425</v>
+        <v>-0.4894445840663408</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.4728330580729505</v>
+        <v>-0.4205928345780592</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.665269327711087</v>
+        <v>-0.5761910408463962</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.7906114489518359</v>
+        <v>-0.6843430889723408</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.7551805757684349</v>
+        <v>-0.5790184797768489</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.114043294830935</v>
+        <v>-0.8792666016748569</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7462694863269093</v>
+        <v>-0.4974403577926765</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5345311789252989</v>
+        <v>-0.2410129085495925</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.8826003708673014</v>
+        <v>-0.599252389009834</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.9758485106408301</v>
+        <v>-0.6325739067810119</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.058205252873101</v>
+        <v>-0.765508459159534</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.066723656442882</v>
+        <v>-0.8439654450807978</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007303</t>
+          <t>X &lt; 0.007307</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2569</v>
+        <v>2599</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6655766342975014</v>
+        <v>-0.8445785076743206</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.095840378731921</v>
+        <v>-1.146879658760867</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7732717311143915</v>
+        <v>-0.8494321850472986</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04361578570193814</v>
+        <v>-0.003445956468297595</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0004608444108313847</v>
+        <v>0.01062111765546803</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1318570917924617</v>
+        <v>0.07396646028018239</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.00142942972957627</v>
+        <v>-0.08596855507532553</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.06095528143949736</v>
+        <v>-0.1006114206421316</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.1523112676976979</v>
+        <v>-0.1428346624230414</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2439040344880681</v>
+        <v>-0.2643149236630506</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5292652201558639</v>
+        <v>-0.5463411213076128</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5917733798991094</v>
+        <v>-0.570538831619082</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7221287983581561</v>
+        <v>-0.6639176128345525</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8816687493992106</v>
+        <v>-0.8129294816198538</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.7631130178535557</v>
+        <v>-0.6647349127250308</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.6735804648426011</v>
+        <v>-0.6036232755906283</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.7298276989074495</v>
+        <v>-0.5920746761574947</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.106513062922808</v>
+        <v>-0.8788641295299513</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.8678548048626737</v>
+        <v>-0.6259255653314639</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.5804941450599372</v>
+        <v>-0.2959101091143381</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.7891658093422436</v>
+        <v>-0.4785912399679546</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8031451437664217</v>
+        <v>-0.4383247507650978</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.8169502115936211</v>
+        <v>-0.5794536360138451</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.025584066675634</v>
+        <v>-0.8570216414614436</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.009186</t>
+          <t>X &lt; 0.009189</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2755</v>
+        <v>2785</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6869566235184195</v>
+        <v>-0.8095077570495093</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.038686974844843</v>
+        <v>-1.072307688189021</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7633185195726924</v>
+        <v>-0.8065455062494848</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4468277772263107</v>
+        <v>-0.4854152722395924</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6543066447219772</v>
+        <v>-0.6339071459373997</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3389362432481704</v>
+        <v>-0.3498163170120847</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4408717556499013</v>
+        <v>-0.5163969192621352</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3374990551538204</v>
+        <v>-0.3714488313342201</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4560595313531977</v>
+        <v>-0.4382591520252745</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3772122747254087</v>
+        <v>-0.3897629523368877</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.552292257431624</v>
+        <v>-0.5631598429001983</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6295115856572409</v>
+        <v>-0.604201272055036</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5741526003913933</v>
+        <v>-0.5146001978633237</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6654411369475639</v>
+        <v>-0.5983952721107784</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.5057927982293862</v>
+        <v>-0.4337663659217057</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5993131898273063</v>
+        <v>-0.5187819162223306</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8056416229669807</v>
+        <v>-0.6585689706762423</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8529676681558911</v>
+        <v>-0.6478265049222216</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5795199513104237</v>
+        <v>-0.361550992318648</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.5163011643658635</v>
+        <v>-0.2546844754463748</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.6749497919202767</v>
+        <v>-0.4271559068091548</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.656790198742641</v>
+        <v>-0.3586918578488252</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.7236553557996857</v>
+        <v>-0.4741237998594912</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.7780988686670014</v>
+        <v>-0.6003561514200442</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2918</v>
+        <v>2947</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.7657195190121016</v>
+        <v>-0.8239506051791565</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9123155387388948</v>
+        <v>-0.9506957259766295</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7319950207378625</v>
+        <v>-0.7681347289030782</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4385860810729554</v>
+        <v>-0.4632160714108267</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6191165839782542</v>
+        <v>-0.5848437367745873</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4472004078097029</v>
+        <v>-0.4430230048401498</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5523136942029865</v>
+        <v>-0.6102501164319989</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2655541102192345</v>
+        <v>-0.2868905712507654</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3069533058940408</v>
+        <v>-0.2752612327542678</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3095696164330803</v>
+        <v>-0.3069322853205492</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2889249827132687</v>
+        <v>-0.2864033204774898</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3431204157840142</v>
+        <v>-0.3063873966082085</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2166348641792624</v>
+        <v>-0.1472136140986393</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3833842030819596</v>
+        <v>-0.3077630063041283</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.2350240625801305</v>
+        <v>-0.1556513245474349</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1876456876456842</v>
+        <v>-0.1033395011807769</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3557508588111915</v>
+        <v>-0.207219912905785</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.508728408306844</v>
+        <v>-0.3061712050371881</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3752182362767442</v>
+        <v>-0.1595746039518176</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.2365868872281851</v>
+        <v>0.0210790280769757</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3138577622355143</v>
+        <v>-0.07130609088096662</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3350686530879869</v>
+        <v>-0.04467017374564364</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.3827628199838458</v>
+        <v>-0.1403638187692593</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.4040142396853597</v>
+        <v>-0.2007043739681293</v>
       </c>
     </row>
     <row r="28">
@@ -7632,161 +7632,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3032</v>
+        <v>3059</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5956604729604607</v>
+        <v>-0.6799071445061742</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6182704889190163</v>
+        <v>-0.6808212305896006</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6298945990827605</v>
+        <v>-0.6812484990393841</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3743845908749819</v>
+        <v>-0.4093192165168844</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5279612232945965</v>
+        <v>-0.5040218808350971</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4866380590963573</v>
+        <v>-0.4919539750247708</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5841153574199112</v>
+        <v>-0.6497275451376794</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4171468695857925</v>
+        <v>-0.4473445621146936</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3898066231517987</v>
+        <v>-0.366249666686258</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3558604641832659</v>
+        <v>-0.3608786241314093</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3585087229985788</v>
+        <v>-0.363721448686448</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2240394470103979</v>
+        <v>-0.1973107740436433</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1447565236614565</v>
+        <v>-0.08511947686162813</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2806528597614744</v>
+        <v>-0.2162164918980451</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.2285575758504805</v>
+        <v>-0.1602422345456347</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2262759170653865</v>
+        <v>-0.1544937712815297</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3736042350061339</v>
+        <v>-0.2910539215686256</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5906141258346622</v>
+        <v>-0.4566177652923216</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5198930311518097</v>
+        <v>-0.3728744923949137</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.4453750636085445</v>
+        <v>-0.2563272630222002</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3754466541261365</v>
+        <v>-0.1701769931611068</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.398730711404248</v>
+        <v>-0.1606008141440185</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.4673073081745542</v>
+        <v>-0.2765609676364704</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.4246757329913962</v>
+        <v>-0.2752478533937435</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01484</t>
+          <t>X &lt; 0.01483</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3136</v>
+        <v>3163</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4109547765098611</v>
+        <v>-0.4756245261603027</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5704924578698325</v>
+        <v>-0.6104341302084251</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5023628594186036</v>
+        <v>-0.557864115186689</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3421278835835651</v>
+        <v>-0.3459573204336692</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4699968377108377</v>
+        <v>-0.4466210754797402</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3921355071113695</v>
+        <v>-0.3982367552632837</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5435628439967815</v>
+        <v>-0.6085863320584508</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4230107828448695</v>
+        <v>-0.454509061066446</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.458697388037308</v>
+        <v>-0.4349372160959319</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5149330396770324</v>
+        <v>-0.519224865659595</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5084902727216516</v>
+        <v>-0.5130033712275193</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2923955516146535</v>
+        <v>-0.2666253695580494</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2210982083947499</v>
+        <v>-0.1635635555247248</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3598356656015369</v>
+        <v>-0.2985701833060332</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.2994528483829626</v>
+        <v>-0.2355140494327301</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2775850104094388</v>
+        <v>-0.211334833140711</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3926691496270323</v>
+        <v>-0.2966313737884576</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6059723152696534</v>
+        <v>-0.4611210415290756</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.498612458542965</v>
+        <v>-0.341475502120332</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3885201673739758</v>
+        <v>-0.1901001822193891</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3388658901497408</v>
+        <v>-0.1254334320198396</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3320128719866844</v>
+        <v>-0.08701377571534863</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.3891951257536022</v>
+        <v>-0.1911503938198393</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3823550448216722</v>
+        <v>-0.2268271686973549</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3189</v>
+        <v>3215</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4652555816760469</v>
+        <v>-0.5432451573004542</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.596614257468481</v>
+        <v>-0.6490346464003025</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4292192848003111</v>
+        <v>-0.464019744913962</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3148176097351012</v>
+        <v>-0.358625840992147</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4461779764935585</v>
+        <v>-0.4622715959448698</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3352903031880956</v>
+        <v>-0.3810738473612716</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5283431258920785</v>
+        <v>-0.6013810205136707</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.383303704241186</v>
+        <v>-0.4551245332156455</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4800992071919268</v>
+        <v>-0.5266999222540889</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.548424188565221</v>
+        <v>-0.6231546335905378</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5999396289451724</v>
+        <v>-0.674462043053758</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.3922213627216991</v>
+        <v>-0.437058368489339</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3411117176128187</v>
+        <v>-0.3548400985995812</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4187570992172596</v>
+        <v>-0.4297470012625837</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3705254175936759</v>
+        <v>-0.3794603565770558</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.2892152681017279</v>
+        <v>-0.2968166215151271</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4046153582388925</v>
+        <v>-0.382451574476903</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6161230421075174</v>
+        <v>-0.5281637393964047</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4756567295086782</v>
+        <v>-0.3576320770208099</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2703277041632433</v>
+        <v>-0.1119511045986386</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1991409805517605</v>
+        <v>-0.0264105313525036</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2249558787182977</v>
+        <v>-0.02090137282993254</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.307942246527702</v>
+        <v>-0.1505172763540443</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2083772928553955</v>
+        <v>-0.09492687717538217</v>
       </c>
     </row>
     <row r="31">
@@ -7878,407 +7878,407 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3240</v>
+        <v>3265</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5302127278971867</v>
+        <v>-0.5459732446910692</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.419523359973077</v>
+        <v>-0.4105664305217118</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3691780727416329</v>
+        <v>-0.3704727189784975</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3290509679855731</v>
+        <v>-0.3372132993498411</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4329305641866483</v>
+        <v>-0.4131679010497891</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.351541585919648</v>
+        <v>-0.361201382162136</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5229609852902612</v>
+        <v>-0.5603086754017355</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4152619850294244</v>
+        <v>-0.45181782986662</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.448456732635357</v>
+        <v>-0.459173324261684</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4663522373501507</v>
+        <v>-0.5059059803656112</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6049606991992533</v>
+        <v>-0.6434919991883632</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3433724674848619</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3414289277020117</v>
+        <v>-0.3820765123770045</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4828636709824821</v>
+        <v>-0.5208849348410425</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4149610846224192</v>
+        <v>-0.4519336132052558</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2948201224063354</v>
+        <v>-0.3309963201413311</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4105127823750863</v>
+        <v>-0.4169373535106473</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4971177803046203</v>
+        <v>-0.4401279889536482</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.4170626591552775</v>
+        <v>-0.3300379430714031</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.212006152278974</v>
+        <v>-0.09748853373203303</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.18128876444257</v>
+        <v>-0.03477664385701473</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2078851962331782</v>
+        <v>-0.06114826360047232</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2852413308499493</v>
+        <v>-0.1543172075933796</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1575660551517259</v>
+        <v>-0.05334346862196782</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.02049</t>
+          <t>X &lt; 0.02048</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2448495391445178</v>
+        <v>-0.2614707979480499</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2297943697738987</v>
+        <v>-0.2203312151243182</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1951963588710228</v>
+        <v>-0.1938300753446001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1630157966439825</v>
+        <v>-0.1671152516790784</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2693091285769214</v>
+        <v>-0.2451241107016102</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2171157701976654</v>
+        <v>-0.2221470727186272</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3645023928800839</v>
+        <v>-0.3973460610291824</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3824030301103036</v>
+        <v>-0.4138345314815979</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3540030280237971</v>
+        <v>-0.359399761108655</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4711175209695497</v>
+        <v>-0.5045708071328718</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5445074249242694</v>
+        <v>-0.5774391111780943</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3495000766769891</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2986779075093438</v>
+        <v>-0.3334613974119378</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3496240034962383</v>
+        <v>-0.3827507150856917</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3198695189237597</v>
+        <v>-0.3519343890374245</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2860235003092129</v>
+        <v>-0.3170228490349984</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3409693778505556</v>
+        <v>-0.3426535087719245</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3667906837050054</v>
+        <v>-0.3064689513542405</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2547585515225137</v>
+        <v>-0.1649664704290714</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.08034403009427393</v>
+        <v>0.03716706477249687</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.05570735071756161</v>
+        <v>0.09324030592085109</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.08279147006476961</v>
+        <v>0.06639014493908491</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1563505432118575</v>
+        <v>-0.02320772361471768</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.09187950346007767</v>
+        <v>0.01440909530211343</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02237</t>
+          <t>X &lt; 0.02236</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3303</v>
+        <v>3328</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.09304194205493843</v>
+        <v>-0.1097909072150784</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1410374456163694</v>
+        <v>-0.1307252628291025</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.08873321352035646</v>
+        <v>-0.08504367526399648</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1229857855519327</v>
+        <v>-0.1232307010843314</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2010990723091055</v>
+        <v>-0.172993145079829</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1477488788704164</v>
+        <v>-0.1488732326962321</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2702615168608204</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3204593706426024</v>
+        <v>-0.3481246376849256</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2919302592448645</v>
+        <v>-0.2930544556439685</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.3844141704474069</v>
+        <v>-0.4137293350330395</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4246872798780572</v>
+        <v>-0.4537372395590182</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3543090021895807</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3134072818855884</v>
+        <v>-0.3432362322805815</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3054274639658345</v>
+        <v>-0.3342637062804243</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2814751959877881</v>
+        <v>-0.3094170123704387</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.2126749219772464</v>
+        <v>-0.2400882289546473</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2682666746502775</v>
+        <v>-0.2663529794041253</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2947346533484492</v>
+        <v>-0.2315658483359186</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1818016399703382</v>
+        <v>-0.08942778037676646</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.09797646447778163</v>
+        <v>0.02277006589234531</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.04790081116276923</v>
+        <v>0.1036262218185726</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1359100515502689</v>
+        <v>0.01629472704547652</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1762694190629333</v>
+        <v>-0.04046129533610099</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.08271827367360629</v>
+        <v>0.02551777828578849</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02425</t>
+          <t>X &lt; 0.02424</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3336</v>
+        <v>3361</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006071612379287217</v>
+        <v>0.003472562669550427</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04471265508136213</v>
+        <v>-0.01968934270894351</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03681841508743133</v>
+        <v>-0.01661619320457675</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.04793190278233794</v>
+        <v>-0.03077922860774152</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1881698671097922</v>
+        <v>-0.1419572353828329</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1335011712969347</v>
+        <v>-0.1164917469434243</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2325772276610749</v>
+        <v>-0.2438301941519754</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3148415385469292</v>
+        <v>-0.3247928329361613</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3160249803693773</v>
+        <v>-0.2986028260893434</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4152188446945075</v>
+        <v>-0.4260831434957879</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4225441559381338</v>
+        <v>-0.4333098075232655</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3854750390482096</v>
+        <v>-0.396575178947522</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3560598054526665</v>
+        <v>-0.3675971447966617</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3503518313576635</v>
+        <v>-0.3612260382225543</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3032468213858479</v>
+        <v>-0.3138467030392675</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2890749601275928</v>
+        <v>-0.2989190094682215</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3155494940510479</v>
+        <v>-0.2962935471100607</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.312883296432183</v>
+        <v>-0.2632084542359507</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2288699246326544</v>
+        <v>-0.1500580931079298</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1440409728966898</v>
+        <v>-0.03684372914307232</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.03993794150760976</v>
+        <v>0.09689535301874486</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1278245482594116</v>
+        <v>0.03942024070386907</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1650680601703129</v>
+        <v>-0.02643354111165053</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1331411506308982</v>
+        <v>-0.02219617188929135</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02614</t>
+          <t>X &lt; 0.02613</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3349</v>
+        <v>3373</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.006839719308246117</v>
+        <v>0.02038858402132604</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.04395484823008644</v>
+        <v>0.05535450687772681</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01304948900268244</v>
+        <v>-0.00492477825760318</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.02686412184054632</v>
+        <v>-0.02112942242762728</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1975418471020802</v>
+        <v>-0.1623672498966329</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1423651336492711</v>
+        <v>-0.1364425437054635</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2143337057948074</v>
+        <v>-0.2366520450665348</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2973495974290756</v>
+        <v>-0.3184055706923843</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2983629411392457</v>
+        <v>-0.2918533282799558</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3704205347278275</v>
+        <v>-0.3921757196858024</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3766444769339188</v>
+        <v>-0.3688685834866376</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3705363065139125</v>
+        <v>-0.3627677385955366</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3455760033270963</v>
+        <v>-0.3378359911996611</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3109718533627586</v>
+        <v>-0.3027996469260259</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2963650113540766</v>
+        <v>-0.2875598676899642</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2799442142605741</v>
+        <v>-0.2706851753794055</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2770348456494176</v>
+        <v>-0.2388436883629197</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2747737374702908</v>
+        <v>-0.206331007598223</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.190237848175947</v>
+        <v>-0.09280390880328326</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1348258808618468</v>
+        <v>-0.008824451809871903</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.03322798804662597</v>
+        <v>0.1224305711916429</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.0912240432189293</v>
+        <v>0.09452976592935158</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09739623052620061</v>
+        <v>0.05943145795212246</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.09572706875814418</v>
+        <v>0.03345517423552735</v>
       </c>
     </row>
   </sheetData>
